--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sophiehuebler/Documents/ODSi/ODSiData/Merging/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EAFFBB-0537-C349-9C68-2885A3E91EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B128DF-FC4F-A44E-A3EA-C2B5474F3AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30800" yWindow="-16840" windowWidth="28360" windowHeight="22280" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34300" yWindow="-13260" windowWidth="30240" windowHeight="18880" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Artacho" sheetId="1" r:id="rId1"/>
     <sheet name="DAmico" sheetId="2" r:id="rId2"/>
     <sheet name="Fujimoto" sheetId="3" r:id="rId3"/>
     <sheet name="Ingham" sheetId="4" r:id="rId4"/>
-    <sheet name="Liu" sheetId="5" r:id="rId5"/>
-    <sheet name="Vallet" sheetId="6" r:id="rId6"/>
+    <sheet name="Jarosch" sheetId="7" r:id="rId5"/>
+    <sheet name="Liu" sheetId="5" r:id="rId6"/>
+    <sheet name="OrbergMO" sheetId="8" r:id="rId7"/>
+    <sheet name="Spindelboek" sheetId="9" r:id="rId8"/>
+    <sheet name="Vallet" sheetId="6" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" iterate="1"/>
 </workbook>
 </file>
 
@@ -7964,6 +7967,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024A0273-05BE-A34B-973C-4C00A08D1FA9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9330,7 +9342,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6D3E53-6B2C-F244-8835-A3CC98F2A4BF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5766487-1A47-E645-A00E-FD9084CF2771}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -1,34 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11004"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sophiehuebler/Documents/ODSi/ODSiData/Merging/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B128DF-FC4F-A44E-A3EA-C2B5474F3AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34300" yWindow="-13260" windowWidth="30240" windowHeight="18880" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Artacho" sheetId="1" r:id="rId1"/>
     <sheet name="DAmico" sheetId="2" r:id="rId2"/>
     <sheet name="Fujimoto" sheetId="3" r:id="rId3"/>
     <sheet name="Ingham" sheetId="4" r:id="rId4"/>
-    <sheet name="Jarosch" sheetId="7" r:id="rId5"/>
-    <sheet name="Liu" sheetId="5" r:id="rId6"/>
-    <sheet name="OrbergMO" sheetId="8" r:id="rId7"/>
-    <sheet name="Spindelboek" sheetId="9" r:id="rId8"/>
-    <sheet name="Vallet" sheetId="6" r:id="rId9"/>
+    <sheet name="Jarosch" sheetId="5" r:id="rId5"/>
+    <sheet name="Liu" sheetId="6" r:id="rId6"/>
+    <sheet name="OrbergMO" sheetId="7" r:id="rId7"/>
+    <sheet name="Spindelboek" sheetId="8" r:id="rId8"/>
+    <sheet name="Vallet" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="124519" iterate="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="990">
   <si>
     <t>column_name</t>
   </si>
@@ -1728,6 +1722,186 @@
     <t>Binary event indicator: disease relapse. Derived as 1 - Sens.0.relapse.1.death.Now. 0 = no relapse; 1 = relapsed.</t>
   </si>
   <si>
+    <t>Patient 01 | Patient 02 | Patient 03 | Patient 04 | Patient 05</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>ChipCytometry | scRNAseq | scRNAseq+SP</t>
+  </si>
+  <si>
+    <t>Biopsy</t>
+  </si>
+  <si>
+    <t>biopsy_c01 | biopsy_c08 | biopsy_c12 | biopsy_c13 | biopsy_c22</t>
+  </si>
+  <si>
+    <t>GvHD (Lerner)</t>
+  </si>
+  <si>
+    <t>1 | 3 | 0 | 2 | 1.5</t>
+  </si>
+  <si>
+    <t>GvHD</t>
+  </si>
+  <si>
+    <t>d after aHSCT</t>
+  </si>
+  <si>
+    <t>115 | 248 | 76 | 39 | 33</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>Sigmoid | Colon 60 cm | Colon 30 cm | Colon 20 cm | Sigmoid 30 cm</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>FFPE | SCS</t>
+  </si>
+  <si>
+    <t>clinical GvHD total</t>
+  </si>
+  <si>
+    <t>4 | 0 | 2 | 3 | 1</t>
+  </si>
+  <si>
+    <t>clinical GvHD GI</t>
+  </si>
+  <si>
+    <t>4 | 3 | 0 | 1 | 2</t>
+  </si>
+  <si>
+    <t>steroid treatment</t>
+  </si>
+  <si>
+    <t>yes | no</t>
+  </si>
+  <si>
+    <t>steroid refractory</t>
+  </si>
+  <si>
+    <t>ABX</t>
+  </si>
+  <si>
+    <t>16S data</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Indoxylsulfate [µmol/mmol creatinine]</t>
+  </si>
+  <si>
+    <t>81.2 | 14.6 | 1.19 | 0.08 | 0.146</t>
+  </si>
+  <si>
+    <t>Richness</t>
+  </si>
+  <si>
+    <t>103 | 90 | 97 | 70 | 40</t>
+  </si>
+  <si>
+    <t>Simpson</t>
+  </si>
+  <si>
+    <t>0.8677527 | 0.864635 | 0.9036373 | 0.5434547 | 0.1455527</t>
+  </si>
+  <si>
+    <t>Shannon</t>
+  </si>
+  <si>
+    <t>2.7097513 | 2.8369634 | 2.6678665 | 1.1706946 | 0.3644036</t>
+  </si>
+  <si>
+    <t>Biopsy ST2 [pg/ml]</t>
+  </si>
+  <si>
+    <t>79258 | 85484 | 50197 | 26249 | 6521</t>
+  </si>
+  <si>
+    <t>Biopsy Reg3a [ng/ml]</t>
+  </si>
+  <si>
+    <t>39 | 56 | 29 | 26 | 34</t>
+  </si>
+  <si>
+    <t>Biopsy MAP</t>
+  </si>
+  <si>
+    <t>0.2362524 | 0.2691285 | 0.1593457 | 0.0956041 | 0.0346206</t>
+  </si>
+  <si>
+    <t>age of patient</t>
+  </si>
+  <si>
+    <t>55-60 | 40-44 | 65-70 | 45-50 | 50-54</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>m | f</t>
+  </si>
+  <si>
+    <t>B-NHL | AML | MPN | MDS | MDS/MPN</t>
+  </si>
+  <si>
+    <t>Donor type</t>
+  </si>
+  <si>
+    <t>unrelated | haplo | sibling</t>
+  </si>
+  <si>
+    <t>HLA</t>
+  </si>
+  <si>
+    <t>mismatch | ident | haplo</t>
+  </si>
+  <si>
+    <t>Donor age</t>
+  </si>
+  <si>
+    <t>25-30 | 55-60 | 45-50 | 15-20 | 20-24</t>
+  </si>
+  <si>
+    <t>Donor gender</t>
+  </si>
+  <si>
+    <t>Conditioning</t>
+  </si>
+  <si>
+    <t>Thio/Treo/Flud | FBM | FTM | Treo/Flud | TBI/VP16</t>
+  </si>
+  <si>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t>RIC | Standard</t>
+  </si>
+  <si>
+    <t>GvHD prophylaxis</t>
+  </si>
+  <si>
+    <t>CyA/MTX | PTCy/Tacro/MMF | CyA/MMF | CyA/Bortezomib</t>
+  </si>
+  <si>
+    <t>Stem cell source</t>
+  </si>
+  <si>
+    <t>PBSC | BM</t>
+  </si>
+  <si>
+    <t>Bx Timepoint</t>
+  </si>
+  <si>
+    <t>Course | Screening | Sceening | Onset</t>
+  </si>
+  <si>
     <t>SAMEA4506927 | SAMEA4506928 | SAMEA4506929 | SAMEA4506930 | SAMEA4506931</t>
   </si>
   <si>
@@ -1938,9 +2112,6 @@
     <t>methotrexate</t>
   </si>
   <si>
-    <t>yes | no</t>
-  </si>
-  <si>
     <t>Binary indicator: whether the recipient received methotrexate as part of GvHD prophylaxis. Values: yes | no. NA for Donor rows.</t>
   </si>
   <si>
@@ -2172,6 +2343,207 @@
     <t>Derived column: case_when(is.na(agvhd_organ) ~ NA, agvhd_organ == 'None documented' ~ 0, TRUE ~ 1). Redundant with agvhd_organ (source) and partially with agvhd_gut (binary for gut involvement only). I would keep agvhd as the primary binary endpoint for analysis (it is the outcome in the paper's logistic regression models) and agvhd_organ for organ-level detail. See agvhd_organ notes for the full redundancy group (agvhd_organ, agvhd, agvhd_gut).</t>
   </si>
   <si>
+    <t>ERR10966602 | ERR10966608 | ERR10966618 | ERR10966620 | ERR10966621</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>sample_alias</t>
+  </si>
+  <si>
+    <t>MO16S_017 | MO16S_023 | MO16S_033 | MO16S_035 | MO16S_036</t>
+  </si>
+  <si>
+    <t>M-AF-2 | M-AG-4 | M-AI-2 | M-AI-4 | M-AI-5</t>
+  </si>
+  <si>
+    <t>M-AF | M-AG | M-AI | M-AJ | M-AK</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>MUC | REG</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>0 | -7 | 14 | 28 | 35</t>
+  </si>
+  <si>
+    <t>0 | COND | 14 | 28 | POST</t>
+  </si>
+  <si>
+    <t>Antibiotic_therapy</t>
+  </si>
+  <si>
+    <t>No ABX | ABX</t>
+  </si>
+  <si>
+    <t>Antifungal_therapy</t>
+  </si>
+  <si>
+    <t>no Antifungals | Antifungals</t>
+  </si>
+  <si>
+    <t>Antiviral_therapy</t>
+  </si>
+  <si>
+    <t>Prophylaxe</t>
+  </si>
+  <si>
+    <t>1 | 2 | 0</t>
+  </si>
+  <si>
+    <t>GVHD</t>
+  </si>
+  <si>
+    <t>0 | 2 | 1</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>ERR13060015 | ERR13060016 | ERR13060017 | ERR13060018 | ERR13060019</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>1 | 2 | 3 | 4 | 5</t>
+  </si>
+  <si>
+    <t>A | B | C | D | E</t>
+  </si>
+  <si>
+    <t>patient | donor</t>
+  </si>
+  <si>
+    <t>K1836-8 | K1836-9 | K1836-20 | K1836-21 | K1836-22</t>
+  </si>
+  <si>
+    <t>aGvHD_pre-treatment | aGvHD_pre-FMT1 | aGvHD_d03-post-FMT1 | aGvHD_pre-FMT2 | aGvHD_d02-post-FMT3</t>
+  </si>
+  <si>
+    <t>fmt_cycle</t>
+  </si>
+  <si>
+    <t>FMT1 | FMT2 | FMT3 | FMT4 | FMT5</t>
+  </si>
+  <si>
+    <t>fmt_cycle_day</t>
+  </si>
+  <si>
+    <t>37 | 48 | 58 | 77 | 89</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>&lt;37 | 40 | &lt;48 | 60 | &lt;58</t>
+  </si>
+  <si>
+    <t>53 | 60 | 61 | 59 | 24</t>
+  </si>
+  <si>
+    <t>diagnosis</t>
+  </si>
+  <si>
+    <t>MDS | Secondary AML/MDS | AML | PMF | Multiple myeloma</t>
+  </si>
+  <si>
+    <t>Donor sex</t>
+  </si>
+  <si>
+    <t>female | male | female; male</t>
+  </si>
+  <si>
+    <t>Donor match</t>
+  </si>
+  <si>
+    <t>URD (HLA 9/10, HLA-DQB1 mismatch) | URD | MSD | HID; HID | MRD</t>
+  </si>
+  <si>
+    <t>GVHD prophylaxis</t>
+  </si>
+  <si>
+    <t>CsA, MMF | Cyclo, CsA, MMF; Cyclo, Tacrolimus, MMF | CsA, MTX</t>
+  </si>
+  <si>
+    <t>Sirolimus</t>
+  </si>
+  <si>
+    <t>Cyclosporine</t>
+  </si>
+  <si>
+    <t>GVHD_therapy</t>
+  </si>
+  <si>
+    <t>Budesonide, ECP, Etanercept, MP, Sirolim | CsA, MP, Budesonide | Budesonide, CsA, ECP, MP, MMF | MP, Sirolimus, Basiliximab, Budesonide | MP, Tacrolimus, Etanercept, Ruxolitinib,</t>
+  </si>
+  <si>
+    <t>Infection</t>
+  </si>
+  <si>
+    <t>Bacteremia (E. coli); UTI (E. coli); UTI | UTI (Pseudomonas species and Klebsiella  | UTI (Enterococcus); Pneumonia | Gastroenteritis (CMV) | Pneumonia, viremia, liver failure (Adeno</t>
+  </si>
+  <si>
+    <t>Infection_day_from_hsct</t>
+  </si>
+  <si>
+    <t>68; 78; 89; 134; 176 | 80; 129 | 116; 116 | 76 | 75</t>
+  </si>
+  <si>
+    <t>Infection_day_from_fmt</t>
+  </si>
+  <si>
+    <t>10; 1; 12; 34; 76 | 4; 53 | 6; n/a | 3 | 4</t>
+  </si>
+  <si>
+    <t>death_day</t>
+  </si>
+  <si>
+    <t>177 | 148 | 119 | 173 | 99</t>
+  </si>
+  <si>
+    <t>septicemia | cerebral infarction | GVHD | Adenovirus MOF</t>
+  </si>
+  <si>
+    <t>GVHD_Onset_Day</t>
+  </si>
+  <si>
+    <t>7 | 10 | 19 | 20 | 25</t>
+  </si>
+  <si>
+    <t>GVHD_Onset_Organ</t>
+  </si>
+  <si>
+    <t>skin | upper_gut | liver | liver; lower_gut | lower_gut</t>
+  </si>
+  <si>
+    <t>GVHD_Onset_Grade</t>
+  </si>
+  <si>
+    <t>1 | 2 | 3 | 4</t>
+  </si>
+  <si>
+    <t>gut_gvhd</t>
+  </si>
+  <si>
+    <t>lower_gut_gvhd_day</t>
+  </si>
+  <si>
+    <t>12 | 11 | 22 | 26 | 34</t>
+  </si>
+  <si>
+    <t>4 | 2 | 3</t>
+  </si>
+  <si>
     <t>SRR22325945 | SRR22325944 | SRR22325892 | SRR22325891 | SRR22325890</t>
   </si>
   <si>
@@ -2436,18 +2808,12 @@
     <t>PATIENT_LEVEL. Continuous, no rounding applied in the metadata (values to ~15 decimal places).</t>
   </si>
   <si>
-    <t>gender</t>
-  </si>
-  <si>
     <t>Patient sex. Values: 1 = male; 2 = female. Confirmed from Parsing_metadata.qmd: `sex = ifelse(gender == 1, 'male', 'female')`.</t>
   </si>
   <si>
     <t>PATIENT_LEVEL. Manuscript tables report female counts.</t>
   </si>
   <si>
-    <t>diagnosis</t>
-  </si>
-  <si>
     <t>ALL | Other malignancies | NHL | CLL | MDS</t>
   </si>
   <si>
@@ -2566,9 +2932,6 @@
   </si>
   <si>
     <t>bos</t>
-  </si>
-  <si>
-    <t>yes</t>
   </si>
   <si>
     <t>Binary indicator of bronchiolitis obliterans syndrome (BOS) diagnosis. Values: yes = patient developed BOS (2 patients in this cohort); NA/missing = no BOS. BOS is a form of chronic lung GVHD clinically recognised as lung function decline (FEV₁ drop) after allogeneic HSCT.</t>
@@ -2634,8 +2997,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2652,18 +3015,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2678,33 +3035,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2742,7 +3090,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2776,7 +3124,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2811,10 +3158,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2987,14 +3333,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="21.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3029,8 +3372,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -3058,8 +3401,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
@@ -3087,8 +3430,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4">
@@ -3116,8 +3459,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
       <c r="B5">
@@ -3145,8 +3488,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
@@ -3171,8 +3514,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7">
@@ -3197,8 +3540,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8">
@@ -3226,8 +3569,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
         <v>40</v>
       </c>
       <c r="B9">
@@ -3252,8 +3595,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
       <c r="B10">
@@ -3281,8 +3624,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
         <v>47</v>
       </c>
       <c r="B11">
@@ -3310,8 +3653,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12">
@@ -3339,8 +3682,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>55</v>
       </c>
       <c r="B13">
@@ -3368,8 +3711,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>59</v>
       </c>
       <c r="B14">
@@ -3397,8 +3740,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>64</v>
       </c>
       <c r="B15">
@@ -3426,8 +3769,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>67</v>
       </c>
       <c r="B16">
@@ -3452,8 +3795,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>70</v>
       </c>
       <c r="B17">
@@ -3481,8 +3824,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
         <v>74</v>
       </c>
       <c r="B18">
@@ -3510,8 +3853,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>78</v>
       </c>
       <c r="B19">
@@ -3539,8 +3882,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>82</v>
       </c>
       <c r="B20">
@@ -3568,8 +3911,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>86</v>
       </c>
       <c r="B21">
@@ -3597,8 +3940,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
         <v>90</v>
       </c>
       <c r="B22">
@@ -3626,8 +3969,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
         <v>94</v>
       </c>
       <c r="B23">
@@ -3655,8 +3998,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
         <v>98</v>
       </c>
       <c r="B24">
@@ -3684,8 +4027,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
         <v>101</v>
       </c>
       <c r="B25">
@@ -3713,8 +4056,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
         <v>105</v>
       </c>
       <c r="B26">
@@ -3742,8 +4085,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>109</v>
       </c>
       <c r="B27">
@@ -3777,14 +4120,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3819,8 +4159,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -3848,8 +4188,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>114</v>
       </c>
       <c r="B3">
@@ -3877,8 +4217,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>119</v>
       </c>
       <c r="B4">
@@ -3906,8 +4246,8 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>123</v>
       </c>
       <c r="B5">
@@ -3935,8 +4275,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>126</v>
       </c>
       <c r="B6">
@@ -3964,8 +4304,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>130</v>
       </c>
       <c r="B7">
@@ -3993,8 +4333,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
         <v>133</v>
       </c>
       <c r="B8">
@@ -4022,8 +4362,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
         <v>137</v>
       </c>
       <c r="B9">
@@ -4051,8 +4391,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
         <v>140</v>
       </c>
       <c r="B10">
@@ -4080,8 +4420,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
         <v>144</v>
       </c>
       <c r="B11">
@@ -4109,8 +4449,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
         <v>148</v>
       </c>
       <c r="B12">
@@ -4138,8 +4478,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>152</v>
       </c>
       <c r="B13">
@@ -4167,8 +4507,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>156</v>
       </c>
       <c r="B14">
@@ -4196,8 +4536,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>160</v>
       </c>
       <c r="B15">
@@ -4225,8 +4565,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
@@ -4254,8 +4594,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>165</v>
       </c>
       <c r="B17">
@@ -4283,8 +4623,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
         <v>169</v>
       </c>
       <c r="B18">
@@ -4312,8 +4652,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>173</v>
       </c>
       <c r="B19">
@@ -4341,8 +4681,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>177</v>
       </c>
       <c r="B20">
@@ -4370,8 +4710,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>181</v>
       </c>
       <c r="B21">
@@ -4399,8 +4739,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
         <v>184</v>
       </c>
       <c r="B22">
@@ -4428,8 +4768,8 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
         <v>188</v>
       </c>
       <c r="B23">
@@ -4457,8 +4797,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
         <v>192</v>
       </c>
       <c r="B24">
@@ -4486,8 +4826,8 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
         <v>196</v>
       </c>
       <c r="B25">
@@ -4515,8 +4855,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
       <c r="B26">
@@ -4544,8 +4884,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>201</v>
       </c>
       <c r="B27">
@@ -4573,8 +4913,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
         <v>205</v>
       </c>
       <c r="B28">
@@ -4602,8 +4942,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
         <v>209</v>
       </c>
       <c r="B29">
@@ -4631,8 +4971,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
         <v>213</v>
       </c>
       <c r="B30">
@@ -4660,8 +5000,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
         <v>217</v>
       </c>
       <c r="B31">
@@ -4689,8 +5029,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
         <v>221</v>
       </c>
       <c r="B32">
@@ -4718,8 +5058,8 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
         <v>225</v>
       </c>
       <c r="B33">
@@ -4747,8 +5087,8 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
         <v>229</v>
       </c>
       <c r="B34">
@@ -4776,8 +5116,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
         <v>233</v>
       </c>
       <c r="B35">
@@ -4805,8 +5145,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
         <v>235</v>
       </c>
       <c r="B36">
@@ -4834,8 +5174,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
         <v>239</v>
       </c>
       <c r="B37">
@@ -4863,8 +5203,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
         <v>25</v>
       </c>
       <c r="B38">
@@ -4889,8 +5229,8 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
         <v>245</v>
       </c>
       <c r="B39">
@@ -4918,8 +5258,8 @@
         <v>248</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
         <v>109</v>
       </c>
       <c r="B40">
@@ -4944,8 +5284,8 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
         <v>250</v>
       </c>
       <c r="B41">
@@ -4973,8 +5313,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
         <v>254</v>
       </c>
       <c r="B42">
@@ -4999,8 +5339,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
         <v>35</v>
       </c>
       <c r="B43">
@@ -5028,8 +5368,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
         <v>260</v>
       </c>
       <c r="B44">
@@ -5054,8 +5394,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
         <v>101</v>
       </c>
       <c r="B45">
@@ -5083,8 +5423,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
         <v>266</v>
       </c>
       <c r="B46">
@@ -5109,8 +5449,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
         <v>269</v>
       </c>
       <c r="B47">
@@ -5135,8 +5475,8 @@
         <v>271</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
         <v>272</v>
       </c>
       <c r="B48">
@@ -5164,8 +5504,8 @@
         <v>275</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
         <v>276</v>
       </c>
       <c r="B49">
@@ -5190,8 +5530,8 @@
         <v>278</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
         <v>279</v>
       </c>
       <c r="B50">
@@ -5219,8 +5559,8 @@
         <v>282</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
         <v>90</v>
       </c>
       <c r="B51">
@@ -5248,8 +5588,8 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
         <v>286</v>
       </c>
       <c r="B52">
@@ -5277,8 +5617,8 @@
         <v>289</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
         <v>290</v>
       </c>
       <c r="B53">
@@ -5303,8 +5643,8 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
         <v>293</v>
       </c>
       <c r="B54">
@@ -5329,8 +5669,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
         <v>296</v>
       </c>
       <c r="B55">
@@ -5358,8 +5698,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
         <v>300</v>
       </c>
       <c r="B56">
@@ -5384,8 +5724,8 @@
         <v>302</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
         <v>303</v>
       </c>
       <c r="B57">
@@ -5416,11 +5756,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5455,8 +5795,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -5484,8 +5824,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>233</v>
       </c>
       <c r="B3">
@@ -5513,8 +5853,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4">
@@ -5542,8 +5882,8 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>109</v>
       </c>
       <c r="B5">
@@ -5571,8 +5911,8 @@
         <v>314</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>315</v>
       </c>
       <c r="B6">
@@ -5600,8 +5940,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>319</v>
       </c>
       <c r="B7">
@@ -5629,8 +5969,8 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
         <v>322</v>
       </c>
       <c r="B8">
@@ -5658,8 +5998,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9">
@@ -5684,8 +6024,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
         <v>254</v>
       </c>
       <c r="B10">
@@ -5710,8 +6050,8 @@
         <v>326</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
         <v>43</v>
       </c>
       <c r="B11">
@@ -5736,8 +6076,8 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
         <v>329</v>
       </c>
       <c r="B12">
@@ -5765,8 +6105,8 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>333</v>
       </c>
       <c r="B13">
@@ -5794,8 +6134,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>337</v>
       </c>
       <c r="B14">
@@ -5820,8 +6160,8 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>340</v>
       </c>
       <c r="B15">
@@ -5846,8 +6186,8 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>342</v>
       </c>
       <c r="B16">
@@ -5875,8 +6215,8 @@
         <v>344</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>345</v>
       </c>
       <c r="B17">
@@ -5901,8 +6241,8 @@
         <v>347</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
         <v>348</v>
       </c>
       <c r="B18">
@@ -5930,8 +6270,8 @@
         <v>351</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>352</v>
       </c>
       <c r="B19">
@@ -5959,8 +6299,8 @@
         <v>355</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>356</v>
       </c>
       <c r="B20">
@@ -5988,8 +6328,8 @@
         <v>359</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>360</v>
       </c>
       <c r="B21">
@@ -6017,8 +6357,8 @@
         <v>363</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
         <v>364</v>
       </c>
       <c r="B22">
@@ -6046,8 +6386,8 @@
         <v>367</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
         <v>368</v>
       </c>
       <c r="B23">
@@ -6081,14 +6421,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="25.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6123,8 +6460,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -6152,8 +6489,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
@@ -6181,8 +6518,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>374</v>
       </c>
       <c r="B4">
@@ -6210,8 +6547,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>376</v>
       </c>
       <c r="B5">
@@ -6239,8 +6576,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6">
@@ -6268,8 +6605,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>381</v>
       </c>
       <c r="B7">
@@ -6297,8 +6634,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
         <v>384</v>
       </c>
       <c r="B8">
@@ -6326,8 +6663,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
         <v>386</v>
       </c>
       <c r="B9">
@@ -6355,8 +6692,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
         <v>389</v>
       </c>
       <c r="B10">
@@ -6384,8 +6721,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
         <v>392</v>
       </c>
       <c r="B11">
@@ -6410,8 +6747,8 @@
         <v>394</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
         <v>395</v>
       </c>
       <c r="B12">
@@ -6436,8 +6773,8 @@
         <v>397</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>398</v>
       </c>
       <c r="B13">
@@ -6462,8 +6799,8 @@
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>401</v>
       </c>
       <c r="B14">
@@ -6488,7 +6825,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>404</v>
       </c>
@@ -6517,8 +6854,8 @@
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>408</v>
       </c>
       <c r="B16">
@@ -6546,8 +6883,8 @@
         <v>411</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>412</v>
       </c>
       <c r="B17">
@@ -6575,7 +6912,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>416</v>
       </c>
@@ -6601,7 +6938,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>419</v>
       </c>
@@ -6630,8 +6967,8 @@
         <v>422</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>423</v>
       </c>
       <c r="B20">
@@ -6656,7 +6993,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>426</v>
       </c>
@@ -6685,7 +7022,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>430</v>
       </c>
@@ -6711,8 +7048,8 @@
         <v>432</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
         <v>433</v>
       </c>
       <c r="B23">
@@ -6740,8 +7077,8 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
         <v>436</v>
       </c>
       <c r="B24">
@@ -6769,8 +7106,8 @@
         <v>438</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
         <v>439</v>
       </c>
       <c r="B25">
@@ -6798,8 +7135,8 @@
         <v>438</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
         <v>441</v>
       </c>
       <c r="B26">
@@ -6824,8 +7161,8 @@
         <v>443</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>444</v>
       </c>
       <c r="B27">
@@ -6850,8 +7187,8 @@
         <v>446</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
         <v>447</v>
       </c>
       <c r="B28">
@@ -6876,8 +7213,8 @@
         <v>450</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
         <v>451</v>
       </c>
       <c r="B29">
@@ -6905,7 +7242,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>455</v>
       </c>
@@ -6931,8 +7268,8 @@
         <v>457</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
         <v>458</v>
       </c>
       <c r="B31">
@@ -6957,8 +7294,8 @@
         <v>459</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
         <v>460</v>
       </c>
       <c r="B32">
@@ -6983,8 +7320,8 @@
         <v>462</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
         <v>463</v>
       </c>
       <c r="B33">
@@ -7009,8 +7346,8 @@
         <v>465</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
         <v>466</v>
       </c>
       <c r="B34">
@@ -7038,8 +7375,8 @@
         <v>454</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
         <v>468</v>
       </c>
       <c r="B35">
@@ -7067,8 +7404,8 @@
         <v>471</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
         <v>472</v>
       </c>
       <c r="B36">
@@ -7093,8 +7430,8 @@
         <v>474</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
         <v>475</v>
       </c>
       <c r="B37">
@@ -7122,8 +7459,8 @@
         <v>477</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
         <v>478</v>
       </c>
       <c r="B38">
@@ -7148,8 +7485,8 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
         <v>480</v>
       </c>
       <c r="B39">
@@ -7174,8 +7511,8 @@
         <v>481</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
         <v>482</v>
       </c>
       <c r="B40">
@@ -7203,7 +7540,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
         <v>486</v>
       </c>
@@ -7232,8 +7569,8 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
         <v>490</v>
       </c>
       <c r="B42">
@@ -7261,8 +7598,8 @@
         <v>493</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
         <v>494</v>
       </c>
       <c r="B43">
@@ -7290,8 +7627,8 @@
         <v>496</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
         <v>497</v>
       </c>
       <c r="B44">
@@ -7316,8 +7653,8 @@
         <v>498</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
         <v>499</v>
       </c>
       <c r="B45">
@@ -7342,8 +7679,8 @@
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
         <v>501</v>
       </c>
       <c r="B46">
@@ -7353,7 +7690,7 @@
         <v>67</v>
       </c>
       <c r="D46">
-        <v>69.099999999999994</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E46" t="s">
         <v>26</v>
@@ -7368,8 +7705,8 @@
         <v>503</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
         <v>504</v>
       </c>
       <c r="B47">
@@ -7379,7 +7716,7 @@
         <v>67</v>
       </c>
       <c r="D47">
-        <v>69.099999999999994</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E47" t="s">
         <v>26</v>
@@ -7394,8 +7731,8 @@
         <v>505</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
         <v>506</v>
       </c>
       <c r="B48">
@@ -7420,8 +7757,8 @@
         <v>508</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
         <v>509</v>
       </c>
       <c r="B49">
@@ -7449,8 +7786,8 @@
         <v>511</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
         <v>512</v>
       </c>
       <c r="B50">
@@ -7478,8 +7815,8 @@
         <v>515</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
         <v>516</v>
       </c>
       <c r="B51">
@@ -7504,8 +7841,8 @@
         <v>518</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
         <v>519</v>
       </c>
       <c r="B52">
@@ -7530,8 +7867,8 @@
         <v>520</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
         <v>521</v>
       </c>
       <c r="B53">
@@ -7556,8 +7893,8 @@
         <v>523</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
         <v>524</v>
       </c>
       <c r="B54">
@@ -7582,8 +7919,8 @@
         <v>526</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
         <v>527</v>
       </c>
       <c r="B55">
@@ -7608,8 +7945,8 @@
         <v>529</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
         <v>530</v>
       </c>
       <c r="B56">
@@ -7637,8 +7974,8 @@
         <v>454</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
         <v>532</v>
       </c>
       <c r="B57">
@@ -7663,8 +8000,8 @@
         <v>533</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
         <v>534</v>
       </c>
       <c r="B58">
@@ -7692,8 +8029,8 @@
         <v>537</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
         <v>538</v>
       </c>
       <c r="B59">
@@ -7721,7 +8058,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>541</v>
       </c>
@@ -7747,7 +8084,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
         <v>544</v>
       </c>
@@ -7773,8 +8110,8 @@
         <v>546</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
         <v>547</v>
       </c>
       <c r="B62">
@@ -7802,8 +8139,8 @@
         <v>549</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
         <v>550</v>
       </c>
       <c r="B63">
@@ -7831,8 +8168,8 @@
         <v>553</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
         <v>554</v>
       </c>
       <c r="B64">
@@ -7857,8 +8194,8 @@
         <v>556</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
         <v>557</v>
       </c>
       <c r="B65">
@@ -7883,8 +8220,8 @@
         <v>559</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="2" t="s">
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
         <v>560</v>
       </c>
       <c r="B66">
@@ -7909,8 +8246,8 @@
         <v>561</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="2" t="s">
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
         <v>562</v>
       </c>
       <c r="B67">
@@ -7935,8 +8272,8 @@
         <v>563</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
         <v>564</v>
       </c>
       <c r="B68">
@@ -7967,23 +8304,815 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024A0273-05BE-A34B-973C-4C00A08D1FA9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>39</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B4">
+        <v>52</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>571</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>573</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>574</v>
+      </c>
+      <c r="B7">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>576</v>
+      </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>578</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>580</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>582</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>584</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>586</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>587</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>590</v>
+      </c>
+      <c r="B16">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>32.7</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>592</v>
+      </c>
+      <c r="B17">
+        <v>38</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>594</v>
+      </c>
+      <c r="B18">
+        <v>46</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>596</v>
+      </c>
+      <c r="B19">
+        <v>46</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>598</v>
+      </c>
+      <c r="B20">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>34.6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>600</v>
+      </c>
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>34.6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>602</v>
+      </c>
+      <c r="B22">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <v>34.6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>604</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>606</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>609</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>611</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>613</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>615</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>616</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>618</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>620</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>622</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>624</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>625</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="19.5" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8018,8 +9147,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -8038,17 +9167,17 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>566</v>
+        <v>626</v>
       </c>
       <c r="H2" t="s">
-        <v>567</v>
+        <v>627</v>
       </c>
       <c r="K2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>130</v>
       </c>
       <c r="B3">
@@ -8067,17 +9196,17 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>566</v>
+        <v>626</v>
       </c>
       <c r="H3" t="s">
-        <v>568</v>
+        <v>628</v>
       </c>
       <c r="K3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4">
@@ -8096,17 +9225,17 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>569</v>
+        <v>629</v>
       </c>
       <c r="H4" t="s">
-        <v>570</v>
+        <v>630</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>376</v>
       </c>
       <c r="B5">
@@ -8125,18 +9254,18 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>566</v>
+        <v>626</v>
       </c>
       <c r="H5" t="s">
-        <v>571</v>
+        <v>631</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>572</v>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>632</v>
       </c>
       <c r="B6">
         <v>79</v>
@@ -8154,17 +9283,17 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>573</v>
+        <v>633</v>
       </c>
       <c r="H6" t="s">
-        <v>574</v>
+        <v>634</v>
       </c>
       <c r="K6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>384</v>
       </c>
       <c r="B7">
@@ -8183,18 +9312,18 @@
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>566</v>
+        <v>626</v>
       </c>
       <c r="H7" t="s">
-        <v>575</v>
+        <v>635</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>576</v>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>636</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -8212,17 +9341,17 @@
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>577</v>
+        <v>637</v>
       </c>
       <c r="H8" t="s">
-        <v>578</v>
+        <v>638</v>
       </c>
       <c r="K8" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
         <v>423</v>
       </c>
       <c r="B9">
@@ -8241,15 +9370,15 @@
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="H9" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>582</v>
+        <v>642</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -8267,14 +9396,14 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>583</v>
+        <v>643</v>
       </c>
       <c r="H10" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
         <v>557</v>
       </c>
       <c r="B11">
@@ -8293,15 +9422,15 @@
         <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>585</v>
+        <v>645</v>
       </c>
       <c r="H11" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>587</v>
+        <v>647</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -8319,15 +9448,15 @@
         <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>588</v>
+        <v>648</v>
       </c>
       <c r="H12" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>590</v>
+        <v>650</v>
       </c>
       <c r="B13">
         <v>20</v>
@@ -8345,17 +9474,17 @@
         <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>591</v>
+        <v>651</v>
       </c>
       <c r="H13" t="s">
-        <v>592</v>
+        <v>652</v>
       </c>
       <c r="K13" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>412</v>
       </c>
       <c r="B14">
@@ -8374,18 +9503,18 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>594</v>
+        <v>654</v>
       </c>
       <c r="H14" t="s">
-        <v>595</v>
+        <v>655</v>
       </c>
       <c r="K14" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>597</v>
+        <v>657</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -8403,18 +9532,18 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>598</v>
+        <v>658</v>
       </c>
       <c r="H15" t="s">
-        <v>599</v>
+        <v>659</v>
       </c>
       <c r="K15" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>601</v>
+        <v>661</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -8432,15 +9561,15 @@
         <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>602</v>
+        <v>662</v>
       </c>
       <c r="H16" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>604</v>
+        <v>664</v>
       </c>
       <c r="B17">
         <v>18</v>
@@ -8458,18 +9587,18 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>605</v>
+        <v>665</v>
       </c>
       <c r="H17" t="s">
-        <v>606</v>
+        <v>666</v>
       </c>
       <c r="K17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>608</v>
+        <v>668</v>
       </c>
       <c r="B18">
         <v>33</v>
@@ -8487,18 +9616,18 @@
         <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>609</v>
+        <v>669</v>
       </c>
       <c r="H18" t="s">
-        <v>610</v>
+        <v>670</v>
       </c>
       <c r="K18" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>612</v>
+        <v>671</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>672</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -8516,18 +9645,18 @@
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>613</v>
+        <v>673</v>
       </c>
       <c r="H19" t="s">
-        <v>614</v>
+        <v>674</v>
       </c>
       <c r="K19" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>616</v>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>676</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -8545,18 +9674,18 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>617</v>
+        <v>677</v>
       </c>
       <c r="H20" t="s">
-        <v>618</v>
+        <v>678</v>
       </c>
       <c r="K20" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>620</v>
+        <v>679</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>680</v>
       </c>
       <c r="B21">
         <v>9</v>
@@ -8574,18 +9703,18 @@
         <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>621</v>
+        <v>681</v>
       </c>
       <c r="H21" t="s">
-        <v>622</v>
+        <v>682</v>
       </c>
       <c r="K21" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>624</v>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>684</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -8603,18 +9732,18 @@
         <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>625</v>
+        <v>685</v>
       </c>
       <c r="H22" t="s">
-        <v>626</v>
+        <v>686</v>
       </c>
       <c r="K22" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>628</v>
+        <v>687</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>688</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -8632,18 +9761,18 @@
         <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>602</v>
+        <v>662</v>
       </c>
       <c r="H23" t="s">
-        <v>629</v>
+        <v>689</v>
       </c>
       <c r="K23" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>631</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>691</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -8661,18 +9790,18 @@
         <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>632</v>
+        <v>692</v>
       </c>
       <c r="H24" t="s">
-        <v>633</v>
+        <v>693</v>
       </c>
       <c r="K24" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>635</v>
+        <v>694</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>695</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -8690,18 +9819,18 @@
         <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="H25" t="s">
-        <v>637</v>
+        <v>696</v>
       </c>
       <c r="K25" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>639</v>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>698</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -8719,18 +9848,18 @@
         <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>602</v>
+        <v>662</v>
       </c>
       <c r="H26" t="s">
-        <v>640</v>
+        <v>699</v>
       </c>
       <c r="K26" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>641</v>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>700</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -8751,15 +9880,15 @@
         <v>491</v>
       </c>
       <c r="H27" t="s">
-        <v>642</v>
+        <v>701</v>
       </c>
       <c r="K27" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>643</v>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>702</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -8777,18 +9906,18 @@
         <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="H28" t="s">
-        <v>644</v>
+        <v>703</v>
       </c>
       <c r="K28" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>645</v>
+        <v>697</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>704</v>
       </c>
       <c r="B29">
         <v>29</v>
@@ -8806,18 +9935,18 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>646</v>
+        <v>705</v>
       </c>
       <c r="H29" t="s">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="K29" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>649</v>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>708</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -8838,15 +9967,15 @@
         <v>316</v>
       </c>
       <c r="H30" t="s">
-        <v>650</v>
+        <v>709</v>
       </c>
       <c r="K30" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>652</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>711</v>
       </c>
       <c r="B31">
         <v>8</v>
@@ -8864,18 +9993,18 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="H31" t="s">
-        <v>654</v>
+        <v>713</v>
       </c>
       <c r="K31" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>656</v>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>715</v>
       </c>
       <c r="B32">
         <v>17</v>
@@ -8893,18 +10022,18 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>657</v>
+        <v>716</v>
       </c>
       <c r="H32" t="s">
-        <v>658</v>
+        <v>717</v>
       </c>
       <c r="K32" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>660</v>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>719</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -8922,18 +10051,18 @@
         <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>602</v>
+        <v>662</v>
       </c>
       <c r="H33" t="s">
-        <v>661</v>
+        <v>720</v>
       </c>
       <c r="K33" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>663</v>
+        <v>721</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>722</v>
       </c>
       <c r="B34">
         <v>13</v>
@@ -8951,18 +10080,18 @@
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="H34" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="K34" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>667</v>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>726</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -8980,18 +10109,18 @@
         <v>60</v>
       </c>
       <c r="G35" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="H35" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
       <c r="K35" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>670</v>
+        <v>728</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>729</v>
       </c>
       <c r="B36">
         <v>24</v>
@@ -9009,18 +10138,18 @@
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>671</v>
+        <v>730</v>
       </c>
       <c r="H36" t="s">
-        <v>672</v>
+        <v>731</v>
       </c>
       <c r="K36" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>674</v>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>733</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -9038,18 +10167,18 @@
         <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="H37" t="s">
-        <v>675</v>
+        <v>734</v>
       </c>
       <c r="K37" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>677</v>
+        <v>735</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>736</v>
       </c>
       <c r="B38">
         <v>21</v>
@@ -9067,18 +10196,18 @@
         <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>678</v>
+        <v>737</v>
       </c>
       <c r="H38" t="s">
-        <v>679</v>
+        <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>681</v>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>740</v>
       </c>
       <c r="B39">
         <v>10</v>
@@ -9096,18 +10225,18 @@
         <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>682</v>
+        <v>741</v>
       </c>
       <c r="H39" t="s">
-        <v>683</v>
+        <v>742</v>
       </c>
       <c r="K39" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>685</v>
+        <v>743</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>744</v>
       </c>
       <c r="B40">
         <v>7</v>
@@ -9125,18 +10254,18 @@
         <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>686</v>
+        <v>745</v>
       </c>
       <c r="H40" t="s">
-        <v>687</v>
+        <v>746</v>
       </c>
       <c r="K40" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>689</v>
+        <v>747</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>748</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -9154,18 +10283,18 @@
         <v>32</v>
       </c>
       <c r="G41" t="s">
-        <v>690</v>
+        <v>749</v>
       </c>
       <c r="H41" t="s">
-        <v>691</v>
+        <v>750</v>
       </c>
       <c r="K41" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>693</v>
+        <v>751</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>752</v>
       </c>
       <c r="B42">
         <v>24</v>
@@ -9183,18 +10312,18 @@
         <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>694</v>
+        <v>753</v>
       </c>
       <c r="H42" t="s">
-        <v>695</v>
+        <v>754</v>
       </c>
       <c r="K42" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>697</v>
+        <v>755</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>756</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -9203,7 +10332,7 @@
         <v>60</v>
       </c>
       <c r="D43">
-        <v>75.900000000000006</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -9212,18 +10341,18 @@
         <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>698</v>
+        <v>757</v>
       </c>
       <c r="H43" t="s">
-        <v>699</v>
+        <v>758</v>
       </c>
       <c r="K43" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>701</v>
+        <v>759</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>760</v>
       </c>
       <c r="B44">
         <v>25</v>
@@ -9241,18 +10370,18 @@
         <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>694</v>
+        <v>753</v>
       </c>
       <c r="H44" t="s">
-        <v>702</v>
+        <v>761</v>
       </c>
       <c r="K44" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>704</v>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>763</v>
       </c>
       <c r="B45">
         <v>45</v>
@@ -9270,18 +10399,18 @@
         <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>705</v>
+        <v>764</v>
       </c>
       <c r="H45" t="s">
-        <v>706</v>
+        <v>765</v>
       </c>
       <c r="K45" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>708</v>
+        <v>766</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>767</v>
       </c>
       <c r="B46">
         <v>27</v>
@@ -9299,17 +10428,17 @@
         <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="H46" t="s">
-        <v>710</v>
+        <v>769</v>
       </c>
       <c r="K46" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
         <v>458</v>
       </c>
       <c r="B47">
@@ -9331,10 +10460,10 @@
         <v>316</v>
       </c>
       <c r="H47" t="s">
-        <v>712</v>
+        <v>771</v>
       </c>
       <c r="K47" t="s">
-        <v>713</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -9343,32 +10472,1159 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6D3E53-6B2C-F244-8835-A3CC98F2A4BF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>269</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>776</v>
+      </c>
+      <c r="B4">
+        <v>269</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B5">
+        <v>269</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>74</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>780</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>782</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>785</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>787</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>1.1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>789</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>1.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>790</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>1.1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>792</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>794</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" t="s">
+        <v>791</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5766487-1A47-E645-A00E-FD9084CF2771}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>206</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1.9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>776</v>
+      </c>
+      <c r="B6">
+        <v>206</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>802</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>12.1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>804</v>
+      </c>
+      <c r="B9">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>1.9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>806</v>
+      </c>
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>13.6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>12.6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>12.6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>809</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>12.6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>811</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>26</v>
+      </c>
+      <c r="D14">
+        <v>12.6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>813</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>26</v>
+      </c>
+      <c r="D15">
+        <v>12.6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>815</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>26</v>
+      </c>
+      <c r="D16">
+        <v>12.6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>817</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>12.6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>818</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>26</v>
+      </c>
+      <c r="D18">
+        <v>12.6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>702</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>12.6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>819</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>26</v>
+      </c>
+      <c r="D20">
+        <v>12.6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>821</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>22.8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>823</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>22.8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>825</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>47</v>
+      </c>
+      <c r="D23">
+        <v>22.8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>12.6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>827</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>69</v>
+      </c>
+      <c r="D25">
+        <v>33.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>468</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>69</v>
+      </c>
+      <c r="D26">
+        <v>33.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>830</v>
+      </c>
+      <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <v>12.6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>832</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>12.6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>834</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>12.6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>836</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>12.6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>837</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>26</v>
+      </c>
+      <c r="D31">
+        <v>12.6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="D32">
+        <v>12.6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" t="s">
+        <v>839</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9403,8 +11659,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
@@ -9423,7 +11679,7 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>714</v>
+        <v>840</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -9432,9 +11688,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>715</v>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>841</v>
       </c>
       <c r="B3">
         <v>50</v>
@@ -9452,18 +11708,18 @@
         <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>716</v>
+        <v>842</v>
       </c>
       <c r="H3" t="s">
-        <v>717</v>
+        <v>843</v>
       </c>
       <c r="K3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>719</v>
+        <v>844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>845</v>
       </c>
       <c r="B4">
         <v>118</v>
@@ -9481,18 +11737,18 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>720</v>
+        <v>846</v>
       </c>
       <c r="H4" t="s">
-        <v>721</v>
+        <v>847</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>722</v>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>848</v>
       </c>
       <c r="B5">
         <v>50</v>
@@ -9510,18 +11766,18 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>723</v>
+        <v>849</v>
       </c>
       <c r="H5" t="s">
-        <v>724</v>
+        <v>850</v>
       </c>
       <c r="K5" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>725</v>
+        <v>844</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>851</v>
       </c>
       <c r="B6">
         <v>82</v>
@@ -9536,21 +11792,21 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G6" t="s">
-        <v>727</v>
+        <v>853</v>
       </c>
       <c r="H6" t="s">
-        <v>728</v>
+        <v>854</v>
       </c>
       <c r="K6" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>730</v>
+        <v>855</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>856</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -9571,15 +11827,15 @@
         <v>491</v>
       </c>
       <c r="H7" t="s">
-        <v>731</v>
+        <v>857</v>
       </c>
       <c r="K7" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>733</v>
+        <v>859</v>
       </c>
       <c r="B8">
         <v>46</v>
@@ -9594,21 +11850,21 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G8" t="s">
-        <v>734</v>
+        <v>860</v>
       </c>
       <c r="H8" t="s">
-        <v>735</v>
+        <v>861</v>
       </c>
       <c r="K8" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>737</v>
+        <v>862</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>863</v>
       </c>
       <c r="B9">
         <v>47</v>
@@ -9623,21 +11879,21 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G9" t="s">
-        <v>738</v>
+        <v>864</v>
       </c>
       <c r="H9" t="s">
-        <v>739</v>
+        <v>865</v>
       </c>
       <c r="K9" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>741</v>
+        <v>867</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -9655,18 +11911,18 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>742</v>
+        <v>868</v>
       </c>
       <c r="H10" t="s">
-        <v>743</v>
+        <v>869</v>
       </c>
       <c r="K10" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>745</v>
+        <v>871</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -9684,18 +11940,18 @@
         <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>746</v>
+        <v>872</v>
       </c>
       <c r="H11" t="s">
-        <v>747</v>
+        <v>873</v>
       </c>
       <c r="K11" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>749</v>
+        <v>874</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>875</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -9713,18 +11969,18 @@
         <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>750</v>
+        <v>876</v>
       </c>
       <c r="H12" t="s">
-        <v>751</v>
+        <v>877</v>
       </c>
       <c r="K12" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>753</v>
+        <v>878</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>879</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -9742,18 +11998,18 @@
         <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>754</v>
+        <v>880</v>
       </c>
       <c r="H13" t="s">
-        <v>755</v>
+        <v>881</v>
       </c>
       <c r="K13" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>616</v>
+        <v>882</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>676</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -9771,18 +12027,18 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>757</v>
+        <v>883</v>
       </c>
       <c r="H14" t="s">
-        <v>758</v>
+        <v>884</v>
       </c>
       <c r="K14" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>760</v>
+        <v>885</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>886</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -9800,17 +12056,17 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>761</v>
+        <v>887</v>
       </c>
       <c r="H15" t="s">
-        <v>762</v>
+        <v>888</v>
       </c>
       <c r="K15" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>458</v>
       </c>
       <c r="B16">
@@ -9832,15 +12088,15 @@
         <v>513</v>
       </c>
       <c r="H16" t="s">
-        <v>764</v>
+        <v>890</v>
       </c>
       <c r="K16" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>766</v>
+        <v>891</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>892</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -9858,18 +12114,18 @@
         <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>767</v>
+        <v>893</v>
       </c>
       <c r="H17" t="s">
-        <v>768</v>
+        <v>894</v>
       </c>
       <c r="K17" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>770</v>
+        <v>895</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>896</v>
       </c>
       <c r="B18">
         <v>30</v>
@@ -9884,20 +12140,20 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G18" t="s">
-        <v>771</v>
+        <v>897</v>
       </c>
       <c r="H18" t="s">
-        <v>772</v>
+        <v>898</v>
       </c>
       <c r="K18" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>564</v>
       </c>
       <c r="B19">
@@ -9916,18 +12172,18 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>774</v>
+        <v>900</v>
       </c>
       <c r="H19" t="s">
-        <v>775</v>
+        <v>901</v>
       </c>
       <c r="K19" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>777</v>
+        <v>902</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>903</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -9948,15 +12204,15 @@
         <v>316</v>
       </c>
       <c r="H20" t="s">
-        <v>778</v>
+        <v>904</v>
       </c>
       <c r="K20" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>780</v>
+        <v>905</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>906</v>
       </c>
       <c r="B21">
         <v>18</v>
@@ -9971,21 +12227,21 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G21" t="s">
-        <v>781</v>
+        <v>907</v>
       </c>
       <c r="H21" t="s">
-        <v>782</v>
+        <v>908</v>
       </c>
       <c r="K21" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>784</v>
+        <v>909</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>910</v>
       </c>
       <c r="B22">
         <v>17</v>
@@ -10000,21 +12256,21 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G22" t="s">
-        <v>785</v>
+        <v>911</v>
       </c>
       <c r="H22" t="s">
-        <v>786</v>
+        <v>912</v>
       </c>
       <c r="K22" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>788</v>
+        <v>913</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>914</v>
       </c>
       <c r="B23">
         <v>30</v>
@@ -10023,27 +12279,27 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>34.700000000000003</v>
+        <v>34.7</v>
       </c>
       <c r="E23" t="s">
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G23" t="s">
-        <v>789</v>
+        <v>915</v>
       </c>
       <c r="H23" t="s">
-        <v>790</v>
+        <v>916</v>
       </c>
       <c r="K23" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>792</v>
+        <v>917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>918</v>
       </c>
       <c r="B24">
         <v>49</v>
@@ -10058,21 +12314,21 @@
         <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G24" t="s">
-        <v>793</v>
+        <v>919</v>
       </c>
       <c r="H24" t="s">
-        <v>794</v>
+        <v>920</v>
       </c>
       <c r="K24" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>796</v>
+        <v>921</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>922</v>
       </c>
       <c r="B25">
         <v>18</v>
@@ -10087,20 +12343,20 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G25" t="s">
-        <v>785</v>
+        <v>911</v>
       </c>
       <c r="H25" t="s">
-        <v>797</v>
+        <v>923</v>
       </c>
       <c r="K25" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
         <v>423</v>
       </c>
       <c r="B26">
@@ -10119,18 +12375,18 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>799</v>
+        <v>925</v>
       </c>
       <c r="H26" t="s">
-        <v>800</v>
+        <v>926</v>
       </c>
       <c r="K26" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>802</v>
+        <v>927</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>606</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -10151,15 +12407,15 @@
         <v>405</v>
       </c>
       <c r="H27" t="s">
-        <v>803</v>
+        <v>928</v>
       </c>
       <c r="K27" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>805</v>
+        <v>929</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>809</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -10177,18 +12433,18 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>806</v>
+        <v>930</v>
       </c>
       <c r="H28" t="s">
-        <v>807</v>
+        <v>931</v>
       </c>
       <c r="K28" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>809</v>
+        <v>932</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>933</v>
       </c>
       <c r="B29">
         <v>11</v>
@@ -10206,18 +12462,18 @@
         <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>810</v>
+        <v>934</v>
       </c>
       <c r="H29" t="s">
-        <v>811</v>
+        <v>935</v>
       </c>
       <c r="K29" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>813</v>
+        <v>936</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>937</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -10226,7 +12482,7 @@
         <v>98</v>
       </c>
       <c r="D30">
-        <v>83.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -10235,18 +12491,18 @@
         <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>814</v>
+        <v>938</v>
       </c>
       <c r="H30" t="s">
-        <v>815</v>
+        <v>939</v>
       </c>
       <c r="K30" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>817</v>
+        <v>941</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -10264,18 +12520,18 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>818</v>
+        <v>942</v>
       </c>
       <c r="H31" t="s">
-        <v>819</v>
+        <v>943</v>
       </c>
       <c r="K31" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>821</v>
+        <v>944</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>945</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -10293,18 +12549,18 @@
         <v>32</v>
       </c>
       <c r="G32" t="s">
-        <v>822</v>
+        <v>946</v>
       </c>
       <c r="H32" t="s">
-        <v>823</v>
+        <v>947</v>
       </c>
       <c r="K32" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>825</v>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>949</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -10322,18 +12578,18 @@
         <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>826</v>
+        <v>950</v>
       </c>
       <c r="H33" t="s">
-        <v>827</v>
+        <v>951</v>
       </c>
       <c r="K33" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>829</v>
+        <v>953</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -10351,18 +12607,18 @@
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>830</v>
+        <v>954</v>
       </c>
       <c r="H34" t="s">
-        <v>831</v>
+        <v>955</v>
       </c>
       <c r="K34" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>833</v>
+        <v>956</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>957</v>
       </c>
       <c r="B35">
         <v>37</v>
@@ -10380,18 +12636,18 @@
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>834</v>
+        <v>958</v>
       </c>
       <c r="H35" t="s">
-        <v>835</v>
+        <v>959</v>
       </c>
       <c r="K35" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>837</v>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>961</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -10409,18 +12665,18 @@
         <v>32</v>
       </c>
       <c r="G36" t="s">
-        <v>838</v>
+        <v>962</v>
       </c>
       <c r="H36" t="s">
-        <v>839</v>
+        <v>963</v>
       </c>
       <c r="K36" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>841</v>
+        <v>964</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>965</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -10435,21 +12691,21 @@
         <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G37" t="s">
-        <v>842</v>
+        <v>966</v>
       </c>
       <c r="H37" t="s">
-        <v>843</v>
+        <v>967</v>
       </c>
       <c r="K37" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>845</v>
+        <v>968</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>969</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -10467,18 +12723,18 @@
         <v>60</v>
       </c>
       <c r="G38" t="s">
-        <v>846</v>
+        <v>589</v>
       </c>
       <c r="H38" t="s">
-        <v>847</v>
+        <v>970</v>
       </c>
       <c r="K38" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>849</v>
+        <v>971</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>972</v>
       </c>
       <c r="B39">
         <v>28</v>
@@ -10493,21 +12749,21 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>726</v>
+        <v>852</v>
       </c>
       <c r="G39" t="s">
-        <v>850</v>
+        <v>973</v>
       </c>
       <c r="H39" t="s">
-        <v>851</v>
+        <v>974</v>
       </c>
       <c r="K39" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>853</v>
+        <v>975</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>976</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -10525,18 +12781,18 @@
         <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>854</v>
+        <v>977</v>
       </c>
       <c r="H40" t="s">
-        <v>855</v>
+        <v>978</v>
       </c>
       <c r="K40" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>857</v>
+        <v>980</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -10554,18 +12810,18 @@
         <v>32</v>
       </c>
       <c r="G41" t="s">
-        <v>858</v>
+        <v>981</v>
       </c>
       <c r="H41" t="s">
-        <v>859</v>
+        <v>982</v>
       </c>
       <c r="K41" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>861</v>
+        <v>984</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -10583,18 +12839,18 @@
         <v>32</v>
       </c>
       <c r="G42" t="s">
-        <v>858</v>
+        <v>981</v>
       </c>
       <c r="H42" t="s">
-        <v>862</v>
+        <v>985</v>
       </c>
       <c r="K42" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>863</v>
+        <v>986</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -10612,22 +12868,16 @@
         <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>864</v>
+        <v>987</v>
       </c>
       <c r="H43" t="s">
-        <v>865</v>
+        <v>988</v>
       </c>
       <c r="K43" t="s">
-        <v>866</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{170051ed-867f-4092-a6af-8a42e27b7e09}" enabled="1" method="Standard" siteId="{5217e0e7-539d-4563-b1bf-7c6dcf074f91}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1145">
   <si>
     <t>column_name</t>
   </si>
@@ -2661,27 +2661,63 @@
     <t>M-AF | M-AG | M-AI | M-AJ | M-AK</t>
   </si>
   <si>
+    <t>Patient identifier; format 'M-XX' for Munich (MUC) patients and 'R-XX' for Regensburg (REG) patients; multiple rows per patient (one per sample timepoint). Derived directly from meta_clinical1.xlsx Patient column.</t>
+  </si>
+  <si>
+    <t>patient-level — one value per patient across all timepoint samples</t>
+  </si>
+  <si>
     <t>Center</t>
   </si>
   <si>
     <t>MUC | REG</t>
   </si>
   <si>
+    <t>Study center: MUC = Technical University of Munich (Klinikum rechts der Isar, Munich, Germany), REG = University Medical Center Regensburg (Universität Regensburg, Germany). Source: Center in meta_clinical1.xlsx. Paper enrolled 25 MUC and 53 REG patients.</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: constant in this study but analytically meaningful — may vary across studies at merge; MUC and REG have different prophylactic but identical therapeutic antifungal standards (paper Methods)</t>
+  </si>
+  <si>
+    <t>Binary flag for active GI-GvHD at the time of sample collection; source: GVHD_01 in meta_clinical1.xlsx (= 1 when GVHD_012 &gt; 0). 0 = no active GI-GvHD; 1 = sample collected during an active GI-GvHD episode. Perfectly redundant with GVHD binarized (GVHD &gt; 0): the two columns are cell-for-cell identical.</t>
+  </si>
+  <si>
+    <t>redundant with GVHD collapsed to binary (&gt;0 vs 0); carries identical information; note during harmonization to avoid double-encoding GvHD status</t>
+  </si>
+  <si>
     <t>Day</t>
   </si>
   <si>
     <t>0 | -7 | 14 | 28 | 35</t>
   </si>
   <si>
+    <t>Sample collection day relative to allo-SCT transplantation day (Day 0 = transplant); source: Time.num in meta_clinical1.xlsx. Values: -50 (DONOR — pre-transplant donor stool), -25 (IDX — single index pre-conditioning sample), -7 (COND — conditioning baseline), 0 (transplant day), +7, +14, +21, +28, +35 (all POST samples ≥ Day +35 collapsed to Day 35 in this column).</t>
+  </si>
+  <si>
+    <t>reference point is transplant day 0; negative = pre-transplant; POST timepoints all assigned Day=35 regardless of actual day (see lateTP flag in source); DONOR and IDX are exceptional non-protocol timepoints outside the main weekly series</t>
+  </si>
+  <si>
     <t>0 | COND | 14 | 28 | POST</t>
   </si>
   <si>
+    <t>Categorical sampling timepoint label corresponding to Day: COND = conditioning baseline (Day -7, 65 samples); 0 = transplant day (17 samples); 7/14/21/28 = weeks post-transplant; POST = late timepoint ≥ Day +35 (23 samples, Day value set to 35); DONOR = pre-transplant donor stool (2 samples, Day -50); IDX = pre-conditioning index sample (1 sample, Day -25). Aligns 1:1 with Day except POST aggregates all ≥Day+35.</t>
+  </si>
+  <si>
+    <t>POST covers all samples after Day +35 (lateTP=TRUE in source); DONOR and IDX are exceptional single samples; the source also contains Timepoint2 with expanded labels (e.g. 'Day -7', 'Day +7', '≥ Day +35') — Timepoint is the short-form version used in the QIIME2 table</t>
+  </si>
+  <si>
     <t>Antibiotic_therapy</t>
   </si>
   <si>
     <t>No ABX | ABX</t>
   </si>
   <si>
+    <t>Cumulative broad-spectrum antibiotic (ABX) exposure status at time of sample: 'No ABX' = no antibiotics received before or at this sample; 'ABX' = patient had received broad-spectrum antibiotics at or before this sample. Per paper (Methods, Antibiotics): once a patient was started on antibiotics, the first and all subsequent samples were classified as ABX. 100% of MUC and 94% of REG patients received ABX during the study.</t>
+  </si>
+  <si>
+    <t>cumulative classification — not antibiotic status on sample day alone; once ABX, all later samples are ABX regardless of cessation; covers systemic broad-spectrum antibiotics per center-specific standards (Supp. Table 6, not available in PDF)</t>
+  </si>
+  <si>
     <t>Antifungal_therapy</t>
   </si>
   <si>
@@ -2691,25 +2727,55 @@
     <t>no Antifungals | Antifungals</t>
   </si>
   <si>
+    <t>Antifungal therapy status at time of sample: 'Antifungals' = received antifungal treatment; 'no Antifungals' = no antifungal treatment. MUC and REG used identical therapeutic but different prophylactic antifungal standards (paper p.4); prophylactic regimen is encoded separately in Prophylaxe. 64 of 266 non-missing samples have Antifungals.</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: exact time window (cumulative-from-first-exposure vs at-sample-only) not stated in main paper; relates to therapeutic antifungals only — prophylactic antifungals are in Prophylaxe; 3 NA</t>
+  </si>
+  <si>
     <t>Antiviral_therapy</t>
   </si>
   <si>
     <t>1.5</t>
   </si>
   <si>
+    <t>Antiviral therapy indicator: 0 = no antiviral therapy; 1 = antiviral therapy received. Only 7 of 265 non-missing samples have code 1, suggesting therapeutic (not prophylactic) antiviral use. Source: Antiviral_therapy in meta_clinical1.xlsx.</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: exact time window (at-sample vs cumulative) and whether this captures therapeutic or prophylactic antiviral therapy are not stated in the main paper; encoded as 0/1 integer unlike Antibiotic_therapy (which uses text labels); 4 NA</t>
+  </si>
+  <si>
     <t>Prophylaxe</t>
   </si>
   <si>
     <t>1 | 2 | 0</t>
   </si>
   <si>
+    <t>Anti-infective prophylaxis regimen code; integer 0/1/2 perfectly segregated by center: 0 = rare MUC variant (3 samples); 1 = standard MUC prophylaxis regimen (84 samples); 2 = REG prophylaxis regimen (179 samples). All code 0 and 1 samples are MUC; all code 2 samples are REG. Paper states MUC and REG used different prophylactic antifungal standards (Supp. Table 2). Specific drug/dose definitions not in available PDF.</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: exact regimen definitions (drugs, doses, durations) for codes 0, 1, and 2 not recoverable from available sources; paper references Supp. Table 2 for center-specific prophylaxis; regimen primarily differs in antifungal prophylaxis (REG used ursodeoxycholic acid + antifungal; MUC differed — not fully confirmed); 3 NA (same 3 samples as Antifungal_therapy NA)</t>
+  </si>
+  <si>
     <t>GVHD</t>
   </si>
   <si>
     <t>0 | 2 | 1</t>
   </si>
   <si>
+    <t>GI-GvHD severity at time of sample; source: GVHD_012 in meta_clinical1.xlsx (a corrected version of the original GVHD column — differs in 4 samples of patient M-AY where original GVHD=0 but GVHD_012=2). Observed codes: 0 = no GI-GvHD (197 samples); 1 = GI-GvHD present, mild (36 samples); 2 = GI-GvHD present, severe (36 samples). Binary collapse: GVHD_01 = 1 iff GVHD &gt; 0 (same as Diagnosis column).</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: whether level 2 means grade 2-4 severity (collapsed severe category) or encodes a competing event (e.g. death/censoring before GvHD onset) is not confirmed from available sources — supplementary tables not in PDF; must confirm before collapsing 1 and 2 to binary; see Vallet competing-risk precedent in CLAUDE.md</t>
+  </si>
+  <si>
     <t>NY</t>
+  </si>
+  <si>
+    <t>Patient-level 3-level integer code (0/1/2); source: NY in meta_clinical1.xlsx. Values: 0 (9 samples, rare — 8 patients?), 1 (200 samples, majority of patients), 2 (60 samples). Constant within patient across all timepoints (PATIENT_LEVEL). Meaning not established from available paper text or meta_clinical1.xlsx column headers.</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: code definition not recoverable from available sources (main paper PDF, meta_clinical1.xlsx headers, Parsing_metadata.qmd); likely a patient-level classification (disease risk index, conditioning response, or donor match type) but cannot confirm; Supp. Table 1 or 2 may clarify</t>
   </si>
   <si>
     <t>206</t>
@@ -11060,10 +11126,16 @@
       <c r="G6" t="s">
         <v>878</v>
       </c>
+      <c r="H6" t="s">
+        <v>879</v>
+      </c>
+      <c r="K6" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -11081,7 +11153,13 @@
         <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>880</v>
+        <v>882</v>
+      </c>
+      <c r="H7" t="s">
+        <v>883</v>
+      </c>
+      <c r="K7" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11106,10 +11184,16 @@
       <c r="G8" t="s">
         <v>349</v>
       </c>
+      <c r="H8" t="s">
+        <v>885</v>
+      </c>
+      <c r="K8" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="B9" t="s">
         <v>282</v>
@@ -11127,7 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>882</v>
+        <v>888</v>
+      </c>
+      <c r="H9" t="s">
+        <v>889</v>
+      </c>
+      <c r="K9" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -11150,12 +11240,18 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>883</v>
+        <v>891</v>
+      </c>
+      <c r="H10" t="s">
+        <v>892</v>
+      </c>
+      <c r="K10" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>884</v>
+        <v>894</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -11173,12 +11269,18 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>885</v>
+        <v>895</v>
+      </c>
+      <c r="H11" t="s">
+        <v>896</v>
+      </c>
+      <c r="K11" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -11187,7 +11289,7 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -11196,12 +11298,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>888</v>
+        <v>900</v>
+      </c>
+      <c r="H12" t="s">
+        <v>901</v>
+      </c>
+      <c r="K12" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -11210,7 +11318,7 @@
         <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -11221,10 +11329,16 @@
       <c r="G13" t="s">
         <v>349</v>
       </c>
+      <c r="H13" t="s">
+        <v>905</v>
+      </c>
+      <c r="K13" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
@@ -11233,7 +11347,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -11242,12 +11356,18 @@
         <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>892</v>
+        <v>908</v>
+      </c>
+      <c r="H14" t="s">
+        <v>909</v>
+      </c>
+      <c r="K14" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -11265,12 +11385,18 @@
         <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>894</v>
+        <v>912</v>
+      </c>
+      <c r="H15" t="s">
+        <v>913</v>
+      </c>
+      <c r="K15" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
@@ -11288,7 +11414,13 @@
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>892</v>
+        <v>908</v>
+      </c>
+      <c r="H16" t="s">
+        <v>916</v>
+      </c>
+      <c r="K16" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
@@ -11341,7 +11473,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -11356,7 +11488,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="H2" t="s">
         <v>868</v>
@@ -11367,7 +11499,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -11385,7 +11517,7 @@
         <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>899</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -11399,7 +11531,7 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>900</v>
+        <v>922</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -11408,7 +11540,7 @@
         <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>901</v>
+        <v>923</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -11431,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>902</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11439,7 +11571,7 @@
         <v>873</v>
       </c>
       <c r="B6" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -11454,10 +11586,10 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>903</v>
+        <v>925</v>
       </c>
       <c r="H6" t="s">
-        <v>904</v>
+        <v>926</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -11468,7 +11600,7 @@
         <v>429</v>
       </c>
       <c r="B7" t="s">
-        <v>905</v>
+        <v>927</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -11483,12 +11615,12 @@
         <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>906</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>907</v>
+        <v>929</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -11497,7 +11629,7 @@
         <v>475</v>
       </c>
       <c r="D8" t="s">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
@@ -11506,21 +11638,21 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>909</v>
+        <v>931</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="B9" t="s">
-        <v>911</v>
+        <v>933</v>
       </c>
       <c r="C9" t="s">
         <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>900</v>
+        <v>922</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -11529,21 +11661,21 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>912</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="B10" t="s">
-        <v>914</v>
+        <v>936</v>
       </c>
       <c r="C10" t="s">
         <v>357</v>
       </c>
       <c r="D10" t="s">
-        <v>915</v>
+        <v>937</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -11552,7 +11684,7 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>916</v>
+        <v>938</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -11563,10 +11695,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D11" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -11586,10 +11718,10 @@
         <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D12" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -11598,21 +11730,21 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>919</v>
+        <v>941</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>920</v>
+        <v>942</v>
       </c>
       <c r="B13" t="s">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D13" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -11621,21 +11753,21 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>921</v>
+        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>922</v>
+        <v>944</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D14" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -11644,21 +11776,21 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>923</v>
+        <v>945</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>924</v>
+        <v>946</v>
       </c>
       <c r="B15" t="s">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D15" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -11667,21 +11799,21 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>925</v>
+        <v>947</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>926</v>
+        <v>948</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D16" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -11690,21 +11822,21 @@
         <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>927</v>
+        <v>949</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>928</v>
+        <v>950</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D17" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -11718,16 +11850,16 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>929</v>
+        <v>951</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D18" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -11747,10 +11879,10 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D19" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -11764,16 +11896,16 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>930</v>
+        <v>952</v>
       </c>
       <c r="B20" t="s">
         <v>282</v>
       </c>
       <c r="C20" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D20" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -11782,12 +11914,12 @@
         <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>931</v>
+        <v>953</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>932</v>
+        <v>954</v>
       </c>
       <c r="B21" t="s">
         <v>282</v>
@@ -11796,7 +11928,7 @@
         <v>263</v>
       </c>
       <c r="D21" t="s">
-        <v>933</v>
+        <v>955</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -11805,12 +11937,12 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>934</v>
+        <v>956</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>935</v>
+        <v>957</v>
       </c>
       <c r="B22" t="s">
         <v>282</v>
@@ -11819,7 +11951,7 @@
         <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>933</v>
+        <v>955</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -11828,12 +11960,12 @@
         <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>936</v>
+        <v>958</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>937</v>
+        <v>959</v>
       </c>
       <c r="B23" t="s">
         <v>792</v>
@@ -11842,7 +11974,7 @@
         <v>263</v>
       </c>
       <c r="D23" t="s">
-        <v>933</v>
+        <v>955</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -11851,7 +11983,7 @@
         <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>938</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -11862,10 +11994,10 @@
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D24" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -11879,16 +12011,16 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>939</v>
+        <v>961</v>
       </c>
       <c r="B25" t="s">
         <v>792</v>
       </c>
       <c r="C25" t="s">
-        <v>940</v>
+        <v>962</v>
       </c>
       <c r="D25" t="s">
-        <v>941</v>
+        <v>963</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -11897,7 +12029,7 @@
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>942</v>
+        <v>964</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -11908,10 +12040,10 @@
         <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>940</v>
+        <v>962</v>
       </c>
       <c r="D26" t="s">
-        <v>941</v>
+        <v>963</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -11920,21 +12052,21 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>943</v>
+        <v>965</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>944</v>
+        <v>966</v>
       </c>
       <c r="B27" t="s">
         <v>315</v>
       </c>
       <c r="C27" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D27" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -11943,21 +12075,21 @@
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>945</v>
+        <v>967</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>946</v>
+        <v>968</v>
       </c>
       <c r="B28" t="s">
         <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D28" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -11966,21 +12098,21 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>947</v>
+        <v>969</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D29" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -11989,21 +12121,21 @@
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>949</v>
+        <v>971</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>950</v>
+        <v>972</v>
       </c>
       <c r="B30" t="s">
         <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D30" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E30" t="s">
         <v>132</v>
@@ -12015,24 +12147,24 @@
         <v>131</v>
       </c>
       <c r="H30" t="s">
-        <v>951</v>
+        <v>973</v>
       </c>
       <c r="K30" t="s">
-        <v>952</v>
+        <v>974</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>953</v>
+        <v>975</v>
       </c>
       <c r="B31" t="s">
         <v>315</v>
       </c>
       <c r="C31" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D31" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -12041,7 +12173,7 @@
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>954</v>
+        <v>976</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -12052,10 +12184,10 @@
         <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>917</v>
+        <v>939</v>
       </c>
       <c r="D32" t="s">
-        <v>918</v>
+        <v>940</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -12064,7 +12196,7 @@
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>955</v>
+        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -12117,7 +12249,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>956</v>
+        <v>978</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -12132,7 +12264,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>957</v>
+        <v>979</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -12143,7 +12275,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="B3" t="s">
         <v>840</v>
@@ -12161,21 +12293,21 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>959</v>
+        <v>981</v>
       </c>
       <c r="H3" t="s">
-        <v>960</v>
+        <v>982</v>
       </c>
       <c r="K3" t="s">
-        <v>961</v>
+        <v>983</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>962</v>
+        <v>984</v>
       </c>
       <c r="B4" t="s">
-        <v>956</v>
+        <v>978</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -12190,10 +12322,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>963</v>
+        <v>985</v>
       </c>
       <c r="H4" t="s">
-        <v>964</v>
+        <v>986</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -12201,7 +12333,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>965</v>
+        <v>987</v>
       </c>
       <c r="B5" t="s">
         <v>840</v>
@@ -12219,21 +12351,21 @@
         <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>966</v>
+        <v>988</v>
       </c>
       <c r="H5" t="s">
-        <v>967</v>
+        <v>989</v>
       </c>
       <c r="K5" t="s">
-        <v>961</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>968</v>
+        <v>990</v>
       </c>
       <c r="B6" t="s">
-        <v>969</v>
+        <v>991</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -12245,21 +12377,21 @@
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G6" t="s">
-        <v>971</v>
+        <v>993</v>
       </c>
       <c r="H6" t="s">
-        <v>972</v>
+        <v>994</v>
       </c>
       <c r="K6" t="s">
-        <v>973</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>974</v>
+        <v>996</v>
       </c>
       <c r="B7" t="s">
         <v>131</v>
@@ -12280,15 +12412,15 @@
         <v>542</v>
       </c>
       <c r="H7" t="s">
-        <v>975</v>
+        <v>997</v>
       </c>
       <c r="K7" t="s">
-        <v>976</v>
+        <v>998</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>977</v>
+        <v>999</v>
       </c>
       <c r="B8" t="s">
         <v>340</v>
@@ -12303,21 +12435,21 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G8" t="s">
-        <v>978</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="s">
-        <v>979</v>
+        <v>1001</v>
       </c>
       <c r="K8" t="s">
-        <v>980</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>981</v>
+        <v>1003</v>
       </c>
       <c r="B9" t="s">
         <v>263</v>
@@ -12332,21 +12464,21 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G9" t="s">
-        <v>982</v>
+        <v>1004</v>
       </c>
       <c r="H9" t="s">
-        <v>983</v>
+        <v>1005</v>
       </c>
       <c r="K9" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>985</v>
+        <v>1007</v>
       </c>
       <c r="B10" t="s">
         <v>58</v>
@@ -12364,18 +12496,18 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="H10" t="s">
-        <v>987</v>
+        <v>1009</v>
       </c>
       <c r="K10" t="s">
-        <v>988</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>989</v>
+        <v>1011</v>
       </c>
       <c r="B11" t="s">
         <v>58</v>
@@ -12393,18 +12525,18 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
       <c r="H11" t="s">
-        <v>991</v>
+        <v>1013</v>
       </c>
       <c r="K11" t="s">
-        <v>992</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>993</v>
+        <v>1015</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
@@ -12422,18 +12554,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>994</v>
+        <v>1016</v>
       </c>
       <c r="H12" t="s">
-        <v>995</v>
+        <v>1017</v>
       </c>
       <c r="K12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>997</v>
+        <v>1019</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -12451,13 +12583,13 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>998</v>
+        <v>1020</v>
       </c>
       <c r="H13" t="s">
-        <v>999</v>
+        <v>1021</v>
       </c>
       <c r="K13" t="s">
-        <v>1000</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -12480,18 +12612,18 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>1001</v>
+        <v>1023</v>
       </c>
       <c r="H14" t="s">
-        <v>1002</v>
+        <v>1024</v>
       </c>
       <c r="K14" t="s">
-        <v>1003</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>1004</v>
+        <v>1026</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -12509,13 +12641,13 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>1005</v>
+        <v>1027</v>
       </c>
       <c r="H15" t="s">
-        <v>1006</v>
+        <v>1028</v>
       </c>
       <c r="K15" t="s">
-        <v>1007</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -12541,15 +12673,15 @@
         <v>570</v>
       </c>
       <c r="H16" t="s">
-        <v>1008</v>
+        <v>1030</v>
       </c>
       <c r="K16" t="s">
-        <v>1009</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>1010</v>
+        <v>1032</v>
       </c>
       <c r="B17" t="s">
         <v>58</v>
@@ -12558,7 +12690,7 @@
         <v>852</v>
       </c>
       <c r="D17" t="s">
-        <v>1011</v>
+        <v>1033</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -12567,18 +12699,18 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>1012</v>
+        <v>1034</v>
       </c>
       <c r="H17" t="s">
-        <v>1013</v>
+        <v>1035</v>
       </c>
       <c r="K17" t="s">
-        <v>1014</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>1015</v>
+        <v>1037</v>
       </c>
       <c r="B18" t="s">
         <v>433</v>
@@ -12587,22 +12719,22 @@
         <v>852</v>
       </c>
       <c r="D18" t="s">
-        <v>1011</v>
+        <v>1033</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G18" t="s">
-        <v>1016</v>
+        <v>1038</v>
       </c>
       <c r="H18" t="s">
-        <v>1017</v>
+        <v>1039</v>
       </c>
       <c r="K18" t="s">
-        <v>1018</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -12625,18 +12757,18 @@
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>1019</v>
+        <v>1041</v>
       </c>
       <c r="H19" t="s">
-        <v>1020</v>
+        <v>1042</v>
       </c>
       <c r="K19" t="s">
-        <v>1021</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>1022</v>
+        <v>1044</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -12657,15 +12789,15 @@
         <v>349</v>
       </c>
       <c r="H20" t="s">
-        <v>1023</v>
+        <v>1045</v>
       </c>
       <c r="K20" t="s">
-        <v>1024</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>1025</v>
+        <v>1047</v>
       </c>
       <c r="B21" t="s">
         <v>299</v>
@@ -12674,85 +12806,85 @@
         <v>517</v>
       </c>
       <c r="D21" t="s">
-        <v>1026</v>
+        <v>1048</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G21" t="s">
-        <v>1027</v>
+        <v>1049</v>
       </c>
       <c r="H21" t="s">
-        <v>1028</v>
+        <v>1050</v>
       </c>
       <c r="K21" t="s">
-        <v>1029</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>1030</v>
+        <v>1052</v>
       </c>
       <c r="B22" t="s">
         <v>385</v>
       </c>
       <c r="C22" t="s">
-        <v>914</v>
+        <v>936</v>
       </c>
       <c r="D22" t="s">
-        <v>1031</v>
+        <v>1053</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G22" t="s">
-        <v>1032</v>
+        <v>1054</v>
       </c>
       <c r="H22" t="s">
-        <v>1033</v>
+        <v>1055</v>
       </c>
       <c r="K22" t="s">
-        <v>1034</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>1035</v>
+        <v>1057</v>
       </c>
       <c r="B23" t="s">
         <v>433</v>
       </c>
       <c r="C23" t="s">
-        <v>1036</v>
+        <v>1058</v>
       </c>
       <c r="D23" t="s">
-        <v>1037</v>
+        <v>1059</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G23" t="s">
-        <v>1038</v>
+        <v>1060</v>
       </c>
       <c r="H23" t="s">
-        <v>1039</v>
+        <v>1061</v>
       </c>
       <c r="K23" t="s">
-        <v>1040</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>1041</v>
+        <v>1063</v>
       </c>
       <c r="B24" t="s">
         <v>852</v>
@@ -12767,45 +12899,45 @@
         <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G24" t="s">
-        <v>1042</v>
+        <v>1064</v>
       </c>
       <c r="H24" t="s">
-        <v>1043</v>
+        <v>1065</v>
       </c>
       <c r="K24" t="s">
-        <v>1044</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>1045</v>
+        <v>1067</v>
       </c>
       <c r="B25" t="s">
         <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>1046</v>
+        <v>1068</v>
       </c>
       <c r="D25" t="s">
-        <v>1047</v>
+        <v>1069</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G25" t="s">
-        <v>1032</v>
+        <v>1054</v>
       </c>
       <c r="H25" t="s">
-        <v>1048</v>
+        <v>1070</v>
       </c>
       <c r="K25" t="s">
-        <v>1049</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -12828,13 +12960,13 @@
         <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>1050</v>
+        <v>1072</v>
       </c>
       <c r="H26" t="s">
-        <v>1051</v>
+        <v>1073</v>
       </c>
       <c r="K26" t="s">
-        <v>1052</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -12860,15 +12992,15 @@
         <v>447</v>
       </c>
       <c r="H27" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
       <c r="K27" t="s">
-        <v>1054</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>920</v>
+        <v>942</v>
       </c>
       <c r="B28" t="s">
         <v>792</v>
@@ -12886,18 +13018,18 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>1055</v>
+        <v>1077</v>
       </c>
       <c r="H28" t="s">
-        <v>1056</v>
+        <v>1078</v>
       </c>
       <c r="K28" t="s">
-        <v>1057</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>1058</v>
+        <v>1080</v>
       </c>
       <c r="B29" t="s">
         <v>602</v>
@@ -12915,27 +13047,27 @@
         <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>1059</v>
+        <v>1081</v>
       </c>
       <c r="H29" t="s">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="K29" t="s">
-        <v>1061</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>1062</v>
+        <v>1084</v>
       </c>
       <c r="B30" t="s">
         <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>1063</v>
+        <v>1085</v>
       </c>
       <c r="D30" t="s">
-        <v>1064</v>
+        <v>1086</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -12944,18 +13076,18 @@
         <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
       <c r="H30" t="s">
-        <v>1066</v>
+        <v>1088</v>
       </c>
       <c r="K30" t="s">
-        <v>1067</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>1068</v>
+        <v>1090</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -12973,18 +13105,18 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>1069</v>
+        <v>1091</v>
       </c>
       <c r="H31" t="s">
-        <v>1070</v>
+        <v>1092</v>
       </c>
       <c r="K31" t="s">
-        <v>1071</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>1072</v>
+        <v>1094</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
@@ -12993,7 +13125,7 @@
         <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>1073</v>
+        <v>1095</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -13002,18 +13134,18 @@
         <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>1074</v>
+        <v>1096</v>
       </c>
       <c r="H32" t="s">
-        <v>1075</v>
+        <v>1097</v>
       </c>
       <c r="K32" t="s">
-        <v>1076</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>1077</v>
+        <v>1099</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -13022,7 +13154,7 @@
         <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>1073</v>
+        <v>1095</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -13031,21 +13163,21 @@
         <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>1078</v>
+        <v>1100</v>
       </c>
       <c r="H33" t="s">
-        <v>1079</v>
+        <v>1101</v>
       </c>
       <c r="K33" t="s">
-        <v>1080</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>1081</v>
+        <v>1103</v>
       </c>
       <c r="B34" t="s">
-        <v>1082</v>
+        <v>1104</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -13060,21 +13192,21 @@
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>1083</v>
+        <v>1105</v>
       </c>
       <c r="H34" t="s">
-        <v>1084</v>
+        <v>1106</v>
       </c>
       <c r="K34" t="s">
-        <v>1085</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="B35" t="s">
-        <v>1087</v>
+        <v>1109</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -13089,27 +13221,27 @@
         <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>1088</v>
+        <v>1110</v>
       </c>
       <c r="H35" t="s">
-        <v>1089</v>
+        <v>1111</v>
       </c>
       <c r="K35" t="s">
-        <v>1090</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>1091</v>
+        <v>1113</v>
       </c>
       <c r="B36" t="s">
         <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>1092</v>
+        <v>1114</v>
       </c>
       <c r="D36" t="s">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="E36" t="s">
         <v>132</v>
@@ -13118,56 +13250,56 @@
         <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>1094</v>
+        <v>1116</v>
       </c>
       <c r="H36" t="s">
-        <v>1095</v>
+        <v>1117</v>
       </c>
       <c r="K36" t="s">
-        <v>1096</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>1097</v>
+        <v>1119</v>
       </c>
       <c r="B37" t="s">
         <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>1092</v>
+        <v>1114</v>
       </c>
       <c r="D37" t="s">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="E37" t="s">
         <v>132</v>
       </c>
       <c r="F37" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G37" t="s">
-        <v>1098</v>
+        <v>1120</v>
       </c>
       <c r="H37" t="s">
-        <v>1099</v>
+        <v>1121</v>
       </c>
       <c r="K37" t="s">
-        <v>1100</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>1101</v>
+        <v>1123</v>
       </c>
       <c r="B38" t="s">
         <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>1092</v>
+        <v>1114</v>
       </c>
       <c r="D38" t="s">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="E38" t="s">
         <v>132</v>
@@ -13179,15 +13311,15 @@
         <v>657</v>
       </c>
       <c r="H38" t="s">
-        <v>1102</v>
+        <v>1124</v>
       </c>
       <c r="K38" t="s">
-        <v>1103</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
@@ -13196,27 +13328,27 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>1105</v>
+        <v>1127</v>
       </c>
       <c r="E39" t="s">
         <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="G39" t="s">
-        <v>1106</v>
+        <v>1128</v>
       </c>
       <c r="H39" t="s">
-        <v>1107</v>
+        <v>1129</v>
       </c>
       <c r="K39" t="s">
-        <v>1108</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>1109</v>
+        <v>1131</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -13225,7 +13357,7 @@
         <v>268</v>
       </c>
       <c r="D40" t="s">
-        <v>1105</v>
+        <v>1127</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -13234,18 +13366,18 @@
         <v>36</v>
       </c>
       <c r="G40" t="s">
-        <v>1110</v>
+        <v>1132</v>
       </c>
       <c r="H40" t="s">
-        <v>1111</v>
+        <v>1133</v>
       </c>
       <c r="K40" t="s">
-        <v>1112</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>1113</v>
+        <v>1135</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -13263,18 +13395,18 @@
         <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>1114</v>
+        <v>1136</v>
       </c>
       <c r="H41" t="s">
-        <v>1115</v>
+        <v>1137</v>
       </c>
       <c r="K41" t="s">
-        <v>1116</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>1117</v>
+        <v>1139</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -13292,18 +13424,18 @@
         <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>1114</v>
+        <v>1136</v>
       </c>
       <c r="H42" t="s">
-        <v>1118</v>
+        <v>1140</v>
       </c>
       <c r="K42" t="s">
-        <v>1116</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>1119</v>
+        <v>1141</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -13321,13 +13453,13 @@
         <v>36</v>
       </c>
       <c r="G43" t="s">
-        <v>1120</v>
+        <v>1142</v>
       </c>
       <c r="H43" t="s">
-        <v>1121</v>
+        <v>1143</v>
       </c>
       <c r="K43" t="s">
-        <v>1122</v>
+        <v>1144</v>
       </c>
     </row>
   </sheetData>

--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2997" uniqueCount="1179">
   <si>
     <t>column_name</t>
   </si>
@@ -2790,15 +2790,24 @@
     <t>1 | 2 | 3 | 4 | 5</t>
   </si>
   <si>
+    <t>Integer case number 1-10; alternative patient identifier (maps to Patient A-J via patient_fmts table in Parsing_metadata.qmd); donor stool samples retain original case numbers from source data (40, 50)</t>
+  </si>
+  <si>
     <t>1.9</t>
   </si>
   <si>
     <t>A | B | C | D | E</t>
   </si>
   <si>
+    <t>Anonymized patient letter A-J; NA for two pure donor stool samples (cases 40, 50) that have no associated transplant recipient</t>
+  </si>
+  <si>
     <t>patient | donor</t>
   </si>
   <si>
+    <t>Sample source: 'patient' (stool from transplant recipient) or 'donor' (stool from FMT donor used as treatment)</t>
+  </si>
+  <si>
     <t>K1836-8 | K1836-9 | K1836-20 | K1836-21 | K1836-22</t>
   </si>
   <si>
@@ -2811,6 +2820,9 @@
     <t>aGvHD_pre-treatment | aGvHD_pre-FMT1 | aGvHD_d03-post-FMT1 | aGvHD_pre-FMT2 | aGvHD_d02-post-FMT3</t>
   </si>
   <si>
+    <t>Author-assigned descriptive label encoding sample context (e.g. aGvHD_pre-FMT1, aGvHD_d03-post-FMT1, aGvHD_donor-1); encodes timing relative to FMT cycle</t>
+  </si>
+  <si>
     <t>fmt_cycle</t>
   </si>
   <si>
@@ -2820,6 +2832,9 @@
     <t>FMT1 | FMT2 | FMT3 | FMT4 | FMT5</t>
   </si>
   <si>
+    <t>FMT cycle label (FMT1-FMT6) indicating which FMT administration the sample is relative to; derived from sample_title by str_extract; NA for donors and pre-study baseline samples</t>
+  </si>
+  <si>
     <t>fmt_cycle_day</t>
   </si>
   <si>
@@ -2829,6 +2844,12 @@
     <t>37 | 48 | 58 | 77 | 89</t>
   </si>
   <si>
+    <t>Absolute day of the corresponding FMT administration relative to HSCT (Day 0); derived from hand-entered patient_fmts table in Parsing_metadata.qmd</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: patient_fmts values differ from paper Table 1 for Patient E FMT2 (60 vs 66), Patient H last FMT (518 vs 525), Patient I FMT1 (21 vs 35); source of discrepancy unknown</t>
+  </si>
+  <si>
     <t>Time</t>
   </si>
   <si>
@@ -2841,51 +2862,93 @@
     <t>&lt;37 | 40 | &lt;48 | 60 | &lt;58</t>
   </si>
   <si>
+    <t>Sample collection day relative to HSCT transplant (Day 0); pre-FMT samples encoded as '&lt;day' (upper bound, 86 rows); post-FMT samples are exact integer days; NA for stool donors</t>
+  </si>
+  <si>
     <t>26</t>
   </si>
   <si>
     <t>12.6</t>
   </si>
   <si>
+    <t>Patient biological sex (male/female)</t>
+  </si>
+  <si>
     <t>53 | 60 | 61 | 59 | 24</t>
   </si>
   <si>
+    <t>Patient age at HSCT in years</t>
+  </si>
+  <si>
     <t>diagnosis</t>
   </si>
   <si>
     <t>MDS | Secondary AML/MDS | AML | PMF | Multiple myeloma</t>
   </si>
   <si>
+    <t>Underlying hematologic diagnosis at HSCT (e.g. AML, MDS, MDS/Secondary AML, PMF, Multiple myeloma)</t>
+  </si>
+  <si>
     <t>Donor sex</t>
   </si>
   <si>
     <t>female | male | female; male</t>
   </si>
   <si>
+    <t>Biological sex of the FMT stool donor(s); semicolon-joined for Patient E who received two sequential allogeneic transplants from different donors</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: Patient E has two values joined by '; '; will require parsing at harmonization</t>
+  </si>
+  <si>
     <t>Donor match</t>
   </si>
   <si>
     <t>URD (HLA 9/10, HLA-DQB1 mismatch) | URD | MSD | HID; HID | MRD</t>
   </si>
   <si>
+    <t>HLA match category between the allogeneic HSCT donor and recipient (e.g. MSD, URD, MRD, HID); semicolon-joined for Patient E (two transplants)</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: Patient E has two values joined by '; '</t>
+  </si>
+  <si>
     <t>GVHD prophylaxis</t>
   </si>
   <si>
     <t>CsA, MMF | Cyclo, CsA, MMF; Cyclo, Tacrolimus, MMF | CsA, MTX</t>
   </si>
   <si>
+    <t>GVHD prophylaxis regimen(s) for the allogeneic HSCT; drugs comma-separated within a regimen; semicolon-joined for Patient E who received two sequential transplants with different regimens</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: Patient E has two regimens joined by '; '</t>
+  </si>
+  <si>
     <t>Sirolimus</t>
   </si>
   <si>
+    <t>One-hot indicator (1/0) for sirolimus (mTOR inhibitor) as a component of the GVHD treatment regimen (GVHD_therapy)</t>
+  </si>
+  <si>
     <t>Cyclosporine</t>
   </si>
   <si>
+    <t>One-hot indicator (1/0) for cyclosporine (calcineurin inhibitor) as a component of the GVHD treatment regimen (GVHD_therapy)</t>
+  </si>
+  <si>
+    <t>One-hot indicator (1/0) for tacrolimus (calcineurin inhibitor) as a component of the GVHD treatment regimen (GVHD_therapy)</t>
+  </si>
+  <si>
     <t>GVHD_therapy</t>
   </si>
   <si>
     <t>Budesonide, ECP, Etanercept, MP, Sirolim | CsA, MP, Budesonide | Budesonide, CsA, ECP, MP, MMF | MP, Sirolimus, Basiliximab, Budesonide | MP, Tacrolimus, Etanercept, Ruxolitinib,</t>
   </si>
   <si>
+    <t>Full GVHD treatment regimen; comma-separated drug names (e.g. MP, CsA, Sirolimus, Budesonide, ECP); MP = methylprednisolone; ECP = extracorporeal photopheresis</t>
+  </si>
+  <si>
     <t>Infection</t>
   </si>
   <si>
@@ -2895,18 +2958,36 @@
     <t>Bacteremia (E. coli); UTI (E. coli); UTI | UTI (Pseudomonas species and Klebsiella  | UTI (Enterococcus); Pneumonia | Gastroenteritis (CMV) | Pneumonia, viremia, liver failure (Adeno</t>
   </si>
   <si>
+    <t>Infection event(s) during follow-up; free-text description of type and pathogen; semicolon-separated list for patients with multiple events; NA if none recorded</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: multiple events semicolon-separated; parallel index to Infection_day_from_hsct and Infection_day_from_fmt</t>
+  </si>
+  <si>
     <t>Infection_day_from_hsct</t>
   </si>
   <si>
     <t>68; 78; 89; 134; 176 | 80; 129 | 116; 116 | 76 | 75</t>
   </si>
   <si>
+    <t>Day of each infection event onset relative to HSCT transplant (Day 0); semicolon-separated parallel list to Infection column</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: parallel list to Infection column; semicolon-separated</t>
+  </si>
+  <si>
     <t>Infection_day_from_fmt</t>
   </si>
   <si>
     <t>10; 1; 12; 34; 76 | 4; 53 | 6; n/a | 3 | 4</t>
   </si>
   <si>
+    <t>Day of each infection event onset relative to first FMT administration; semicolon-separated parallel list to Infection column</t>
+  </si>
+  <si>
+    <t>Death indicator (1 = died before end of follow-up, 0 = alive at last follow-up)</t>
+  </si>
+  <si>
     <t>death_day</t>
   </si>
   <si>
@@ -2919,27 +3000,42 @@
     <t>177 | 148 | 119 | 173 | 99</t>
   </si>
   <si>
+    <t>Day of death relative to HSCT transplant (Day 0); NA if patient was alive at last follow-up</t>
+  </si>
+  <si>
     <t>septicemia | cerebral infarction | GVHD | Adenovirus MOF</t>
   </si>
   <si>
+    <t>Recorded cause of death (e.g. GVHD, septicemia, cerebral infarction, Adenovirus MOF); NA if patient was alive at last follow-up</t>
+  </si>
+  <si>
     <t>GVHD_Onset_Day</t>
   </si>
   <si>
     <t>7 | 10 | 19 | 20 | 25</t>
   </si>
   <si>
+    <t>Day of aGVHD onset relative to HSCT transplant (Day 0); NA for stool donors who did not undergo transplant</t>
+  </si>
+  <si>
     <t>GVHD_Onset_Organ</t>
   </si>
   <si>
     <t>skin | upper_gut | liver | liver; lower_gut | lower_gut</t>
   </si>
   <si>
+    <t>Primary organ(s) involved at aGVHD onset; semicolon-separated if multiple organs (skin, upper_gut, lower_gut, liver)</t>
+  </si>
+  <si>
     <t>GVHD_Onset_Grade</t>
   </si>
   <si>
     <t>1 | 2 | 3 | 4</t>
   </si>
   <si>
+    <t>Overall aGVHD severity grade at onset using modified Glucksberg grading (Przepiorka 1994); I-IV; all enrolled patients had grade III-IV at time of first FMT (study inclusion criterion)</t>
+  </si>
+  <si>
     <t>gut_gvhd</t>
   </si>
   <si>
@@ -2955,7 +3051,13 @@
     <t>12 | 11 | 22 | 26 | 34</t>
   </si>
   <si>
+    <t>Day of lower GI (gut) aGVHD onset relative to HSCT transplant (Day 0); NA for patients without lower GI involvement</t>
+  </si>
+  <si>
     <t>4 | 2 | 3</t>
+  </si>
+  <si>
+    <t>GI organ stage at aGVHD onset using Glucksberg GI staging (Przepiorka 1994); 1-4; NA for donors and patients without gut involvement at onset</t>
   </si>
   <si>
     <t>118</t>
@@ -11519,6 +11621,9 @@
       <c r="G3" t="s">
         <v>921</v>
       </c>
+      <c r="H3" t="s">
+        <v>922</v>
+      </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
@@ -11531,7 +11636,7 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -11540,7 +11645,10 @@
         <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>923</v>
+        <v>924</v>
+      </c>
+      <c r="H4" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -11563,7 +11671,10 @@
         <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>924</v>
+        <v>926</v>
+      </c>
+      <c r="H5" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11586,10 +11697,10 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="H6" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -11600,7 +11711,7 @@
         <v>429</v>
       </c>
       <c r="B7" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -11615,12 +11726,15 @@
         <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>928</v>
+        <v>931</v>
+      </c>
+      <c r="H7" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -11629,7 +11743,7 @@
         <v>475</v>
       </c>
       <c r="D8" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
@@ -11638,21 +11752,24 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>931</v>
+        <v>935</v>
+      </c>
+      <c r="H8" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="B9" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="C9" t="s">
         <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -11661,21 +11778,27 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>934</v>
+        <v>939</v>
+      </c>
+      <c r="H9" t="s">
+        <v>940</v>
+      </c>
+      <c r="K9" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="B10" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="C10" t="s">
         <v>357</v>
       </c>
       <c r="D10" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -11684,7 +11807,10 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>938</v>
+        <v>945</v>
+      </c>
+      <c r="H10" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -11695,10 +11821,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D11" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -11708,6 +11834,9 @@
       </c>
       <c r="G11" t="s">
         <v>723</v>
+      </c>
+      <c r="H11" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -11718,10 +11847,10 @@
         <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D12" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -11730,21 +11859,24 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>941</v>
+        <v>950</v>
+      </c>
+      <c r="H12" t="s">
+        <v>951</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="B13" t="s">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D13" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -11753,21 +11885,24 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>943</v>
+        <v>953</v>
+      </c>
+      <c r="H13" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D14" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -11776,21 +11911,27 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>945</v>
+        <v>956</v>
+      </c>
+      <c r="H14" t="s">
+        <v>957</v>
+      </c>
+      <c r="K14" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="B15" t="s">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D15" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -11799,21 +11940,27 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>947</v>
+        <v>960</v>
+      </c>
+      <c r="H15" t="s">
+        <v>961</v>
+      </c>
+      <c r="K15" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>948</v>
+        <v>963</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D16" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -11822,21 +11969,27 @@
         <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>949</v>
+        <v>964</v>
+      </c>
+      <c r="H16" t="s">
+        <v>965</v>
+      </c>
+      <c r="K16" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>950</v>
+        <v>967</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D17" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -11847,19 +12000,22 @@
       <c r="G17" t="s">
         <v>63</v>
       </c>
+      <c r="H17" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>951</v>
+        <v>969</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D18" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -11869,6 +12025,9 @@
       </c>
       <c r="G18" t="s">
         <v>349</v>
+      </c>
+      <c r="H18" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -11879,10 +12038,10 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D19" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -11893,19 +12052,22 @@
       <c r="G19" t="s">
         <v>349</v>
       </c>
+      <c r="H19" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
       <c r="B20" t="s">
         <v>282</v>
       </c>
       <c r="C20" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D20" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -11914,12 +12076,15 @@
         <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>953</v>
+        <v>973</v>
+      </c>
+      <c r="H20" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="B21" t="s">
         <v>282</v>
@@ -11928,7 +12093,7 @@
         <v>263</v>
       </c>
       <c r="D21" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -11937,12 +12102,18 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>956</v>
+        <v>977</v>
+      </c>
+      <c r="H21" t="s">
+        <v>978</v>
+      </c>
+      <c r="K21" t="s">
+        <v>979</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>957</v>
+        <v>980</v>
       </c>
       <c r="B22" t="s">
         <v>282</v>
@@ -11951,7 +12122,7 @@
         <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -11960,12 +12131,18 @@
         <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>958</v>
+        <v>981</v>
+      </c>
+      <c r="H22" t="s">
+        <v>982</v>
+      </c>
+      <c r="K22" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>959</v>
+        <v>984</v>
       </c>
       <c r="B23" t="s">
         <v>792</v>
@@ -11974,7 +12151,7 @@
         <v>263</v>
       </c>
       <c r="D23" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -11983,7 +12160,13 @@
         <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>960</v>
+        <v>985</v>
+      </c>
+      <c r="H23" t="s">
+        <v>986</v>
+      </c>
+      <c r="K23" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -11994,10 +12177,10 @@
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D24" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -12008,19 +12191,22 @@
       <c r="G24" t="s">
         <v>63</v>
       </c>
+      <c r="H24" t="s">
+        <v>987</v>
+      </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="B25" t="s">
         <v>792</v>
       </c>
       <c r="C25" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="D25" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -12029,7 +12215,10 @@
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>964</v>
+        <v>991</v>
+      </c>
+      <c r="H25" t="s">
+        <v>992</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -12040,10 +12229,10 @@
         <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="D26" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -12052,21 +12241,24 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>965</v>
+        <v>993</v>
+      </c>
+      <c r="H26" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>966</v>
+        <v>995</v>
       </c>
       <c r="B27" t="s">
         <v>315</v>
       </c>
       <c r="C27" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D27" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -12075,21 +12267,24 @@
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>967</v>
+        <v>996</v>
+      </c>
+      <c r="H27" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>968</v>
+        <v>998</v>
       </c>
       <c r="B28" t="s">
         <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D28" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -12098,21 +12293,24 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>969</v>
+        <v>999</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>970</v>
+        <v>1001</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D29" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -12121,21 +12319,24 @@
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>971</v>
+        <v>1002</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>972</v>
+        <v>1004</v>
       </c>
       <c r="B30" t="s">
         <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D30" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E30" t="s">
         <v>132</v>
@@ -12147,24 +12348,24 @@
         <v>131</v>
       </c>
       <c r="H30" t="s">
-        <v>973</v>
+        <v>1005</v>
       </c>
       <c r="K30" t="s">
-        <v>974</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>975</v>
+        <v>1007</v>
       </c>
       <c r="B31" t="s">
         <v>315</v>
       </c>
       <c r="C31" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D31" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -12173,7 +12374,10 @@
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>976</v>
+        <v>1008</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1009</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -12184,10 +12388,10 @@
         <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D32" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -12196,7 +12400,10 @@
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>977</v>
+        <v>1010</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1011</v>
       </c>
     </row>
   </sheetData>
@@ -12249,7 +12456,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>978</v>
+        <v>1012</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -12264,7 +12471,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>979</v>
+        <v>1013</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -12275,7 +12482,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="B3" t="s">
         <v>840</v>
@@ -12293,21 +12500,21 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>981</v>
+        <v>1015</v>
       </c>
       <c r="H3" t="s">
-        <v>982</v>
+        <v>1016</v>
       </c>
       <c r="K3" t="s">
-        <v>983</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>984</v>
+        <v>1018</v>
       </c>
       <c r="B4" t="s">
-        <v>978</v>
+        <v>1012</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -12322,10 +12529,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>985</v>
+        <v>1019</v>
       </c>
       <c r="H4" t="s">
-        <v>986</v>
+        <v>1020</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -12333,7 +12540,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>987</v>
+        <v>1021</v>
       </c>
       <c r="B5" t="s">
         <v>840</v>
@@ -12351,21 +12558,21 @@
         <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>988</v>
+        <v>1022</v>
       </c>
       <c r="H5" t="s">
-        <v>989</v>
+        <v>1023</v>
       </c>
       <c r="K5" t="s">
-        <v>983</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>990</v>
+        <v>1024</v>
       </c>
       <c r="B6" t="s">
-        <v>991</v>
+        <v>1025</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -12377,21 +12584,21 @@
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G6" t="s">
-        <v>993</v>
+        <v>1027</v>
       </c>
       <c r="H6" t="s">
-        <v>994</v>
+        <v>1028</v>
       </c>
       <c r="K6" t="s">
-        <v>995</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>996</v>
+        <v>1030</v>
       </c>
       <c r="B7" t="s">
         <v>131</v>
@@ -12412,15 +12619,15 @@
         <v>542</v>
       </c>
       <c r="H7" t="s">
-        <v>997</v>
+        <v>1031</v>
       </c>
       <c r="K7" t="s">
-        <v>998</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>999</v>
+        <v>1033</v>
       </c>
       <c r="B8" t="s">
         <v>340</v>
@@ -12435,21 +12642,21 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G8" t="s">
-        <v>1000</v>
+        <v>1034</v>
       </c>
       <c r="H8" t="s">
-        <v>1001</v>
+        <v>1035</v>
       </c>
       <c r="K8" t="s">
-        <v>1002</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>1003</v>
+        <v>1037</v>
       </c>
       <c r="B9" t="s">
         <v>263</v>
@@ -12464,21 +12671,21 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G9" t="s">
-        <v>1004</v>
+        <v>1038</v>
       </c>
       <c r="H9" t="s">
-        <v>1005</v>
+        <v>1039</v>
       </c>
       <c r="K9" t="s">
-        <v>1006</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>1007</v>
+        <v>1041</v>
       </c>
       <c r="B10" t="s">
         <v>58</v>
@@ -12496,18 +12703,18 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>1008</v>
+        <v>1042</v>
       </c>
       <c r="H10" t="s">
-        <v>1009</v>
+        <v>1043</v>
       </c>
       <c r="K10" t="s">
-        <v>1010</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>1011</v>
+        <v>1045</v>
       </c>
       <c r="B11" t="s">
         <v>58</v>
@@ -12525,18 +12732,18 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>1012</v>
+        <v>1046</v>
       </c>
       <c r="H11" t="s">
-        <v>1013</v>
+        <v>1047</v>
       </c>
       <c r="K11" t="s">
-        <v>1014</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>1015</v>
+        <v>1049</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
@@ -12554,18 +12761,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>1016</v>
+        <v>1050</v>
       </c>
       <c r="H12" t="s">
-        <v>1017</v>
+        <v>1051</v>
       </c>
       <c r="K12" t="s">
-        <v>1018</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>1019</v>
+        <v>1053</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -12583,13 +12790,13 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>1020</v>
+        <v>1054</v>
       </c>
       <c r="H13" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="K13" t="s">
-        <v>1022</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -12612,18 +12819,18 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>1023</v>
+        <v>1057</v>
       </c>
       <c r="H14" t="s">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="K14" t="s">
-        <v>1025</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>1026</v>
+        <v>1060</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -12641,13 +12848,13 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>1027</v>
+        <v>1061</v>
       </c>
       <c r="H15" t="s">
-        <v>1028</v>
+        <v>1062</v>
       </c>
       <c r="K15" t="s">
-        <v>1029</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -12673,15 +12880,15 @@
         <v>570</v>
       </c>
       <c r="H16" t="s">
-        <v>1030</v>
+        <v>1064</v>
       </c>
       <c r="K16" t="s">
-        <v>1031</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>1032</v>
+        <v>1066</v>
       </c>
       <c r="B17" t="s">
         <v>58</v>
@@ -12690,7 +12897,7 @@
         <v>852</v>
       </c>
       <c r="D17" t="s">
-        <v>1033</v>
+        <v>1067</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -12699,18 +12906,18 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>1034</v>
+        <v>1068</v>
       </c>
       <c r="H17" t="s">
-        <v>1035</v>
+        <v>1069</v>
       </c>
       <c r="K17" t="s">
-        <v>1036</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>1037</v>
+        <v>1071</v>
       </c>
       <c r="B18" t="s">
         <v>433</v>
@@ -12719,22 +12926,22 @@
         <v>852</v>
       </c>
       <c r="D18" t="s">
-        <v>1033</v>
+        <v>1067</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G18" t="s">
-        <v>1038</v>
+        <v>1072</v>
       </c>
       <c r="H18" t="s">
-        <v>1039</v>
+        <v>1073</v>
       </c>
       <c r="K18" t="s">
-        <v>1040</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -12757,18 +12964,18 @@
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>1041</v>
+        <v>1075</v>
       </c>
       <c r="H19" t="s">
-        <v>1042</v>
+        <v>1076</v>
       </c>
       <c r="K19" t="s">
-        <v>1043</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>1044</v>
+        <v>1078</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -12789,15 +12996,15 @@
         <v>349</v>
       </c>
       <c r="H20" t="s">
-        <v>1045</v>
+        <v>1079</v>
       </c>
       <c r="K20" t="s">
-        <v>1046</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>1047</v>
+        <v>1081</v>
       </c>
       <c r="B21" t="s">
         <v>299</v>
@@ -12806,85 +13013,85 @@
         <v>517</v>
       </c>
       <c r="D21" t="s">
-        <v>1048</v>
+        <v>1082</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G21" t="s">
-        <v>1049</v>
+        <v>1083</v>
       </c>
       <c r="H21" t="s">
-        <v>1050</v>
+        <v>1084</v>
       </c>
       <c r="K21" t="s">
-        <v>1051</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>1052</v>
+        <v>1086</v>
       </c>
       <c r="B22" t="s">
         <v>385</v>
       </c>
       <c r="C22" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="D22" t="s">
-        <v>1053</v>
+        <v>1087</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G22" t="s">
-        <v>1054</v>
+        <v>1088</v>
       </c>
       <c r="H22" t="s">
-        <v>1055</v>
+        <v>1089</v>
       </c>
       <c r="K22" t="s">
-        <v>1056</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>1057</v>
+        <v>1091</v>
       </c>
       <c r="B23" t="s">
         <v>433</v>
       </c>
       <c r="C23" t="s">
-        <v>1058</v>
+        <v>1092</v>
       </c>
       <c r="D23" t="s">
-        <v>1059</v>
+        <v>1093</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G23" t="s">
-        <v>1060</v>
+        <v>1094</v>
       </c>
       <c r="H23" t="s">
-        <v>1061</v>
+        <v>1095</v>
       </c>
       <c r="K23" t="s">
-        <v>1062</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>1063</v>
+        <v>1097</v>
       </c>
       <c r="B24" t="s">
         <v>852</v>
@@ -12899,45 +13106,45 @@
         <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G24" t="s">
-        <v>1064</v>
+        <v>1098</v>
       </c>
       <c r="H24" t="s">
-        <v>1065</v>
+        <v>1099</v>
       </c>
       <c r="K24" t="s">
-        <v>1066</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>1067</v>
+        <v>1101</v>
       </c>
       <c r="B25" t="s">
         <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>1068</v>
+        <v>1102</v>
       </c>
       <c r="D25" t="s">
-        <v>1069</v>
+        <v>1103</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G25" t="s">
-        <v>1054</v>
+        <v>1088</v>
       </c>
       <c r="H25" t="s">
-        <v>1070</v>
+        <v>1104</v>
       </c>
       <c r="K25" t="s">
-        <v>1071</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -12960,13 +13167,13 @@
         <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>1072</v>
+        <v>1106</v>
       </c>
       <c r="H26" t="s">
-        <v>1073</v>
+        <v>1107</v>
       </c>
       <c r="K26" t="s">
-        <v>1074</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -12992,15 +13199,15 @@
         <v>447</v>
       </c>
       <c r="H27" t="s">
-        <v>1075</v>
+        <v>1109</v>
       </c>
       <c r="K27" t="s">
-        <v>1076</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="B28" t="s">
         <v>792</v>
@@ -13018,18 +13225,18 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>1077</v>
+        <v>1111</v>
       </c>
       <c r="H28" t="s">
-        <v>1078</v>
+        <v>1112</v>
       </c>
       <c r="K28" t="s">
-        <v>1079</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>1080</v>
+        <v>1114</v>
       </c>
       <c r="B29" t="s">
         <v>602</v>
@@ -13047,27 +13254,27 @@
         <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>1081</v>
+        <v>1115</v>
       </c>
       <c r="H29" t="s">
-        <v>1082</v>
+        <v>1116</v>
       </c>
       <c r="K29" t="s">
-        <v>1083</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>1084</v>
+        <v>1118</v>
       </c>
       <c r="B30" t="s">
         <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>1085</v>
+        <v>1119</v>
       </c>
       <c r="D30" t="s">
-        <v>1086</v>
+        <v>1120</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -13076,18 +13283,18 @@
         <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>1087</v>
+        <v>1121</v>
       </c>
       <c r="H30" t="s">
-        <v>1088</v>
+        <v>1122</v>
       </c>
       <c r="K30" t="s">
-        <v>1089</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>1090</v>
+        <v>1124</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -13105,18 +13312,18 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>1091</v>
+        <v>1125</v>
       </c>
       <c r="H31" t="s">
-        <v>1092</v>
+        <v>1126</v>
       </c>
       <c r="K31" t="s">
-        <v>1093</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>1094</v>
+        <v>1128</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
@@ -13125,7 +13332,7 @@
         <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>1095</v>
+        <v>1129</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -13134,18 +13341,18 @@
         <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>1096</v>
+        <v>1130</v>
       </c>
       <c r="H32" t="s">
-        <v>1097</v>
+        <v>1131</v>
       </c>
       <c r="K32" t="s">
-        <v>1098</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>1099</v>
+        <v>1133</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -13154,7 +13361,7 @@
         <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>1095</v>
+        <v>1129</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -13163,21 +13370,21 @@
         <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>1100</v>
+        <v>1134</v>
       </c>
       <c r="H33" t="s">
-        <v>1101</v>
+        <v>1135</v>
       </c>
       <c r="K33" t="s">
-        <v>1102</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>1103</v>
+        <v>1137</v>
       </c>
       <c r="B34" t="s">
-        <v>1104</v>
+        <v>1138</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -13192,21 +13399,21 @@
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>1105</v>
+        <v>1139</v>
       </c>
       <c r="H34" t="s">
-        <v>1106</v>
+        <v>1140</v>
       </c>
       <c r="K34" t="s">
-        <v>1107</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>1108</v>
+        <v>1142</v>
       </c>
       <c r="B35" t="s">
-        <v>1109</v>
+        <v>1143</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -13221,27 +13428,27 @@
         <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>1110</v>
+        <v>1144</v>
       </c>
       <c r="H35" t="s">
-        <v>1111</v>
+        <v>1145</v>
       </c>
       <c r="K35" t="s">
-        <v>1112</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>1113</v>
+        <v>1147</v>
       </c>
       <c r="B36" t="s">
         <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>1114</v>
+        <v>1148</v>
       </c>
       <c r="D36" t="s">
-        <v>1115</v>
+        <v>1149</v>
       </c>
       <c r="E36" t="s">
         <v>132</v>
@@ -13250,56 +13457,56 @@
         <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>1116</v>
+        <v>1150</v>
       </c>
       <c r="H36" t="s">
-        <v>1117</v>
+        <v>1151</v>
       </c>
       <c r="K36" t="s">
-        <v>1118</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>1119</v>
+        <v>1153</v>
       </c>
       <c r="B37" t="s">
         <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>1114</v>
+        <v>1148</v>
       </c>
       <c r="D37" t="s">
-        <v>1115</v>
+        <v>1149</v>
       </c>
       <c r="E37" t="s">
         <v>132</v>
       </c>
       <c r="F37" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G37" t="s">
-        <v>1120</v>
+        <v>1154</v>
       </c>
       <c r="H37" t="s">
-        <v>1121</v>
+        <v>1155</v>
       </c>
       <c r="K37" t="s">
-        <v>1122</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>1123</v>
+        <v>1157</v>
       </c>
       <c r="B38" t="s">
         <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>1114</v>
+        <v>1148</v>
       </c>
       <c r="D38" t="s">
-        <v>1115</v>
+        <v>1149</v>
       </c>
       <c r="E38" t="s">
         <v>132</v>
@@ -13311,15 +13518,15 @@
         <v>657</v>
       </c>
       <c r="H38" t="s">
-        <v>1124</v>
+        <v>1158</v>
       </c>
       <c r="K38" t="s">
-        <v>1125</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>1126</v>
+        <v>1160</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
@@ -13328,27 +13535,27 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>1127</v>
+        <v>1161</v>
       </c>
       <c r="E39" t="s">
         <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="G39" t="s">
-        <v>1128</v>
+        <v>1162</v>
       </c>
       <c r="H39" t="s">
-        <v>1129</v>
+        <v>1163</v>
       </c>
       <c r="K39" t="s">
-        <v>1130</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>1131</v>
+        <v>1165</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -13357,7 +13564,7 @@
         <v>268</v>
       </c>
       <c r="D40" t="s">
-        <v>1127</v>
+        <v>1161</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -13366,18 +13573,18 @@
         <v>36</v>
       </c>
       <c r="G40" t="s">
-        <v>1132</v>
+        <v>1166</v>
       </c>
       <c r="H40" t="s">
-        <v>1133</v>
+        <v>1167</v>
       </c>
       <c r="K40" t="s">
-        <v>1134</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>1135</v>
+        <v>1169</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -13395,18 +13602,18 @@
         <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>1136</v>
+        <v>1170</v>
       </c>
       <c r="H41" t="s">
-        <v>1137</v>
+        <v>1171</v>
       </c>
       <c r="K41" t="s">
-        <v>1138</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>1139</v>
+        <v>1173</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -13424,18 +13631,18 @@
         <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>1136</v>
+        <v>1170</v>
       </c>
       <c r="H42" t="s">
-        <v>1140</v>
+        <v>1174</v>
       </c>
       <c r="K42" t="s">
-        <v>1138</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>1141</v>
+        <v>1175</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -13453,13 +13660,13 @@
         <v>36</v>
       </c>
       <c r="G43" t="s">
-        <v>1142</v>
+        <v>1176</v>
       </c>
       <c r="H43" t="s">
-        <v>1143</v>
+        <v>1177</v>
       </c>
       <c r="K43" t="s">
-        <v>1144</v>
+        <v>1178</v>
       </c>
     </row>
   </sheetData>

--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2997" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="1226">
   <si>
     <t>column_name</t>
   </si>
@@ -1920,12 +1920,21 @@
     <t>Patient 01 | Patient 02 | Patient 03 | Patient 04 | Patient 05</t>
   </si>
   <si>
+    <t>Anonymized patient identifier (e.g. 'Patient 01', 'Patient 55'); 39 distinct patients across 52 biopsies; one patient may have multiple biopsies at different time points or anatomical locations</t>
+  </si>
+  <si>
     <t>Dataset</t>
   </si>
   <si>
     <t>ChipCytometry | scRNAseq | scRNAseq+SP</t>
   </si>
   <si>
+    <t>Single-cell genomics technology applied to this biopsy: ChipCytometry (cyclic immunofluorescence imaging on FFPE tissue sections, 37 biopsies), scRNAseq (single-cell RNA sequencing on fresh single-cell suspension, 10 biopsies), or scRNAseq+SP (scRNA-seq plus surface protein measurement via DNA-barcoded antibodies, 5 biopsies)</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: pairs deterministically with Type (FFPE = ChipCytometry; SCS = scRNAseq or scRNAseq+SP); identifies the omics modality and determines which derived data types exist for each biopsy</t>
+  </si>
+  <si>
     <t>Biopsy</t>
   </si>
   <si>
@@ -1944,9 +1953,21 @@
     <t>1 | 3 | 0 | 2 | 1.5</t>
   </si>
   <si>
+    <t>Histologic aGvHD severity grade of the biopsy tissue assessed by the pathologist using the Lerner grading scale: 0 = no histologic GvHD / normal; 1 = focal epithelial cell apoptosis; 2 = widespread apoptosis; 3 = widespread apoptosis with crypt drop-out; fractional values (1.5, 2.5) appear in 4 biopsies. This column is the natural source for histologic GvHD severity (contrast with clinical GvHD total and clinical GvHD GI for the concurrent clinical grade).</t>
+  </si>
+  <si>
+    <t>NOTE: GvHD (Lerner) is the histologic tissue-level grade; clinical GvHD total and clinical GvHD GI are the concurrent clinical Glucksberg grades. GvHD (binary, column 'GvHD') is not a strict derivation from Lerner &gt; 0: 4 biopsies are discordant (2 with Lerner=0 but GvHD=1, and 2 with Lerner=1 but GvHD=0)</t>
+  </si>
+  <si>
     <t>GvHD</t>
   </si>
   <si>
+    <t>Binary indicator of GvHD at the biopsy (1 = GvHD, 0 = no GvHD); related to but not strictly derived from GvHD (Lerner) &gt; 0; 37 biopsies positive, 15 negative</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: 4 biopsies are discordant with GvHD (Lerner): 2 have Lerner=0 but GvHD=1, and 2 have Lerner=1 but GvHD=0; the exact derivation rule for this column is not documented in the paper or supplement</t>
+  </si>
+  <si>
     <t>d after aHSCT</t>
   </si>
   <si>
@@ -1956,42 +1977,81 @@
     <t>115 | 248 | 76 | 39 | 33</t>
   </si>
   <si>
+    <t>Day of biopsy collection relative to allogeneic HSCT (Day 0 = transplant day); range 14-479 days post-transplant; confirmed as the biopsy day in the paper (STAR Methods, Figure 2I)</t>
+  </si>
+  <si>
     <t>Origin</t>
   </si>
   <si>
     <t>Sigmoid | Colon 60 cm | Colon 30 cm | Colon 20 cm | Sigmoid 30 cm</t>
   </si>
   <si>
+    <t>Anatomical site of the endoscopic biopsy within the GI tract; predominantly sigmoid colon (22/52); colon locations include distance from anus in cm (e.g. 'Colon 30 cm'); Pars descendens = descending duodenum; Duodenum = duodenum; Caecum = cecum</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: minor formatting inconsistencies in colon distance labels ('Colon 40 cm' vs 'Colon 40cm', 'Colon 60 cm' vs 'Colon 60cm') suggest manual entry; distances likely represent colonoscopy withdrawal distance</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
     <t>FFPE | SCS</t>
   </si>
   <si>
+    <t>Biopsy processing method: FFPE (formalin-fixed paraffin-embedded, used for ChipCytometry tissue imaging, 37 biopsies) or SCS (single cell suspension, used for scRNA-seq, 15 biopsies)</t>
+  </si>
+  <si>
+    <t>NOTE: Type is deterministically paired with Dataset: FFPE corresponds to ChipCytometry; SCS corresponds to scRNAseq or scRNAseq+SP</t>
+  </si>
+  <si>
     <t>clinical GvHD total</t>
   </si>
   <si>
     <t>4 | 0 | 2 | 3 | 1</t>
   </si>
   <si>
+    <t>Overall clinical aGvHD severity grade at time of biopsy using the Glucksberg grading system: 0 = no GvHD, 1 = mild, 2 = moderate, 3 = severe, 4 = very severe; concurrent with biopsy collection, not necessarily at disease onset. This is the natural source for overall aGvHD clinical grade; see GvHD (Lerner) for histologic grade and clinical GvHD GI for GI organ stage.</t>
+  </si>
+  <si>
+    <t>NOTE: compare GvHD (Lerner) (histologic tissue grade) and clinical GvHD GI (GI organ stage only); the paper groups grades 0-1 as 'mild' and 2-4 as 'severe' for analysis</t>
+  </si>
+  <si>
     <t>clinical GvHD GI</t>
   </si>
   <si>
     <t>4 | 3 | 0 | 1 | 2</t>
   </si>
   <si>
+    <t>GI organ stage of aGvHD at time of biopsy using the Glucksberg GI staging scale: 0 = no GI involvement, 1-4 = increasing GI severity (diarrhea volume and/or abdominal pain); concurrent with biopsy. This is the natural source for gut aGvHD stage.</t>
+  </si>
+  <si>
+    <t>NOTE: compare clinical GvHD total (overall grade across all organs) and GvHD (Lerner) (histologic grade)</t>
+  </si>
+  <si>
     <t>steroid treatment</t>
   </si>
   <si>
     <t>yes | no</t>
   </si>
   <si>
+    <t>Whether the patient was receiving systemic steroid (corticosteroid) treatment at the time of biopsy: yes (37/52) or no (15/52); steroids are first-line therapy for aGvHD</t>
+  </si>
+  <si>
     <t>steroid refractory</t>
   </si>
   <si>
+    <t>Whether the aGvHD was considered steroid-refractory at the time of biopsy: yes (29/52) or no (23/52); steroid-refractory GvHD = inadequate response to initial corticosteroid therapy</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: 5 biopsies have steroid refractory=yes but steroid treatment=no, suggesting 'steroid refractory' may refer to a history of steroid-refractoriness rather than current steroid status; the paper does not state the definition or time window explicitly</t>
+  </si>
+  <si>
     <t>ABX</t>
   </si>
   <si>
+    <t>Antibiotic exposure status at biopsy: yes = patient received systemic broad-spectrum antibiotics at least 24 h before biopsy; no = patient did not receive broad-spectrum antibiotics at time of biopsy or had discontinued at least 14 days before biopsy (per STAR Methods)</t>
+  </si>
+  <si>
     <t>16S data</t>
   </si>
   <si>
@@ -2013,6 +2073,12 @@
     <t>81.2 | 14.6 | 1.19 | 0.08 | 0.146</t>
   </si>
   <si>
+    <t>Urinary indoxyl sulfate concentration normalized to urinary creatinine (µmol/mmol creatinine), collected at time of biopsy; a bacterial tryptophan catabolite and marker of gut barrier integrity; lower values correlate with antibiotic exposure and reduced microbiome diversity; 17/52 biopsies have no urine measurement</t>
+  </si>
+  <si>
+    <t>NOTE: urinary biomarker (not tissue or serum); cited in the paper as inversely correlated with antibiotic exposure and Treg infiltration (Figure 2H, S2E)</t>
+  </si>
+  <si>
     <t>Richness</t>
   </si>
   <si>
@@ -2022,18 +2088,27 @@
     <t>103 | 90 | 97 | 70 | 40</t>
   </si>
   <si>
+    <t>Species richness (number of observed amplicon sequence variants / OTUs) from 16S rRNA sequencing of the biopsy-matched stool sample; higher values = greater bacterial diversity; computed by the study authors</t>
+  </si>
+  <si>
     <t>Simpson</t>
   </si>
   <si>
     <t>0.8677527 | 0.864635 | 0.9036373 | 0.5434547 | 0.1455527</t>
   </si>
   <si>
+    <t>Simpson diversity index (1-D) from 16S rRNA sequencing of the biopsy-matched stool sample; range 0-1 where higher values = greater diversity and evenness; biopsy-matched stool</t>
+  </si>
+  <si>
     <t>Shannon</t>
   </si>
   <si>
     <t>2.7097513 | 2.8369634 | 2.6678665 | 1.1706946 | 0.3644036</t>
   </si>
   <si>
+    <t>Shannon diversity index (H) from 16S rRNA sequencing of the biopsy-matched stool sample; range 0-log(S) where higher values = greater diversity and evenness; biopsy-matched stool</t>
+  </si>
+  <si>
     <t>Biopsy ST2 [pg/ml]</t>
   </si>
   <si>
@@ -2046,82 +2121,148 @@
     <t>79258 | 85484 | 50197 | 26249 | 6521</t>
   </si>
   <si>
+    <t>Serum concentration of soluble ST2 (suppression of tumorigenicity 2, sST2), a MAGIC GvHD biomarker, measured at the time of biopsy in pg/ml; higher levels indicate greater GvHD severity and epithelial damage; 18/52 biopsies have no measurement</t>
+  </si>
+  <si>
+    <t>NOTE: 'Biopsy' prefix distinguishes measurements at biopsy time from 'Onset' measurements (at disease onset); serum measurement, not tissue</t>
+  </si>
+  <si>
     <t>Biopsy Reg3a [ng/ml]</t>
   </si>
   <si>
     <t>39 | 56 | 29 | 26 | 34</t>
   </si>
   <si>
+    <t>Serum concentration of Reg3a (Regenerating islet-derived protein 3 alpha), a MAGIC GvHD biomarker for GI epithelial damage, measured at time of biopsy in ng/ml; higher levels indicate greater GI GvHD severity; 18/52 biopsies have no measurement</t>
+  </si>
+  <si>
+    <t>NOTE: 'Biopsy' prefix distinguishes from 'Onset' measurements; serum measurement, not tissue</t>
+  </si>
+  <si>
     <t>Biopsy MAP</t>
   </si>
   <si>
     <t>0.2362524 | 0.2691285 | 0.1593457 | 0.0956041 | 0.0346206</t>
   </si>
   <si>
+    <t>MAGIC Algorithm Prediction (MAP) score calculated from serum ST2 and Reg3a at the time of biopsy; composite biomarker predicting GvHD-related outcomes; probability-like score (range ~0-1 in this cohort); higher MAP associated with severe GvHD (Figure S1A); 18/52 biopsies have no measurement</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: the paper does not spell out the MAP acronym; 'MAP' is interpreted as MAGIC Algorithm Prediction based on the MAGIC biomarker literature; the exact formula (from Hartwell et al. 2017 or similar) is not cited in this paper</t>
+  </si>
+  <si>
     <t>age of patient</t>
   </si>
   <si>
     <t>55-60 | 40-44 | 65-70 | 45-50 | 50-54</t>
   </si>
   <si>
+    <t>Patient age in 5-year bands (e.g. '55-60'); classified as SAMPLE_LEVEL because Patient 56 has two different bands across biopsies (50-54 and 55-60), consistent with a birthday crossing a band boundary between biopsy visits</t>
+  </si>
+  <si>
     <t>gender</t>
   </si>
   <si>
     <t>m | f</t>
   </si>
   <si>
+    <t>Patient biological sex: m (male, 34/52 biopsies) or f (female, 18/52 biopsies)</t>
+  </si>
+  <si>
     <t>B-NHL | AML | MPN | MDS | MDS/MPN</t>
   </si>
   <si>
+    <t>Underlying hematologic disease at HSCT: AML (acute myeloid leukemia), ALL (acute lymphoblastic leukemia), B-NHL (B-cell non-Hodgkin lymphoma), T-NHL (T-cell non-Hodgkin lymphoma), Hodgkin (Hodgkin lymphoma), MDS (myelodysplastic syndrome), MPN (myeloproliferative neoplasm), MDS/MPN (MDS/MPN overlap syndrome)</t>
+  </si>
+  <si>
+    <t>NOTE: 1 biopsy (biopsy_41, Patient 37) has 'Hdogkin' (misspelling of Hodgkin); combined Hodgkin count is 3 (2 'Hodgkin' + 1 'Hdogkin')</t>
+  </si>
+  <si>
     <t>Donor type</t>
   </si>
   <si>
     <t>unrelated | haplo | sibling</t>
   </si>
   <si>
+    <t>Relationship of the allogeneic HSCT stem cell donor to the recipient: unrelated (matched unrelated donor, 30/52), sibling (matched related sibling donor, 13/52), haplo (haploidentical donor, 9/52)</t>
+  </si>
+  <si>
     <t>HLA</t>
   </si>
   <si>
     <t>mismatch | ident | haplo</t>
   </si>
   <si>
+    <t>HLA matching status between donor and recipient: ident (HLA-identical / fully matched, 24/52), mismatch (HLA-mismatched, 18/52), haplo (haploidentical, 10/52)</t>
+  </si>
+  <si>
     <t>Donor age</t>
   </si>
   <si>
     <t>25-30 | 55-60 | 45-50 | 15-20 | 20-24</t>
   </si>
   <si>
+    <t>Donor age at HSCT in 5-year bands (e.g. '25-30'); 12 distinct band values observed</t>
+  </si>
+  <si>
+    <t>NOTE: two slightly different band formats appear in the data ('50-55' once, '50-54' once); likely a data entry inconsistency</t>
+  </si>
+  <si>
     <t>Donor gender</t>
   </si>
   <si>
+    <t>Donor biological sex: m (male, 36/52) or f (female, 16/52)</t>
+  </si>
+  <si>
     <t>Conditioning</t>
   </si>
   <si>
     <t>Thio/Treo/Flud | FBM | FTM | Treo/Flud | TBI/VP16</t>
   </si>
   <si>
+    <t>Pre-HSCT conditioning regimen; abbreviations: Thio = Thiotepa; Treo = Treosulfan; Flu/Flud = Fludarabine; Bu = Busulfan; Mel = Melphalan; FBM = Fludarabine + Busulfan + Melphalan; FTM = Fludarabine + Treosulfan + Melphalan; TBI = Total body irradiation (dose in Gy noted where specified); VP16 = Etoposide; CY2 = Cyclophosphamide; FLAMSA = Fludarabine + Amsacrine + Cytarabine (sequential protocol)</t>
+  </si>
+  <si>
+    <t>NOTE: abbreviation key sourced from Table S1 legend in Supplement 1.pdf</t>
+  </si>
+  <si>
     <t>Intensity</t>
   </si>
   <si>
     <t>RIC | Standard</t>
   </si>
   <si>
+    <t>Conditioning intensity: RIC (reduced intensity conditioning, 44/52) or Standard (standard/myeloablative conditioning, 8/52)</t>
+  </si>
+  <si>
     <t>GvHD prophylaxis</t>
   </si>
   <si>
     <t>CyA/MTX | PTCy/Tacro/MMF | CyA/MMF | CyA/Bortezomib</t>
   </si>
   <si>
+    <t>GVHD prophylaxis regimen(s) received after HSCT; abbreviations: CyA = Cyclosporine A; MTX = Methotrexate; PTCy = Post-transplant cyclophosphamide; Tacro = Tacrolimus; MMF = Mycophenolate mofetil; Bortezomib = proteasome inhibitor used in experimental prophylaxis</t>
+  </si>
+  <si>
     <t>Stem cell source</t>
   </si>
   <si>
     <t>PBSC | BM</t>
   </si>
   <si>
+    <t>Source of the allogeneic stem cell graft: PBSC (peripheral blood stem cells, 42/52) or BM (bone marrow, 10/52)</t>
+  </si>
+  <si>
     <t>Bx Timepoint</t>
   </si>
   <si>
     <t>Course | Screening | Sceening | Onset</t>
+  </si>
+  <si>
+    <t>Clinical context of the biopsy relative to aGvHD onset: Screening = no clinical GvHD sign at time of biopsy; Onset = biopsy taken within 7 days of first GvHD symptoms; Course = biopsy taken more than 7 days after onset (per Table S1 legend, Supplement 1.pdf)</t>
+  </si>
+  <si>
+    <t>NOTE: one biopsy has value 'Sceening' (misspelling of 'Screening', biopsy not individually identified in source); intended value is Screening. Counts: Onset=24, Screening=14, Course=13, Sceening=1</t>
   </si>
   <si>
     <t>79</t>
@@ -8932,10 +9073,13 @@
       <c r="G2" t="s">
         <v>631</v>
       </c>
+      <c r="H2" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -8953,15 +9097,21 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>633</v>
+        <v>634</v>
+      </c>
+      <c r="H3" t="s">
+        <v>635</v>
+      </c>
+      <c r="K3" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B4" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -8976,10 +9126,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="H4" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -8987,7 +9137,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B5" t="s">
         <v>91</v>
@@ -9005,12 +9155,18 @@
         <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>639</v>
+        <v>642</v>
+      </c>
+      <c r="H5" t="s">
+        <v>643</v>
+      </c>
+      <c r="K5" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -9030,13 +9186,19 @@
       <c r="G6" t="s">
         <v>63</v>
       </c>
+      <c r="H6" t="s">
+        <v>646</v>
+      </c>
+      <c r="K6" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B7" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -9051,12 +9213,15 @@
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>643</v>
+        <v>650</v>
+      </c>
+      <c r="H7" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B8" t="s">
         <v>510</v>
@@ -9074,12 +9239,18 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>645</v>
+        <v>653</v>
+      </c>
+      <c r="H8" t="s">
+        <v>654</v>
+      </c>
+      <c r="K8" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -9097,12 +9268,18 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>647</v>
+        <v>657</v>
+      </c>
+      <c r="H9" t="s">
+        <v>658</v>
+      </c>
+      <c r="K9" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="B10" t="s">
         <v>100</v>
@@ -9120,12 +9297,18 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>649</v>
+        <v>661</v>
+      </c>
+      <c r="H10" t="s">
+        <v>662</v>
+      </c>
+      <c r="K10" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="B11" t="s">
         <v>100</v>
@@ -9143,12 +9326,18 @@
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>651</v>
+        <v>665</v>
+      </c>
+      <c r="H11" t="s">
+        <v>666</v>
+      </c>
+      <c r="K11" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -9166,12 +9355,15 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>653</v>
+        <v>669</v>
+      </c>
+      <c r="H12" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -9189,12 +9381,18 @@
         <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>653</v>
+        <v>669</v>
+      </c>
+      <c r="H13" t="s">
+        <v>672</v>
+      </c>
+      <c r="K13" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>655</v>
+        <v>674</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -9212,12 +9410,15 @@
         <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>653</v>
+        <v>669</v>
+      </c>
+      <c r="H14" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="B15" t="s">
         <v>131</v>
@@ -9235,18 +9436,18 @@
         <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="H15" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="K15" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="B16" t="s">
         <v>470</v>
@@ -9255,7 +9456,7 @@
         <v>385</v>
       </c>
       <c r="D16" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
@@ -9264,15 +9465,21 @@
         <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>682</v>
+      </c>
+      <c r="H16" t="s">
+        <v>683</v>
+      </c>
+      <c r="K16" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>663</v>
+        <v>685</v>
       </c>
       <c r="B17" t="s">
-        <v>664</v>
+        <v>686</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -9287,12 +9494,15 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>687</v>
+      </c>
+      <c r="H17" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="B18" t="s">
         <v>340</v>
@@ -9310,12 +9520,15 @@
         <v>40</v>
       </c>
       <c r="G18" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>690</v>
+      </c>
+      <c r="H18" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="B19" t="s">
         <v>340</v>
@@ -9333,21 +9546,24 @@
         <v>40</v>
       </c>
       <c r="G19" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>693</v>
+      </c>
+      <c r="H19" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="B20" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="C20" t="s">
         <v>299</v>
       </c>
       <c r="D20" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E20" t="s">
         <v>35</v>
@@ -9356,12 +9572,18 @@
         <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>698</v>
+      </c>
+      <c r="H20" t="s">
+        <v>699</v>
+      </c>
+      <c r="K20" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="B21" t="s">
         <v>475</v>
@@ -9370,7 +9592,7 @@
         <v>299</v>
       </c>
       <c r="D21" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E21" t="s">
         <v>35</v>
@@ -9379,21 +9601,27 @@
         <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>702</v>
+      </c>
+      <c r="H21" t="s">
+        <v>703</v>
+      </c>
+      <c r="K21" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>676</v>
+        <v>705</v>
       </c>
       <c r="B22" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="C22" t="s">
         <v>299</v>
       </c>
       <c r="D22" t="s">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
@@ -9402,12 +9630,18 @@
         <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>706</v>
+      </c>
+      <c r="H22" t="s">
+        <v>707</v>
+      </c>
+      <c r="K22" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="B23" t="s">
         <v>282</v>
@@ -9425,12 +9659,15 @@
         <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>710</v>
+      </c>
+      <c r="H23" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -9448,10 +9685,13 @@
         <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>713</v>
+      </c>
+      <c r="H24" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
         <v>281</v>
       </c>
@@ -9471,12 +9711,18 @@
         <v>36</v>
       </c>
       <c r="G25" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>715</v>
+      </c>
+      <c r="H25" t="s">
+        <v>716</v>
+      </c>
+      <c r="K25" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>683</v>
+        <v>718</v>
       </c>
       <c r="B26" t="s">
         <v>58</v>
@@ -9494,12 +9740,15 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>719</v>
+      </c>
+      <c r="H26" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="B27" t="s">
         <v>58</v>
@@ -9517,12 +9766,15 @@
         <v>36</v>
       </c>
       <c r="G27" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>722</v>
+      </c>
+      <c r="H27" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>687</v>
+        <v>724</v>
       </c>
       <c r="B28" t="s">
         <v>48</v>
@@ -9540,12 +9792,18 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>725</v>
+      </c>
+      <c r="H28" t="s">
+        <v>726</v>
+      </c>
+      <c r="K28" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>689</v>
+        <v>728</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -9563,12 +9821,15 @@
         <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>713</v>
+      </c>
+      <c r="H29" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="B30" t="s">
         <v>315</v>
@@ -9586,12 +9847,18 @@
         <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>731</v>
+      </c>
+      <c r="H30" t="s">
+        <v>732</v>
+      </c>
+      <c r="K30" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>692</v>
+        <v>734</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -9609,12 +9876,15 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>735</v>
+      </c>
+      <c r="H31" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>694</v>
+        <v>737</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
@@ -9632,12 +9902,15 @@
         <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>738</v>
+      </c>
+      <c r="H32" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>696</v>
+        <v>740</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -9655,12 +9928,15 @@
         <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>741</v>
+      </c>
+      <c r="H33" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>698</v>
+        <v>743</v>
       </c>
       <c r="B34" t="s">
         <v>53</v>
@@ -9678,7 +9954,13 @@
         <v>36</v>
       </c>
       <c r="G34" t="s">
-        <v>699</v>
+        <v>744</v>
+      </c>
+      <c r="H34" t="s">
+        <v>745</v>
+      </c>
+      <c r="K34" t="s">
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -9731,7 +10013,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -9746,10 +10028,10 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>701</v>
+        <v>748</v>
       </c>
       <c r="H2" t="s">
-        <v>702</v>
+        <v>749</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -9760,7 +10042,7 @@
         <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -9775,10 +10057,10 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>701</v>
+        <v>748</v>
       </c>
       <c r="H3" t="s">
-        <v>703</v>
+        <v>750</v>
       </c>
       <c r="K3" t="s">
         <v>18</v>
@@ -9789,7 +10071,7 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -9804,10 +10086,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>704</v>
+        <v>751</v>
       </c>
       <c r="H4" t="s">
-        <v>705</v>
+        <v>752</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -9818,7 +10100,7 @@
         <v>416</v>
       </c>
       <c r="B5" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -9833,10 +10115,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>701</v>
+        <v>748</v>
       </c>
       <c r="H5" t="s">
-        <v>706</v>
+        <v>753</v>
       </c>
       <c r="K5" t="s">
         <v>18</v>
@@ -9844,10 +10126,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>707</v>
+        <v>754</v>
       </c>
       <c r="B6" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -9862,10 +10144,10 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>708</v>
+        <v>755</v>
       </c>
       <c r="H6" t="s">
-        <v>709</v>
+        <v>756</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -9876,7 +10158,7 @@
         <v>424</v>
       </c>
       <c r="B7" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -9891,10 +10173,10 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>701</v>
+        <v>748</v>
       </c>
       <c r="H7" t="s">
-        <v>710</v>
+        <v>757</v>
       </c>
       <c r="K7" t="s">
         <v>18</v>
@@ -9902,7 +10184,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>711</v>
+        <v>758</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
@@ -9920,13 +10202,13 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>712</v>
+        <v>759</v>
       </c>
       <c r="H8" t="s">
-        <v>713</v>
+        <v>760</v>
       </c>
       <c r="K8" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -9934,13 +10216,13 @@
         <v>466</v>
       </c>
       <c r="B9" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="C9" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D9" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -9949,24 +10231,24 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="H9" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="B10" t="s">
         <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D10" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -9975,10 +10257,10 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H10" t="s">
-        <v>722</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -10001,15 +10283,15 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>723</v>
+        <v>770</v>
       </c>
       <c r="H11" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>725</v>
+        <v>772</v>
       </c>
       <c r="B12" t="s">
         <v>84</v>
@@ -10027,24 +10309,24 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>726</v>
+        <v>773</v>
       </c>
       <c r="H12" t="s">
-        <v>727</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>728</v>
+        <v>775</v>
       </c>
       <c r="B13" t="s">
         <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D13" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -10053,13 +10335,13 @@
         <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>729</v>
+        <v>776</v>
       </c>
       <c r="H13" t="s">
-        <v>730</v>
+        <v>777</v>
       </c>
       <c r="K13" t="s">
-        <v>731</v>
+        <v>778</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -10070,10 +10352,10 @@
         <v>282</v>
       </c>
       <c r="C14" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D14" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -10082,27 +10364,27 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>732</v>
+        <v>779</v>
       </c>
       <c r="H14" t="s">
-        <v>733</v>
+        <v>780</v>
       </c>
       <c r="K14" t="s">
-        <v>734</v>
+        <v>781</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>735</v>
+        <v>782</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D15" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -10111,27 +10393,27 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>736</v>
+        <v>783</v>
       </c>
       <c r="H15" t="s">
-        <v>737</v>
+        <v>784</v>
       </c>
       <c r="K15" t="s">
-        <v>738</v>
+        <v>785</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>739</v>
+        <v>786</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D16" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -10140,15 +10422,15 @@
         <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="H16" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>742</v>
+        <v>789</v>
       </c>
       <c r="B17" t="s">
         <v>299</v>
@@ -10157,7 +10439,7 @@
         <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>743</v>
+        <v>790</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -10166,27 +10448,27 @@
         <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>744</v>
+        <v>791</v>
       </c>
       <c r="H17" t="s">
-        <v>745</v>
+        <v>792</v>
       </c>
       <c r="K17" t="s">
-        <v>746</v>
+        <v>793</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>747</v>
+        <v>794</v>
       </c>
       <c r="B18" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="C18" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D18" t="s">
-        <v>748</v>
+        <v>795</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -10195,27 +10477,27 @@
         <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>749</v>
+        <v>796</v>
       </c>
       <c r="H18" t="s">
-        <v>750</v>
+        <v>797</v>
       </c>
       <c r="K18" t="s">
-        <v>751</v>
+        <v>798</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D19" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -10224,27 +10506,27 @@
         <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>753</v>
+        <v>800</v>
       </c>
       <c r="H19" t="s">
-        <v>754</v>
+        <v>801</v>
       </c>
       <c r="K19" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>756</v>
+        <v>803</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D20" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -10253,27 +10535,27 @@
         <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>757</v>
+        <v>804</v>
       </c>
       <c r="H20" t="s">
-        <v>758</v>
+        <v>805</v>
       </c>
       <c r="K20" t="s">
-        <v>759</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>760</v>
+        <v>807</v>
       </c>
       <c r="B21" t="s">
         <v>282</v>
       </c>
       <c r="C21" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D21" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -10282,27 +10564,27 @@
         <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="H21" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="K21" t="s">
-        <v>763</v>
+        <v>810</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>764</v>
+        <v>811</v>
       </c>
       <c r="B22" t="s">
         <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D22" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -10311,27 +10593,27 @@
         <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>765</v>
+        <v>812</v>
       </c>
       <c r="H22" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="K22" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>768</v>
+        <v>815</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D23" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -10340,27 +10622,27 @@
         <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="H23" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
       <c r="K23" t="s">
-        <v>770</v>
+        <v>817</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>771</v>
+        <v>818</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D24" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -10369,27 +10651,27 @@
         <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>772</v>
+        <v>819</v>
       </c>
       <c r="H24" t="s">
-        <v>773</v>
+        <v>820</v>
       </c>
       <c r="K24" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D25" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -10398,27 +10680,27 @@
         <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="H25" t="s">
-        <v>776</v>
+        <v>823</v>
       </c>
       <c r="K25" t="s">
-        <v>777</v>
+        <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D26" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -10427,27 +10709,27 @@
         <v>67</v>
       </c>
       <c r="G26" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="H26" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="K26" t="s">
-        <v>777</v>
+        <v>824</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>780</v>
+        <v>827</v>
       </c>
       <c r="B27" t="s">
         <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D27" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E27" t="s">
         <v>132</v>
@@ -10459,7 +10741,7 @@
         <v>542</v>
       </c>
       <c r="H27" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="K27" t="s">
         <v>544</v>
@@ -10467,16 +10749,16 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D28" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -10485,27 +10767,27 @@
         <v>67</v>
       </c>
       <c r="G28" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="H28" t="s">
-        <v>783</v>
+        <v>830</v>
       </c>
       <c r="K28" t="s">
-        <v>777</v>
+        <v>824</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>784</v>
+        <v>831</v>
       </c>
       <c r="B29" t="s">
         <v>459</v>
       </c>
       <c r="C29" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D29" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -10514,27 +10796,27 @@
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="H29" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="K29" t="s">
-        <v>787</v>
+        <v>834</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D30" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -10546,24 +10828,24 @@
         <v>349</v>
       </c>
       <c r="H30" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="K30" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="B31" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="C31" t="s">
-        <v>793</v>
+        <v>840</v>
       </c>
       <c r="D31" t="s">
-        <v>794</v>
+        <v>841</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -10572,27 +10854,27 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="H31" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="K31" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>798</v>
+        <v>845</v>
       </c>
       <c r="B32" t="s">
         <v>385</v>
       </c>
       <c r="C32" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="D32" t="s">
-        <v>800</v>
+        <v>847</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -10601,27 +10883,27 @@
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="H32" t="s">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="K32" t="s">
-        <v>803</v>
+        <v>850</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>804</v>
+        <v>851</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D33" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -10630,18 +10912,18 @@
         <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="H33" t="s">
-        <v>805</v>
+        <v>852</v>
       </c>
       <c r="K33" t="s">
-        <v>806</v>
+        <v>853</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>807</v>
+        <v>854</v>
       </c>
       <c r="B34" t="s">
         <v>79</v>
@@ -10650,7 +10932,7 @@
         <v>583</v>
       </c>
       <c r="D34" t="s">
-        <v>808</v>
+        <v>855</v>
       </c>
       <c r="E34" t="s">
         <v>29</v>
@@ -10659,27 +10941,27 @@
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>809</v>
+        <v>856</v>
       </c>
       <c r="H34" t="s">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="K34" t="s">
-        <v>811</v>
+        <v>858</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>812</v>
+        <v>859</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D35" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E35" t="s">
         <v>29</v>
@@ -10688,18 +10970,18 @@
         <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="H35" t="s">
-        <v>813</v>
+        <v>860</v>
       </c>
       <c r="K35" t="s">
-        <v>814</v>
+        <v>861</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>815</v>
+        <v>862</v>
       </c>
       <c r="B36" t="s">
         <v>470</v>
@@ -10708,7 +10990,7 @@
         <v>470</v>
       </c>
       <c r="D36" t="s">
-        <v>816</v>
+        <v>863</v>
       </c>
       <c r="E36" t="s">
         <v>29</v>
@@ -10717,27 +10999,27 @@
         <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="H36" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="K36" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>820</v>
+        <v>867</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D37" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E37" t="s">
         <v>29</v>
@@ -10746,18 +11028,18 @@
         <v>67</v>
       </c>
       <c r="G37" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="H37" t="s">
-        <v>821</v>
+        <v>868</v>
       </c>
       <c r="K37" t="s">
-        <v>822</v>
+        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>823</v>
+        <v>870</v>
       </c>
       <c r="B38" t="s">
         <v>137</v>
@@ -10766,7 +11048,7 @@
         <v>470</v>
       </c>
       <c r="D38" t="s">
-        <v>816</v>
+        <v>863</v>
       </c>
       <c r="E38" t="s">
         <v>29</v>
@@ -10775,27 +11057,27 @@
         <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>824</v>
+        <v>871</v>
       </c>
       <c r="H38" t="s">
-        <v>825</v>
+        <v>872</v>
       </c>
       <c r="K38" t="s">
-        <v>826</v>
+        <v>873</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>827</v>
+        <v>874</v>
       </c>
       <c r="B39" t="s">
         <v>315</v>
       </c>
       <c r="C39" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D39" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E39" t="s">
         <v>29</v>
@@ -10804,27 +11086,27 @@
         <v>36</v>
       </c>
       <c r="G39" t="s">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="H39" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="K39" t="s">
-        <v>830</v>
+        <v>877</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>831</v>
+        <v>878</v>
       </c>
       <c r="B40" t="s">
         <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D40" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -10833,27 +11115,27 @@
         <v>36</v>
       </c>
       <c r="G40" t="s">
-        <v>832</v>
+        <v>879</v>
       </c>
       <c r="H40" t="s">
-        <v>833</v>
+        <v>880</v>
       </c>
       <c r="K40" t="s">
-        <v>834</v>
+        <v>881</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D41" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E41" t="s">
         <v>29</v>
@@ -10862,27 +11144,27 @@
         <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>836</v>
+        <v>883</v>
       </c>
       <c r="H41" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="K41" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>839</v>
+        <v>886</v>
       </c>
       <c r="B42" t="s">
         <v>470</v>
       </c>
       <c r="C42" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="D42" t="s">
-        <v>841</v>
+        <v>888</v>
       </c>
       <c r="E42" t="s">
         <v>29</v>
@@ -10891,27 +11173,27 @@
         <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="H42" t="s">
-        <v>843</v>
+        <v>890</v>
       </c>
       <c r="K42" t="s">
-        <v>844</v>
+        <v>891</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>845</v>
+        <v>892</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>846</v>
+        <v>893</v>
       </c>
       <c r="D43" t="s">
-        <v>847</v>
+        <v>894</v>
       </c>
       <c r="E43" t="s">
         <v>29</v>
@@ -10920,27 +11202,27 @@
         <v>36</v>
       </c>
       <c r="G43" t="s">
-        <v>848</v>
+        <v>895</v>
       </c>
       <c r="H43" t="s">
-        <v>849</v>
+        <v>896</v>
       </c>
       <c r="K43" t="s">
-        <v>850</v>
+        <v>897</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>851</v>
+        <v>898</v>
       </c>
       <c r="B44" t="s">
         <v>475</v>
       </c>
       <c r="C44" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D44" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="E44" t="s">
         <v>29</v>
@@ -10949,27 +11231,27 @@
         <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="H44" t="s">
-        <v>853</v>
+        <v>900</v>
       </c>
       <c r="K44" t="s">
-        <v>854</v>
+        <v>901</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>855</v>
+        <v>902</v>
       </c>
       <c r="B45" t="s">
         <v>316</v>
       </c>
       <c r="C45" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="D45" t="s">
-        <v>856</v>
+        <v>903</v>
       </c>
       <c r="E45" t="s">
         <v>29</v>
@@ -10978,27 +11260,27 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>857</v>
+        <v>904</v>
       </c>
       <c r="H45" t="s">
-        <v>858</v>
+        <v>905</v>
       </c>
       <c r="K45" t="s">
-        <v>859</v>
+        <v>906</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>860</v>
+        <v>907</v>
       </c>
       <c r="B46" t="s">
-        <v>671</v>
+        <v>696</v>
       </c>
       <c r="C46" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="D46" t="s">
-        <v>841</v>
+        <v>888</v>
       </c>
       <c r="E46" t="s">
         <v>29</v>
@@ -11007,13 +11289,13 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>861</v>
+        <v>908</v>
       </c>
       <c r="H46" t="s">
-        <v>862</v>
+        <v>909</v>
       </c>
       <c r="K46" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -11024,10 +11306,10 @@
         <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="D47" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="E47" t="s">
         <v>29</v>
@@ -11039,10 +11321,10 @@
         <v>349</v>
       </c>
       <c r="H47" t="s">
-        <v>864</v>
+        <v>911</v>
       </c>
       <c r="K47" t="s">
-        <v>865</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -11095,7 +11377,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -11110,10 +11392,10 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="H2" t="s">
-        <v>868</v>
+        <v>915</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -11121,7 +11403,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>869</v>
+        <v>916</v>
       </c>
       <c r="B3" t="s">
         <v>131</v>
@@ -11139,21 +11421,21 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="H3" t="s">
-        <v>871</v>
+        <v>918</v>
       </c>
       <c r="K3" t="s">
-        <v>872</v>
+        <v>919</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>873</v>
+        <v>920</v>
       </c>
       <c r="B4" t="s">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -11168,10 +11450,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>874</v>
+        <v>921</v>
       </c>
       <c r="H4" t="s">
-        <v>875</v>
+        <v>922</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -11182,7 +11464,7 @@
         <v>429</v>
       </c>
       <c r="B5" t="s">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -11197,10 +11479,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>876</v>
+        <v>923</v>
       </c>
       <c r="H5" t="s">
-        <v>877</v>
+        <v>924</v>
       </c>
       <c r="K5" t="s">
         <v>18</v>
@@ -11226,18 +11508,18 @@
         <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>878</v>
+        <v>925</v>
       </c>
       <c r="H6" t="s">
-        <v>879</v>
+        <v>926</v>
       </c>
       <c r="K6" t="s">
-        <v>880</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>881</v>
+        <v>928</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
@@ -11255,13 +11537,13 @@
         <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>882</v>
+        <v>929</v>
       </c>
       <c r="H7" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
       <c r="K7" t="s">
-        <v>884</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -11287,15 +11569,15 @@
         <v>349</v>
       </c>
       <c r="H8" t="s">
-        <v>885</v>
+        <v>932</v>
       </c>
       <c r="K8" t="s">
-        <v>886</v>
+        <v>933</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>887</v>
+        <v>934</v>
       </c>
       <c r="B9" t="s">
         <v>282</v>
@@ -11313,13 +11595,13 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>888</v>
+        <v>935</v>
       </c>
       <c r="H9" t="s">
-        <v>889</v>
+        <v>936</v>
       </c>
       <c r="K9" t="s">
-        <v>890</v>
+        <v>937</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -11342,18 +11624,18 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>891</v>
+        <v>938</v>
       </c>
       <c r="H10" t="s">
-        <v>892</v>
+        <v>939</v>
       </c>
       <c r="K10" t="s">
-        <v>893</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>894</v>
+        <v>941</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -11371,18 +11653,18 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>895</v>
+        <v>942</v>
       </c>
       <c r="H11" t="s">
-        <v>896</v>
+        <v>943</v>
       </c>
       <c r="K11" t="s">
-        <v>897</v>
+        <v>944</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>898</v>
+        <v>945</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -11391,7 +11673,7 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>899</v>
+        <v>946</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -11400,18 +11682,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>900</v>
+        <v>947</v>
       </c>
       <c r="H12" t="s">
-        <v>901</v>
+        <v>948</v>
       </c>
       <c r="K12" t="s">
-        <v>902</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>903</v>
+        <v>950</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -11420,7 +11702,7 @@
         <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>904</v>
+        <v>951</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -11432,15 +11714,15 @@
         <v>349</v>
       </c>
       <c r="H13" t="s">
-        <v>905</v>
+        <v>952</v>
       </c>
       <c r="K13" t="s">
-        <v>906</v>
+        <v>953</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>907</v>
+        <v>954</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
@@ -11449,7 +11731,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>899</v>
+        <v>946</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -11458,18 +11740,18 @@
         <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>908</v>
+        <v>955</v>
       </c>
       <c r="H14" t="s">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="K14" t="s">
-        <v>910</v>
+        <v>957</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -11487,18 +11769,18 @@
         <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>912</v>
+        <v>959</v>
       </c>
       <c r="H15" t="s">
-        <v>913</v>
+        <v>960</v>
       </c>
       <c r="K15" t="s">
-        <v>914</v>
+        <v>961</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>915</v>
+        <v>962</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
@@ -11516,13 +11798,13 @@
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>908</v>
+        <v>955</v>
       </c>
       <c r="H16" t="s">
-        <v>916</v>
+        <v>963</v>
       </c>
       <c r="K16" t="s">
-        <v>917</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -11575,7 +11857,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>918</v>
+        <v>965</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -11590,10 +11872,10 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>919</v>
+        <v>966</v>
       </c>
       <c r="H2" t="s">
-        <v>868</v>
+        <v>915</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -11601,7 +11883,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>920</v>
+        <v>967</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -11619,10 +11901,10 @@
         <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>921</v>
+        <v>968</v>
       </c>
       <c r="H3" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -11636,7 +11918,7 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>923</v>
+        <v>970</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -11645,10 +11927,10 @@
         <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>924</v>
+        <v>971</v>
       </c>
       <c r="H4" t="s">
-        <v>925</v>
+        <v>972</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -11671,18 +11953,18 @@
         <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>926</v>
+        <v>973</v>
       </c>
       <c r="H5" t="s">
-        <v>927</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>873</v>
+        <v>920</v>
       </c>
       <c r="B6" t="s">
-        <v>918</v>
+        <v>965</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -11697,10 +11979,10 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>928</v>
+        <v>975</v>
       </c>
       <c r="H6" t="s">
-        <v>929</v>
+        <v>976</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
@@ -11711,7 +11993,7 @@
         <v>429</v>
       </c>
       <c r="B7" t="s">
-        <v>930</v>
+        <v>977</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -11726,15 +12008,15 @@
         <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>931</v>
+        <v>978</v>
       </c>
       <c r="H7" t="s">
-        <v>932</v>
+        <v>979</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>933</v>
+        <v>980</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -11743,7 +12025,7 @@
         <v>475</v>
       </c>
       <c r="D8" t="s">
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
@@ -11752,24 +12034,24 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>935</v>
+        <v>982</v>
       </c>
       <c r="H8" t="s">
-        <v>936</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>937</v>
+        <v>984</v>
       </c>
       <c r="B9" t="s">
-        <v>938</v>
+        <v>985</v>
       </c>
       <c r="C9" t="s">
         <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>923</v>
+        <v>970</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -11778,27 +12060,27 @@
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>939</v>
+        <v>986</v>
       </c>
       <c r="H9" t="s">
-        <v>940</v>
+        <v>987</v>
       </c>
       <c r="K9" t="s">
-        <v>941</v>
+        <v>988</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>942</v>
+        <v>989</v>
       </c>
       <c r="B10" t="s">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="C10" t="s">
         <v>357</v>
       </c>
       <c r="D10" t="s">
-        <v>944</v>
+        <v>991</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -11807,10 +12089,10 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>945</v>
+        <v>992</v>
       </c>
       <c r="H10" t="s">
-        <v>946</v>
+        <v>993</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -11821,10 +12103,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D11" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -11833,10 +12115,10 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>723</v>
+        <v>770</v>
       </c>
       <c r="H11" t="s">
-        <v>949</v>
+        <v>996</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -11847,10 +12129,10 @@
         <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D12" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -11859,24 +12141,24 @@
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>950</v>
+        <v>997</v>
       </c>
       <c r="H12" t="s">
-        <v>951</v>
+        <v>998</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>952</v>
+        <v>999</v>
       </c>
       <c r="B13" t="s">
         <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D13" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -11885,24 +12167,24 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>953</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="s">
-        <v>954</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>955</v>
+        <v>1002</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D14" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
@@ -11911,27 +12193,27 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>956</v>
+        <v>1003</v>
       </c>
       <c r="H14" t="s">
-        <v>957</v>
+        <v>1004</v>
       </c>
       <c r="K14" t="s">
-        <v>958</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>959</v>
+        <v>1006</v>
       </c>
       <c r="B15" t="s">
         <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D15" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -11940,27 +12222,27 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>960</v>
+        <v>1007</v>
       </c>
       <c r="H15" t="s">
-        <v>961</v>
+        <v>1008</v>
       </c>
       <c r="K15" t="s">
-        <v>962</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>963</v>
+        <v>1010</v>
       </c>
       <c r="B16" t="s">
         <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D16" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -11969,27 +12251,27 @@
         <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>964</v>
+        <v>1011</v>
       </c>
       <c r="H16" t="s">
-        <v>965</v>
+        <v>1012</v>
       </c>
       <c r="K16" t="s">
-        <v>966</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>967</v>
+        <v>1014</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D17" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -12001,21 +12283,21 @@
         <v>63</v>
       </c>
       <c r="H17" t="s">
-        <v>968</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>969</v>
+        <v>1016</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D18" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -12027,21 +12309,21 @@
         <v>349</v>
       </c>
       <c r="H18" t="s">
-        <v>970</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D19" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -12053,21 +12335,21 @@
         <v>349</v>
       </c>
       <c r="H19" t="s">
-        <v>971</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>972</v>
+        <v>1019</v>
       </c>
       <c r="B20" t="s">
         <v>282</v>
       </c>
       <c r="C20" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D20" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -12076,15 +12358,15 @@
         <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>973</v>
+        <v>1020</v>
       </c>
       <c r="H20" t="s">
-        <v>974</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="B21" t="s">
         <v>282</v>
@@ -12093,7 +12375,7 @@
         <v>263</v>
       </c>
       <c r="D21" t="s">
-        <v>976</v>
+        <v>1023</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -12102,18 +12384,18 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="H21" t="s">
-        <v>978</v>
+        <v>1025</v>
       </c>
       <c r="K21" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>980</v>
+        <v>1027</v>
       </c>
       <c r="B22" t="s">
         <v>282</v>
@@ -12122,7 +12404,7 @@
         <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>976</v>
+        <v>1023</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
@@ -12131,27 +12413,27 @@
         <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>981</v>
+        <v>1028</v>
       </c>
       <c r="H22" t="s">
-        <v>982</v>
+        <v>1029</v>
       </c>
       <c r="K22" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>984</v>
+        <v>1031</v>
       </c>
       <c r="B23" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="C23" t="s">
         <v>263</v>
       </c>
       <c r="D23" t="s">
-        <v>976</v>
+        <v>1023</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -12160,13 +12442,13 @@
         <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>985</v>
+        <v>1032</v>
       </c>
       <c r="H23" t="s">
-        <v>986</v>
+        <v>1033</v>
       </c>
       <c r="K23" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -12177,10 +12459,10 @@
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D24" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
@@ -12192,21 +12474,21 @@
         <v>63</v>
       </c>
       <c r="H24" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>988</v>
+        <v>1035</v>
       </c>
       <c r="B25" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="C25" t="s">
-        <v>989</v>
+        <v>1036</v>
       </c>
       <c r="D25" t="s">
-        <v>990</v>
+        <v>1037</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
@@ -12215,10 +12497,10 @@
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="H25" t="s">
-        <v>992</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -12229,10 +12511,10 @@
         <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>989</v>
+        <v>1036</v>
       </c>
       <c r="D26" t="s">
-        <v>990</v>
+        <v>1037</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -12241,24 +12523,24 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>993</v>
+        <v>1040</v>
       </c>
       <c r="H26" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>995</v>
+        <v>1042</v>
       </c>
       <c r="B27" t="s">
         <v>315</v>
       </c>
       <c r="C27" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D27" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -12267,24 +12549,24 @@
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>996</v>
+        <v>1043</v>
       </c>
       <c r="H27" t="s">
-        <v>997</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>998</v>
+        <v>1045</v>
       </c>
       <c r="B28" t="s">
         <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D28" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
@@ -12293,24 +12575,24 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>999</v>
+        <v>1046</v>
       </c>
       <c r="H28" t="s">
-        <v>1000</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>1001</v>
+        <v>1048</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D29" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -12319,24 +12601,24 @@
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>1002</v>
+        <v>1049</v>
       </c>
       <c r="H29" t="s">
-        <v>1003</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>1004</v>
+        <v>1051</v>
       </c>
       <c r="B30" t="s">
         <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D30" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E30" t="s">
         <v>132</v>
@@ -12348,24 +12630,24 @@
         <v>131</v>
       </c>
       <c r="H30" t="s">
-        <v>1005</v>
+        <v>1052</v>
       </c>
       <c r="K30" t="s">
-        <v>1006</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>1007</v>
+        <v>1054</v>
       </c>
       <c r="B31" t="s">
         <v>315</v>
       </c>
       <c r="C31" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D31" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E31" t="s">
         <v>29</v>
@@ -12374,10 +12656,10 @@
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>1008</v>
+        <v>1055</v>
       </c>
       <c r="H31" t="s">
-        <v>1009</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -12388,10 +12670,10 @@
         <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="D32" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -12400,10 +12682,10 @@
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>1010</v>
+        <v>1057</v>
       </c>
       <c r="H32" t="s">
-        <v>1011</v>
+        <v>1058</v>
       </c>
     </row>
   </sheetData>
@@ -12456,7 +12738,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>1012</v>
+        <v>1059</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -12471,7 +12753,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>1013</v>
+        <v>1060</v>
       </c>
       <c r="H2" t="s">
         <v>17</v>
@@ -12482,10 +12764,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>1014</v>
+        <v>1061</v>
       </c>
       <c r="B3" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -12500,21 +12782,21 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>1015</v>
+        <v>1062</v>
       </c>
       <c r="H3" t="s">
-        <v>1016</v>
+        <v>1063</v>
       </c>
       <c r="K3" t="s">
-        <v>1017</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>1018</v>
+        <v>1065</v>
       </c>
       <c r="B4" t="s">
-        <v>1012</v>
+        <v>1059</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -12529,10 +12811,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>1019</v>
+        <v>1066</v>
       </c>
       <c r="H4" t="s">
-        <v>1020</v>
+        <v>1067</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -12540,10 +12822,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>1021</v>
+        <v>1068</v>
       </c>
       <c r="B5" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -12558,21 +12840,21 @@
         <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>1022</v>
+        <v>1069</v>
       </c>
       <c r="H5" t="s">
-        <v>1023</v>
+        <v>1070</v>
       </c>
       <c r="K5" t="s">
-        <v>1017</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>1024</v>
+        <v>1071</v>
       </c>
       <c r="B6" t="s">
-        <v>1025</v>
+        <v>1072</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -12584,21 +12866,21 @@
         <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G6" t="s">
-        <v>1027</v>
+        <v>1074</v>
       </c>
       <c r="H6" t="s">
-        <v>1028</v>
+        <v>1075</v>
       </c>
       <c r="K6" t="s">
-        <v>1029</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>1030</v>
+        <v>1077</v>
       </c>
       <c r="B7" t="s">
         <v>131</v>
@@ -12619,15 +12901,15 @@
         <v>542</v>
       </c>
       <c r="H7" t="s">
-        <v>1031</v>
+        <v>1078</v>
       </c>
       <c r="K7" t="s">
-        <v>1032</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>1033</v>
+        <v>1080</v>
       </c>
       <c r="B8" t="s">
         <v>340</v>
@@ -12642,21 +12924,21 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G8" t="s">
-        <v>1034</v>
+        <v>1081</v>
       </c>
       <c r="H8" t="s">
-        <v>1035</v>
+        <v>1082</v>
       </c>
       <c r="K8" t="s">
-        <v>1036</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>1037</v>
+        <v>1084</v>
       </c>
       <c r="B9" t="s">
         <v>263</v>
@@ -12671,21 +12953,21 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G9" t="s">
-        <v>1038</v>
+        <v>1085</v>
       </c>
       <c r="H9" t="s">
-        <v>1039</v>
+        <v>1086</v>
       </c>
       <c r="K9" t="s">
-        <v>1040</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>1041</v>
+        <v>1088</v>
       </c>
       <c r="B10" t="s">
         <v>58</v>
@@ -12703,18 +12985,18 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>1042</v>
+        <v>1089</v>
       </c>
       <c r="H10" t="s">
-        <v>1043</v>
+        <v>1090</v>
       </c>
       <c r="K10" t="s">
-        <v>1044</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>1045</v>
+        <v>1092</v>
       </c>
       <c r="B11" t="s">
         <v>58</v>
@@ -12732,18 +13014,18 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>1046</v>
+        <v>1093</v>
       </c>
       <c r="H11" t="s">
-        <v>1047</v>
+        <v>1094</v>
       </c>
       <c r="K11" t="s">
-        <v>1048</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>1049</v>
+        <v>1096</v>
       </c>
       <c r="B12" t="s">
         <v>58</v>
@@ -12761,18 +13043,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>1050</v>
+        <v>1097</v>
       </c>
       <c r="H12" t="s">
-        <v>1051</v>
+        <v>1098</v>
       </c>
       <c r="K12" t="s">
-        <v>1052</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>1053</v>
+        <v>1100</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -12790,18 +13072,18 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>1054</v>
+        <v>1101</v>
       </c>
       <c r="H13" t="s">
-        <v>1055</v>
+        <v>1102</v>
       </c>
       <c r="K13" t="s">
-        <v>1056</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>756</v>
+        <v>803</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -12819,18 +13101,18 @@
         <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>1057</v>
+        <v>1104</v>
       </c>
       <c r="H14" t="s">
-        <v>1058</v>
+        <v>1105</v>
       </c>
       <c r="K14" t="s">
-        <v>1059</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>1060</v>
+        <v>1107</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
@@ -12848,13 +13130,13 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>1061</v>
+        <v>1108</v>
       </c>
       <c r="H15" t="s">
-        <v>1062</v>
+        <v>1109</v>
       </c>
       <c r="K15" t="s">
-        <v>1063</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -12880,24 +13162,24 @@
         <v>570</v>
       </c>
       <c r="H16" t="s">
-        <v>1064</v>
+        <v>1111</v>
       </c>
       <c r="K16" t="s">
-        <v>1065</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>1066</v>
+        <v>1113</v>
       </c>
       <c r="B17" t="s">
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D17" t="s">
-        <v>1067</v>
+        <v>1114</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
@@ -12906,42 +13188,42 @@
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>1068</v>
+        <v>1115</v>
       </c>
       <c r="H17" t="s">
-        <v>1069</v>
+        <v>1116</v>
       </c>
       <c r="K17" t="s">
-        <v>1070</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>1071</v>
+        <v>1118</v>
       </c>
       <c r="B18" t="s">
         <v>433</v>
       </c>
       <c r="C18" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="D18" t="s">
-        <v>1067</v>
+        <v>1114</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G18" t="s">
-        <v>1072</v>
+        <v>1119</v>
       </c>
       <c r="H18" t="s">
-        <v>1073</v>
+        <v>1120</v>
       </c>
       <c r="K18" t="s">
-        <v>1074</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -12964,18 +13246,18 @@
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="H19" t="s">
-        <v>1076</v>
+        <v>1123</v>
       </c>
       <c r="K19" t="s">
-        <v>1077</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>1078</v>
+        <v>1125</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -12996,15 +13278,15 @@
         <v>349</v>
       </c>
       <c r="H20" t="s">
-        <v>1079</v>
+        <v>1126</v>
       </c>
       <c r="K20" t="s">
-        <v>1080</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>1081</v>
+        <v>1128</v>
       </c>
       <c r="B21" t="s">
         <v>299</v>
@@ -13013,88 +13295,88 @@
         <v>517</v>
       </c>
       <c r="D21" t="s">
-        <v>1082</v>
+        <v>1129</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G21" t="s">
-        <v>1083</v>
+        <v>1130</v>
       </c>
       <c r="H21" t="s">
-        <v>1084</v>
+        <v>1131</v>
       </c>
       <c r="K21" t="s">
-        <v>1085</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>1086</v>
+        <v>1133</v>
       </c>
       <c r="B22" t="s">
         <v>385</v>
       </c>
       <c r="C22" t="s">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="D22" t="s">
-        <v>1087</v>
+        <v>1134</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G22" t="s">
-        <v>1088</v>
+        <v>1135</v>
       </c>
       <c r="H22" t="s">
-        <v>1089</v>
+        <v>1136</v>
       </c>
       <c r="K22" t="s">
-        <v>1090</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>1091</v>
+        <v>1138</v>
       </c>
       <c r="B23" t="s">
         <v>433</v>
       </c>
       <c r="C23" t="s">
-        <v>1092</v>
+        <v>1139</v>
       </c>
       <c r="D23" t="s">
-        <v>1093</v>
+        <v>1140</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G23" t="s">
-        <v>1094</v>
+        <v>1141</v>
       </c>
       <c r="H23" t="s">
-        <v>1095</v>
+        <v>1142</v>
       </c>
       <c r="K23" t="s">
-        <v>1096</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>1097</v>
+        <v>1144</v>
       </c>
       <c r="B24" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -13106,45 +13388,45 @@
         <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G24" t="s">
-        <v>1098</v>
+        <v>1145</v>
       </c>
       <c r="H24" t="s">
-        <v>1099</v>
+        <v>1146</v>
       </c>
       <c r="K24" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="B25" t="s">
         <v>299</v>
       </c>
       <c r="C25" t="s">
-        <v>1102</v>
+        <v>1149</v>
       </c>
       <c r="D25" t="s">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G25" t="s">
-        <v>1088</v>
+        <v>1135</v>
       </c>
       <c r="H25" t="s">
-        <v>1104</v>
+        <v>1151</v>
       </c>
       <c r="K25" t="s">
-        <v>1105</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -13152,7 +13434,7 @@
         <v>466</v>
       </c>
       <c r="B26" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -13167,18 +13449,18 @@
         <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>1106</v>
+        <v>1153</v>
       </c>
       <c r="H26" t="s">
-        <v>1107</v>
+        <v>1154</v>
       </c>
       <c r="K26" t="s">
-        <v>1108</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -13199,18 +13481,18 @@
         <v>447</v>
       </c>
       <c r="H27" t="s">
-        <v>1109</v>
+        <v>1156</v>
       </c>
       <c r="K27" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>952</v>
+        <v>999</v>
       </c>
       <c r="B28" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -13225,18 +13507,18 @@
         <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>1111</v>
+        <v>1158</v>
       </c>
       <c r="H28" t="s">
-        <v>1112</v>
+        <v>1159</v>
       </c>
       <c r="K28" t="s">
-        <v>1113</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>1114</v>
+        <v>1161</v>
       </c>
       <c r="B29" t="s">
         <v>602</v>
@@ -13254,27 +13536,27 @@
         <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>1115</v>
+        <v>1162</v>
       </c>
       <c r="H29" t="s">
-        <v>1116</v>
+        <v>1163</v>
       </c>
       <c r="K29" t="s">
-        <v>1117</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>1118</v>
+        <v>1165</v>
       </c>
       <c r="B30" t="s">
         <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>1119</v>
+        <v>1166</v>
       </c>
       <c r="D30" t="s">
-        <v>1120</v>
+        <v>1167</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -13283,18 +13565,18 @@
         <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>1121</v>
+        <v>1168</v>
       </c>
       <c r="H30" t="s">
-        <v>1122</v>
+        <v>1169</v>
       </c>
       <c r="K30" t="s">
-        <v>1123</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>1124</v>
+        <v>1171</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -13312,18 +13594,18 @@
         <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>1125</v>
+        <v>1172</v>
       </c>
       <c r="H31" t="s">
-        <v>1126</v>
+        <v>1173</v>
       </c>
       <c r="K31" t="s">
-        <v>1127</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>1128</v>
+        <v>1175</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
@@ -13332,7 +13614,7 @@
         <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>1129</v>
+        <v>1176</v>
       </c>
       <c r="E32" t="s">
         <v>29</v>
@@ -13341,18 +13623,18 @@
         <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>1130</v>
+        <v>1177</v>
       </c>
       <c r="H32" t="s">
-        <v>1131</v>
+        <v>1178</v>
       </c>
       <c r="K32" t="s">
-        <v>1132</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>1133</v>
+        <v>1180</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -13361,7 +13643,7 @@
         <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>1129</v>
+        <v>1176</v>
       </c>
       <c r="E33" t="s">
         <v>29</v>
@@ -13370,21 +13652,21 @@
         <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>1134</v>
+        <v>1181</v>
       </c>
       <c r="H33" t="s">
-        <v>1135</v>
+        <v>1182</v>
       </c>
       <c r="K33" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="B34" t="s">
-        <v>1138</v>
+        <v>1185</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -13399,21 +13681,21 @@
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>1139</v>
+        <v>1186</v>
       </c>
       <c r="H34" t="s">
-        <v>1140</v>
+        <v>1187</v>
       </c>
       <c r="K34" t="s">
-        <v>1141</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>1142</v>
+        <v>1189</v>
       </c>
       <c r="B35" t="s">
-        <v>1143</v>
+        <v>1190</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -13428,27 +13710,27 @@
         <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>1144</v>
+        <v>1191</v>
       </c>
       <c r="H35" t="s">
-        <v>1145</v>
+        <v>1192</v>
       </c>
       <c r="K35" t="s">
-        <v>1146</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>1147</v>
+        <v>1194</v>
       </c>
       <c r="B36" t="s">
         <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>1148</v>
+        <v>1195</v>
       </c>
       <c r="D36" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="E36" t="s">
         <v>132</v>
@@ -13457,56 +13739,56 @@
         <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>1150</v>
+        <v>1197</v>
       </c>
       <c r="H36" t="s">
-        <v>1151</v>
+        <v>1198</v>
       </c>
       <c r="K36" t="s">
-        <v>1152</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>1153</v>
+        <v>1200</v>
       </c>
       <c r="B37" t="s">
         <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>1148</v>
+        <v>1195</v>
       </c>
       <c r="D37" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="E37" t="s">
         <v>132</v>
       </c>
       <c r="F37" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G37" t="s">
-        <v>1154</v>
+        <v>1201</v>
       </c>
       <c r="H37" t="s">
-        <v>1155</v>
+        <v>1202</v>
       </c>
       <c r="K37" t="s">
-        <v>1156</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>1157</v>
+        <v>1204</v>
       </c>
       <c r="B38" t="s">
         <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>1148</v>
+        <v>1195</v>
       </c>
       <c r="D38" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="E38" t="s">
         <v>132</v>
@@ -13515,18 +13797,18 @@
         <v>67</v>
       </c>
       <c r="G38" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="H38" t="s">
-        <v>1158</v>
+        <v>1205</v>
       </c>
       <c r="K38" t="s">
-        <v>1159</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>1160</v>
+        <v>1207</v>
       </c>
       <c r="B39" t="s">
         <v>357</v>
@@ -13535,27 +13817,27 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>1161</v>
+        <v>1208</v>
       </c>
       <c r="E39" t="s">
         <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="G39" t="s">
-        <v>1162</v>
+        <v>1209</v>
       </c>
       <c r="H39" t="s">
-        <v>1163</v>
+        <v>1210</v>
       </c>
       <c r="K39" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>1165</v>
+        <v>1212</v>
       </c>
       <c r="B40" t="s">
         <v>58</v>
@@ -13564,7 +13846,7 @@
         <v>268</v>
       </c>
       <c r="D40" t="s">
-        <v>1161</v>
+        <v>1208</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -13573,18 +13855,18 @@
         <v>36</v>
       </c>
       <c r="G40" t="s">
-        <v>1166</v>
+        <v>1213</v>
       </c>
       <c r="H40" t="s">
-        <v>1167</v>
+        <v>1214</v>
       </c>
       <c r="K40" t="s">
-        <v>1168</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>1169</v>
+        <v>1216</v>
       </c>
       <c r="B41" t="s">
         <v>34</v>
@@ -13602,18 +13884,18 @@
         <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>1170</v>
+        <v>1217</v>
       </c>
       <c r="H41" t="s">
-        <v>1171</v>
+        <v>1218</v>
       </c>
       <c r="K41" t="s">
-        <v>1172</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>1173</v>
+        <v>1220</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
@@ -13631,18 +13913,18 @@
         <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>1170</v>
+        <v>1217</v>
       </c>
       <c r="H42" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
       <c r="K42" t="s">
-        <v>1172</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>1175</v>
+        <v>1222</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -13660,13 +13942,13 @@
         <v>36</v>
       </c>
       <c r="G43" t="s">
-        <v>1176</v>
+        <v>1223</v>
       </c>
       <c r="H43" t="s">
-        <v>1177</v>
+        <v>1224</v>
       </c>
       <c r="K43" t="s">
-        <v>1178</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>

--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="1153">
   <si>
     <t>column_name</t>
   </si>
@@ -2532,111 +2532,216 @@
     <t>M-AF | M-AG | M-AI | M-AJ | M-AK</t>
   </si>
   <si>
+    <t>Anonymized patient identifier; format M-XX (Munich, MUC center) or R-XX (Regensburg, REG center) where XX is an alphabetic code; 74 distinct patients across 269 samples</t>
+  </si>
+  <si>
     <t>Center</t>
   </si>
   <si>
     <t>MUC | REG</t>
   </si>
   <si>
+    <t>Academic medical center where the patient was treated and stool samples collected: MUC = Technical University of Munich (Klinikum rechts der Isar); REG = University Medical Center Regensburg; 90 samples from 23 MUC patients, 179 samples from 51 REG patients</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: site-level covariate; antifungal prophylaxis standards (Prophylaxe), dietary standards, and ABX treatment rates differ between MUC and REG (paper Methods and Supp. Table 2)</t>
+  </si>
+  <si>
     <t>Day</t>
   </si>
   <si>
     <t>0 | -7 | 14 | 28 | 35</t>
   </si>
   <si>
+    <t>Day of stool sample collection relative to allo-SCT (Day 0 = day of transplantation); range -50 to +35; negative values are pre-transplant; sampling began at Day -7 (conditioning), then weekly through approximately Day +35 or patient discharge/death; exact numeric counterpart to Timepoint</t>
+  </si>
+  <si>
     <t>0 | COND | 14 | 28 | POST</t>
   </si>
   <si>
+    <t>Named sampling time point: COND = Day -7 (conditioning phase, pre-transplant); 0 = Day 0 (transplant day); 7/14/21/28 = Days 7/14/21/28 post-transplant; POST = Day 35; DONOR = Day -50 (donor stool samples, 2 rows); IDX = Day -25 (1 row, meaning unclear). Timepoint and Day are in perfect 1:1 correspondence with no discrepancies.</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: IDX (1 sample, Day -25) is not documented in the paper or source files; DONOR (2 samples, Day -50) appear to be stool samples from the stem cell donor, not the transplant recipient</t>
+  </si>
+  <si>
     <t>Antibiotic_therapy</t>
   </si>
   <si>
     <t>No ABX | ABX</t>
   </si>
   <si>
+    <t>Antibiotic exposure status at the time of the sample: 'ABX' = the patient had received systemic broad-spectrum antibiotics at or before this sample (cumulative: once started, all subsequent samples of that patient are labeled 'ABX'); 'No ABX' = no antibiotic exposure prior to this sample (paper Methods: Antibiotics section)</t>
+  </si>
+  <si>
     <t>Antifungal_therapy</t>
   </si>
   <si>
     <t>no Antifungals | Antifungals</t>
   </si>
   <si>
+    <t>Therapeutic antifungal treatment at the time of the sample: 'Antifungals' = receiving therapeutic antifungal agents (64/266 non-missing samples); 'no Antifungals' = not receiving therapeutic antifungals; 3 rows missing; distinct from anti-infective prophylaxis (encoded in Prophylaxe)</t>
+  </si>
+  <si>
     <t>Antiviral_therapy</t>
   </si>
   <si>
+    <t>Antiviral therapy at the time of the sample: 1 = receiving antiviral agents (7/265 non-missing samples); 0 = no antiviral therapy; 4 rows missing</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: encoded as integer (0/1) unlike Antibiotic_therapy and Antifungal_therapy which use text labels; specific antiviral agents and the window definition are not documented in available sources</t>
+  </si>
+  <si>
     <t>Prophylaxe</t>
   </si>
   <si>
     <t>1 | 2 | 0</t>
   </si>
   <si>
+    <t>Site-specific anti-infective prophylaxis regimen code: 0 = no prophylaxis (3 MUC patients); 1 = MUC prophylaxis standard; 2 = REG prophylaxis standard; perfectly center-correlated (all 179 REG samples code 2; 84/87 MUC samples code 1; 3 MUC samples code 0); 3 rows missing</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: exact drug regimens for codes 1 and 2 are documented in Supp. Table 2 of the paper (not in local files); paper states 'identical antifungal therapeutic (but different prophylactic) standards between Munich and Regensburg'; MERGE NOTE: Prophylaxe is a site proxy, co-linear with Center</t>
+  </si>
+  <si>
     <t>Current_GVHD_Grade</t>
   </si>
   <si>
     <t>0 | 2 | 1</t>
   </si>
   <si>
+    <t>GI-GvHD status/grade active at the time of this stool sample (source column GVHD_012 in meta_clinical1.xlsx); sample-level, changes within a patient: 0 = no active GI-GvHD at this sample (197/269 samples); 1 = mild GI-GvHD active at this sample (36/269); 2 = severe GI-GvHD active at this sample (36/269). Describes the sample's clinical state, not the patient's final outcome.</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: sample-time GI-GvHD status; not the patient-level outcome used for harmonization. Harmonization source is GVHD_Grade / GVHD (patient-level, from meta_clinical4.csv). UNCERTAIN: exact definition of codes 1 vs 2 (mild vs severe GI-GvHD grade grouping) not stated in available sources; inferred from cross-tabulation with GVHD_Grade</t>
+  </si>
+  <si>
     <t>Patient_Age</t>
   </si>
   <si>
     <t>56 | 61 | 51 | 55 | 54</t>
   </si>
   <si>
+    <t>Patient age at allo-SCT in years (decimal); range 19.6 to 71 years; patient-level variable replicated across that patient's samples</t>
+  </si>
+  <si>
     <t>Male_Sex</t>
   </si>
   <si>
+    <t>Patient biological sex: 1 = male; 0 = female; based on electronic patient records (paper Methods: Study Design section)</t>
+  </si>
+  <si>
     <t>NHL | CMML | AML | BPDCN | MDS/MPN</t>
   </si>
   <si>
+    <t>Underlying hematologic disease indication for allo-SCT; abbreviations: AML = acute myeloid leukemia; MDS = myelodysplastic syndrome; ALL = acute lymphoblastic leukemia; MM = multiple myeloma; NHL = non-Hodgkin lymphoma (B-cell); CMML = chronic myelomonocytic leukemia; MDS/MPN = myelodysplastic syndrome / myeloproliferative neoplasm overlap; BPDCN = blastic plasmacytoid dendritic cell neoplasm; Myelosarkom = myelosarcoma (German spelling); CLL = chronic lymphocytic leukemia; CML = chronic myeloid leukemia; MPS = myeloproliferative syndrome (non-standard abbreviation, likely MPN); Myelofibrose = myelofibrosis (German); CAEBV/Immunodeficiency = chronic active Epstein-Barr virus infection / immunodeficiency; OMF = osteomyelofibrosis (primary myelofibrosis); OMF nach ET = osteomyelofibrosis following essential thrombocythemia (German); sAA = severe aplastic anemia; T-NHL = T-cell non-Hodgkin lymphoma; T-PLL = T-cell prolymphocytic leukemia; Myelom = myeloma (German; same disease as MM)</t>
+  </si>
+  <si>
+    <t>NOTE: 'Myelom' (2 samples) and 'MM' (12 samples) appear to encode the same disease (multiple myeloma) using German and English spellings respectively; 'MPS' is a non-standard abbreviation, likely equivalent to MPN; German disease names are used inconsistently alongside English abbreviations</t>
+  </si>
+  <si>
     <t>Graft_type</t>
   </si>
   <si>
+    <t>Type of allogeneic stem cell graft: 0 = unmodified peripheral blood stem cells (PBSC; 221/268 non-missing samples = 82%); 1 = other graft type (47/268 = 18%); center-specific rates (94% MUC code 0, 77% REG code 0) match paper-reported PBSC rates of 96% and 75% for MUC and REG respectively</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: code 1 (other graft type) is not defined in the paper; likely bone marrow based on standard allo-SCT practice, but the paper does not state this; code 0 confirmed as unmodified PBSC by matching paper-reported percentages (paper: 'unmodified peripheral-blood stem cells')</t>
+  </si>
+  <si>
     <t>Donor_type</t>
   </si>
   <si>
     <t>2 | 0 | 1</t>
   </si>
   <si>
+    <t>Relationship between the stem cell donor and recipient: 0 = unrelated donor (56/77 patients = 73%, matching paper-reported 72-74% unrelated); 1 = related donor (9/77 = 12%); 2 = haploidentical donor (12/77 = 16%); 1 sample missing</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: codes 1 (related/sibling) and 2 (haploidentical) are inferred from clinical epidemiology (paper reports 72-74% unrelated); the paper does not provide an explicit coding key; MERGE NOTE: three-level code; do not collapse to binary without confirming how haplo donors should be treated</t>
+  </si>
+  <si>
     <t>Conditioning_Regimen</t>
   </si>
   <si>
+    <t>Pre-transplant conditioning intensity: 0 = reduced intensity conditioning (RIC; 236/268 samples = 88%); 1 = myeloablative conditioning (MAC; 32/268 = 12%); matches paper-reported 88% and 87% RIC in MUC and REG respectively; 1 sample missing</t>
+  </si>
+  <si>
+    <t>Total body irradiation as part of the conditioning regimen: 1 = received TBI (35/268 samples); 0 = no TBI (233/268 samples); 1 sample missing</t>
+  </si>
+  <si>
     <t>HCT_CI</t>
   </si>
   <si>
     <t>0 | 3 | 9 | 4 | 2</t>
   </si>
   <si>
+    <t>Hematopoietic Cell Transplantation Comorbidity Index (HCT-CI); integer scale 0-9 where 0 = no comorbidities and higher scores predict greater non-relapse mortality; 90 of 269 samples have no HCT-CI recorded</t>
+  </si>
+  <si>
+    <t>NOTE: 90 missing samples reflect patients for whom the HCT-CI was not assessed; as a patient-level variable, all samples from the same patient share the same value or the same missingness</t>
+  </si>
+  <si>
     <t>Onset_days</t>
   </si>
   <si>
     <t>365 | 48 | 99 | 36 | 305</t>
   </si>
   <si>
+    <t>Days from allo-SCT (Day 0) to GI-GvHD onset (for patients with GVHD_Grade &gt; 0) or to censoring (for patients with GVHD_Grade = 0); most no-GvHD patients are censored at 365 days (1-year follow-up); 6 samples have no value; range 9-365 days</t>
+  </si>
+  <si>
+    <t>NOTE: for the 36 patients with GVHD_Grade=0, Onset_days is a censoring time, not an onset day: 34 patients have 365 (censored at 1 year), 1 has 170 (censored at death, confirmed by survival_1yr_days=170), 1 has 305 (censored at loss to follow-up, survival_1yr_overall=2); non-event values must be masked at harmonization</t>
+  </si>
+  <si>
     <t>Steroidrefractory</t>
   </si>
   <si>
     <t>2 | 1 | 0</t>
   </si>
   <si>
+    <t>Steroid refractoriness classification: 2 = no GI-GvHD (assessment not applicable; 35/77 patients, all with GVHD_Grade=0); 0 = GI-GvHD present and responded to corticosteroids (steroid-sensitive; 19/77 patients); 1 = GI-GvHD present and did not respond to corticosteroids (steroid-refractory; 23/77 patients); 1 patient missing</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: code assignment is inferred from cross-tabulation with GVHD_Grade (code 2 aligns entirely with GVHD_Grade=0 patients; codes 0 and 1 align with GVHD-positive patients); the paper does not provide an explicit coding key; code 2 as 'no GvHD / not applicable' is counter-intuitive numbering; MERGE NOTE: three-level code; collapsing to binary requires deciding how to handle code 2 (NA or 0)</t>
+  </si>
+  <si>
     <t>survival_1yr_overall</t>
   </si>
   <si>
     <t>0 | 1 | 2</t>
   </si>
   <si>
+    <t>1-year overall survival status: 0 = alive at 1 year (61/78 patients at patient level); 1 = died within 1 year (15/78 patients); 2 = unknown/censored before 1 year (2/78 patients, with survival_1yr_days &lt; 365)</t>
+  </si>
+  <si>
+    <t>UNCERTAIN: code 2 (2 patients) interpretation inferred from data — both patients have survival_1yr_days &lt; 365 and matching Onset_days, suggesting censoring before 1 year due to loss to follow-up or administrative reasons; the paper does not define this three-level coding</t>
+  </si>
+  <si>
     <t>survival_1yr_days</t>
   </si>
   <si>
     <t>365 | 74 | 335 | 88 | 305</t>
   </si>
   <si>
+    <t>Days from allo-SCT (Day 0) to death or censoring at 1 year; event patients (survival_1yr_overall=1) have the actual day of death; patients alive at 1 year (survival_1yr_overall=0) have 365 (208/269 samples have value 365); 2 patients censored before 1 year have their last contact day</t>
+  </si>
+  <si>
     <t>Relapse</t>
   </si>
   <si>
+    <t>Disease relapse within 1-year follow-up after allo-SCT: 1 = relapsed (30/269 samples across relapsed patients); 0 = no relapse within 1 year (239/269 samples)</t>
+  </si>
+  <si>
     <t>Relapse_days</t>
   </si>
   <si>
     <t>365 | 335 | 90 | 305 | 60</t>
   </si>
   <si>
+    <t>Days from allo-SCT (Day 0) to relapse (for Relapse=1) or censoring at 1 year (for Relapse=0); non-relapse patients are censored at 365 days; range 30-365 days; 6 samples have no value</t>
+  </si>
+  <si>
     <t>AlloTx_2nd</t>
   </si>
   <si>
@@ -2655,13 +2760,31 @@
     <t>TRM_1yr</t>
   </si>
   <si>
+    <t>Transplant-related mortality within 1 year after allo-SCT: 1 = patient died from transplant-related causes without prior relapse within 1 year (38/269 samples across TRM patients); 0 = no TRM within 1 year (231/269 samples)</t>
+  </si>
+  <si>
     <t>Relapse_days_only_approx</t>
   </si>
   <si>
+    <t>Flag indicating that the Relapse_days value is approximate rather than exact: 1 = approximate date (13/269 samples, corresponding to 4 patients in meta_clinical4.csv); 0 = exact date known (256/269 samples)</t>
+  </si>
+  <si>
     <t>GVHD_Grade</t>
   </si>
   <si>
+    <t>Patient-level GI-GvHD outcome grade during follow-up (source column GvHD in meta_clinical4.csv, renamed in Parsing_metadata.qmd): 0 = no GI-GvHD (103/268 non-missing samples, 36/77 patients = 47%); 1 = mild GI-GvHD (90/268 samples, 22 patients = 29%); 2 = severe GI-GvHD (75/268 samples, 19 patients = 25%); 1 sample missing. This is the patient-level GI-GvHD outcome used by the authors.</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: patient-level GI-GvHD outcome; harmonization source for aGvHD outcome alongside the derived binary GVHD column. UNCERTAIN: the grade grouping (1=mild, 2=severe) is inferred from paper grouping (groups 0-1 as 'mild' and 2-4 as 'severe GI-GvHD'); the explicit coding key (e.g., whether grade 1 maps to clinical GI stage 1 only or to stages 1-2) is not stated in the source files</t>
+  </si>
+  <si>
     <t>GVHD</t>
+  </si>
+  <si>
+    <t>Binary GI-GvHD indicator derived from GVHD_Grade in Parsing_metadata.qmd: 1 = any GI-GvHD (GVHD_Grade &gt; 0; 165/268 non-missing samples, 41/77 patients = 53%); 0 = no GI-GvHD (GVHD_Grade = 0; 103/268 samples, 36 patients = 47%); 1 sample missing</t>
+  </si>
+  <si>
+    <t>MERGE NOTE: patient-level binary GI-GvHD outcome; primary harmonization source for the binary aGvHD outcome</t>
   </si>
   <si>
     <t>ERR13060015 | ERR13060016 | ERR13060017 | ERR13060018 | ERR13060019</t>
@@ -11168,10 +11291,13 @@
       <c r="G6" t="s">
         <v>835</v>
       </c>
+      <c r="H6" t="s">
+        <v>836</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -11189,12 +11315,18 @@
         <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>837</v>
+        <v>838</v>
+      </c>
+      <c r="H7" t="s">
+        <v>839</v>
+      </c>
+      <c r="K7" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -11212,7 +11344,10 @@
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>839</v>
+        <v>842</v>
+      </c>
+      <c r="H8" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -11235,12 +11370,18 @@
         <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>840</v>
+        <v>844</v>
+      </c>
+      <c r="H9" t="s">
+        <v>845</v>
+      </c>
+      <c r="K9" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -11258,12 +11399,15 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>842</v>
+        <v>848</v>
+      </c>
+      <c r="H10" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -11281,12 +11425,15 @@
         <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>844</v>
+        <v>851</v>
+      </c>
+      <c r="H11" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -11306,10 +11453,16 @@
       <c r="G12" t="s">
         <v>316</v>
       </c>
+      <c r="H12" t="s">
+        <v>854</v>
+      </c>
+      <c r="K12" t="s">
+        <v>855</v>
+      </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11327,12 +11480,18 @@
         <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>847</v>
+        <v>857</v>
+      </c>
+      <c r="H13" t="s">
+        <v>858</v>
+      </c>
+      <c r="K13" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -11350,12 +11509,18 @@
         <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>849</v>
+        <v>861</v>
+      </c>
+      <c r="H14" t="s">
+        <v>862</v>
+      </c>
+      <c r="K14" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="B15">
         <v>65</v>
@@ -11373,12 +11538,15 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>851</v>
+        <v>865</v>
+      </c>
+      <c r="H15" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -11397,6 +11565,9 @@
       </c>
       <c r="G16" t="s">
         <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -11419,12 +11590,18 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>853</v>
+        <v>869</v>
+      </c>
+      <c r="H17" t="s">
+        <v>870</v>
+      </c>
+      <c r="K17" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -11444,10 +11621,16 @@
       <c r="G18" t="s">
         <v>316</v>
       </c>
+      <c r="H18" t="s">
+        <v>873</v>
+      </c>
+      <c r="K18" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -11465,12 +11648,18 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>856</v>
+        <v>876</v>
+      </c>
+      <c r="H19" t="s">
+        <v>877</v>
+      </c>
+      <c r="K19" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>857</v>
+        <v>879</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -11489,6 +11678,9 @@
       </c>
       <c r="G20" t="s">
         <v>316</v>
+      </c>
+      <c r="H20" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -11513,10 +11705,13 @@
       <c r="G21" t="s">
         <v>316</v>
       </c>
+      <c r="H21" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -11534,12 +11729,18 @@
         <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>859</v>
+        <v>883</v>
+      </c>
+      <c r="H22" t="s">
+        <v>884</v>
+      </c>
+      <c r="K22" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>860</v>
+        <v>886</v>
       </c>
       <c r="B23">
         <v>28</v>
@@ -11557,12 +11758,18 @@
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>861</v>
+        <v>887</v>
+      </c>
+      <c r="H23" t="s">
+        <v>888</v>
+      </c>
+      <c r="K23" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>862</v>
+        <v>890</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -11580,12 +11787,18 @@
         <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>863</v>
+        <v>891</v>
+      </c>
+      <c r="H24" t="s">
+        <v>892</v>
+      </c>
+      <c r="K24" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>864</v>
+        <v>894</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -11603,12 +11816,18 @@
         <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>865</v>
+        <v>895</v>
+      </c>
+      <c r="H25" t="s">
+        <v>896</v>
+      </c>
+      <c r="K25" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>866</v>
+        <v>898</v>
       </c>
       <c r="B26">
         <v>15</v>
@@ -11626,12 +11845,15 @@
         <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>867</v>
+        <v>899</v>
+      </c>
+      <c r="H26" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -11651,10 +11873,13 @@
       <c r="G27" t="s">
         <v>316</v>
       </c>
+      <c r="H27" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>869</v>
+        <v>903</v>
       </c>
       <c r="B28">
         <v>21</v>
@@ -11672,12 +11897,15 @@
         <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>870</v>
+        <v>904</v>
+      </c>
+      <c r="H28" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>871</v>
+        <v>906</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -11695,15 +11923,15 @@
         <v>32</v>
       </c>
       <c r="H29" t="s">
-        <v>872</v>
+        <v>907</v>
       </c>
       <c r="K29" t="s">
-        <v>873</v>
+        <v>908</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>874</v>
+        <v>909</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -11721,15 +11949,15 @@
         <v>32</v>
       </c>
       <c r="H30" t="s">
-        <v>875</v>
+        <v>910</v>
       </c>
       <c r="K30" t="s">
-        <v>873</v>
+        <v>908</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>876</v>
+        <v>911</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -11749,10 +11977,13 @@
       <c r="G31" t="s">
         <v>316</v>
       </c>
+      <c r="H31" t="s">
+        <v>912</v>
+      </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>877</v>
+        <v>913</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -11772,10 +12003,13 @@
       <c r="G32" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>878</v>
+        <v>915</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -11793,12 +12027,18 @@
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>861</v>
+      </c>
+      <c r="H33" t="s">
+        <v>916</v>
+      </c>
+      <c r="K33" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>879</v>
+        <v>918</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -11817,6 +12057,12 @@
       </c>
       <c r="G34" t="s">
         <v>316</v>
+      </c>
+      <c r="H34" t="s">
+        <v>919</v>
+      </c>
+      <c r="K34" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -11884,10 +12130,10 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>880</v>
+        <v>921</v>
       </c>
       <c r="H2" t="s">
-        <v>881</v>
+        <v>922</v>
       </c>
       <c r="K2" t="s">
         <v>16</v>
@@ -11895,7 +12141,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -11913,10 +12159,10 @@
         <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>883</v>
+        <v>924</v>
       </c>
       <c r="H3" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -11939,10 +12185,10 @@
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="H4" t="s">
-        <v>886</v>
+        <v>927</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -11965,10 +12211,10 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>887</v>
+        <v>928</v>
       </c>
       <c r="H5" t="s">
-        <v>888</v>
+        <v>929</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -11991,10 +12237,10 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>889</v>
+        <v>930</v>
       </c>
       <c r="H6" t="s">
-        <v>890</v>
+        <v>931</v>
       </c>
       <c r="K6" t="s">
         <v>16</v>
@@ -12020,15 +12266,15 @@
         <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>891</v>
+        <v>932</v>
       </c>
       <c r="H7" t="s">
-        <v>892</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>893</v>
+        <v>934</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -12046,15 +12292,15 @@
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="H8" t="s">
-        <v>895</v>
+        <v>936</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
       <c r="B9">
         <v>34</v>
@@ -12072,18 +12318,18 @@
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>897</v>
+        <v>938</v>
       </c>
       <c r="H9" t="s">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="K9" t="s">
-        <v>899</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>900</v>
+        <v>941</v>
       </c>
       <c r="B10">
         <v>77</v>
@@ -12101,10 +12347,10 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>901</v>
+        <v>942</v>
       </c>
       <c r="H10" t="s">
-        <v>902</v>
+        <v>943</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -12130,7 +12376,7 @@
         <v>695</v>
       </c>
       <c r="H11" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -12153,15 +12399,15 @@
         <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>904</v>
+        <v>945</v>
       </c>
       <c r="H12" t="s">
-        <v>905</v>
+        <v>946</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -12179,15 +12425,15 @@
         <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>907</v>
+        <v>948</v>
       </c>
       <c r="H13" t="s">
-        <v>908</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>909</v>
+        <v>950</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -12205,18 +12451,18 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>910</v>
+        <v>951</v>
       </c>
       <c r="H14" t="s">
-        <v>911</v>
+        <v>952</v>
       </c>
       <c r="K14" t="s">
-        <v>912</v>
+        <v>953</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>913</v>
+        <v>954</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -12234,18 +12480,18 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>914</v>
+        <v>955</v>
       </c>
       <c r="H15" t="s">
-        <v>915</v>
+        <v>956</v>
       </c>
       <c r="K15" t="s">
-        <v>916</v>
+        <v>957</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>917</v>
+        <v>958</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -12263,18 +12509,18 @@
         <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>918</v>
+        <v>959</v>
       </c>
       <c r="H16" t="s">
-        <v>919</v>
+        <v>960</v>
       </c>
       <c r="K16" t="s">
-        <v>920</v>
+        <v>961</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>921</v>
+        <v>962</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -12295,12 +12541,12 @@
         <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>922</v>
+        <v>963</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>923</v>
+        <v>964</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -12321,7 +12567,7 @@
         <v>316</v>
       </c>
       <c r="H18" t="s">
-        <v>924</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -12347,12 +12593,12 @@
         <v>316</v>
       </c>
       <c r="H19" t="s">
-        <v>925</v>
+        <v>966</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>926</v>
+        <v>967</v>
       </c>
       <c r="B20">
         <v>9</v>
@@ -12370,15 +12616,15 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="H20" t="s">
-        <v>928</v>
+        <v>969</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="B21">
         <v>9</v>
@@ -12396,18 +12642,18 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>930</v>
+        <v>971</v>
       </c>
       <c r="H21" t="s">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="K21" t="s">
-        <v>932</v>
+        <v>973</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>933</v>
+        <v>974</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -12425,18 +12671,18 @@
         <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>934</v>
+        <v>975</v>
       </c>
       <c r="H22" t="s">
-        <v>935</v>
+        <v>976</v>
       </c>
       <c r="K22" t="s">
-        <v>936</v>
+        <v>977</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>937</v>
+        <v>978</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -12454,13 +12700,13 @@
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>938</v>
+        <v>979</v>
       </c>
       <c r="H23" t="s">
-        <v>939</v>
+        <v>980</v>
       </c>
       <c r="K23" t="s">
-        <v>936</v>
+        <v>977</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -12486,12 +12732,12 @@
         <v>56</v>
       </c>
       <c r="H24" t="s">
-        <v>940</v>
+        <v>981</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>941</v>
+        <v>982</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -12509,10 +12755,10 @@
         <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>942</v>
+        <v>983</v>
       </c>
       <c r="H25" t="s">
-        <v>943</v>
+        <v>984</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -12535,15 +12781,15 @@
         <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>944</v>
+        <v>985</v>
       </c>
       <c r="H26" t="s">
-        <v>945</v>
+        <v>986</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>946</v>
+        <v>987</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -12561,15 +12807,15 @@
         <v>27</v>
       </c>
       <c r="G27" t="s">
-        <v>947</v>
+        <v>988</v>
       </c>
       <c r="H27" t="s">
-        <v>948</v>
+        <v>989</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>949</v>
+        <v>990</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -12587,15 +12833,15 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>950</v>
+        <v>991</v>
       </c>
       <c r="H28" t="s">
-        <v>951</v>
+        <v>992</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>952</v>
+        <v>993</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -12613,15 +12859,15 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>953</v>
+        <v>994</v>
       </c>
       <c r="H29" t="s">
-        <v>954</v>
+        <v>995</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>955</v>
+        <v>996</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -12642,15 +12888,15 @@
         <v>230</v>
       </c>
       <c r="H30" t="s">
-        <v>956</v>
+        <v>997</v>
       </c>
       <c r="K30" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>958</v>
+        <v>999</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -12668,10 +12914,10 @@
         <v>27</v>
       </c>
       <c r="G31" t="s">
-        <v>959</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="s">
-        <v>960</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -12694,10 +12940,10 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>961</v>
+        <v>1002</v>
       </c>
       <c r="H32" t="s">
-        <v>962</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -12765,7 +13011,7 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>963</v>
+        <v>1004</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -12776,7 +13022,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>964</v>
+        <v>1005</v>
       </c>
       <c r="B3">
         <v>50</v>
@@ -12794,18 +13040,18 @@
         <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>965</v>
+        <v>1006</v>
       </c>
       <c r="H3" t="s">
-        <v>966</v>
+        <v>1007</v>
       </c>
       <c r="K3" t="s">
-        <v>967</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>968</v>
+        <v>1009</v>
       </c>
       <c r="B4">
         <v>118</v>
@@ -12823,10 +13069,10 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>969</v>
+        <v>1010</v>
       </c>
       <c r="H4" t="s">
-        <v>970</v>
+        <v>1011</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
@@ -12834,7 +13080,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>971</v>
+        <v>1012</v>
       </c>
       <c r="B5">
         <v>50</v>
@@ -12852,18 +13098,18 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>972</v>
+        <v>1013</v>
       </c>
       <c r="H5" t="s">
-        <v>973</v>
+        <v>1014</v>
       </c>
       <c r="K5" t="s">
-        <v>967</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>974</v>
+        <v>1015</v>
       </c>
       <c r="B6">
         <v>82</v>
@@ -12878,21 +13124,21 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G6" t="s">
-        <v>976</v>
+        <v>1017</v>
       </c>
       <c r="H6" t="s">
-        <v>977</v>
+        <v>1018</v>
       </c>
       <c r="K6" t="s">
-        <v>978</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>979</v>
+        <v>1020</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -12913,15 +13159,15 @@
         <v>491</v>
       </c>
       <c r="H7" t="s">
-        <v>980</v>
+        <v>1021</v>
       </c>
       <c r="K7" t="s">
-        <v>981</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>982</v>
+        <v>1023</v>
       </c>
       <c r="B8">
         <v>46</v>
@@ -12936,21 +13182,21 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G8" t="s">
-        <v>983</v>
+        <v>1024</v>
       </c>
       <c r="H8" t="s">
-        <v>984</v>
+        <v>1025</v>
       </c>
       <c r="K8" t="s">
-        <v>985</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>986</v>
+        <v>1027</v>
       </c>
       <c r="B9">
         <v>47</v>
@@ -12965,21 +13211,21 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G9" t="s">
-        <v>987</v>
+        <v>1028</v>
       </c>
       <c r="H9" t="s">
-        <v>988</v>
+        <v>1029</v>
       </c>
       <c r="K9" t="s">
-        <v>989</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>990</v>
+        <v>1031</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -12997,18 +13243,18 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>991</v>
+        <v>1032</v>
       </c>
       <c r="H10" t="s">
-        <v>992</v>
+        <v>1033</v>
       </c>
       <c r="K10" t="s">
-        <v>993</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>994</v>
+        <v>1035</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -13026,18 +13272,18 @@
         <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>995</v>
+        <v>1036</v>
       </c>
       <c r="H11" t="s">
-        <v>996</v>
+        <v>1037</v>
       </c>
       <c r="K11" t="s">
-        <v>997</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>998</v>
+        <v>1039</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -13055,18 +13301,18 @@
         <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>999</v>
+        <v>1040</v>
       </c>
       <c r="H12" t="s">
-        <v>1000</v>
+        <v>1041</v>
       </c>
       <c r="K12" t="s">
-        <v>1001</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>1002</v>
+        <v>1043</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -13084,13 +13330,13 @@
         <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>1003</v>
+        <v>1044</v>
       </c>
       <c r="H13" t="s">
-        <v>1004</v>
+        <v>1045</v>
       </c>
       <c r="K13" t="s">
-        <v>1005</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -13113,18 +13359,18 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>1006</v>
+        <v>1047</v>
       </c>
       <c r="H14" t="s">
-        <v>1007</v>
+        <v>1048</v>
       </c>
       <c r="K14" t="s">
-        <v>1008</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>1009</v>
+        <v>1050</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -13142,13 +13388,13 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>1010</v>
+        <v>1051</v>
       </c>
       <c r="H15" t="s">
-        <v>1011</v>
+        <v>1052</v>
       </c>
       <c r="K15" t="s">
-        <v>1012</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -13174,15 +13420,15 @@
         <v>513</v>
       </c>
       <c r="H16" t="s">
-        <v>1013</v>
+        <v>1054</v>
       </c>
       <c r="K16" t="s">
-        <v>1014</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>1015</v>
+        <v>1056</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -13200,18 +13446,18 @@
         <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>1016</v>
+        <v>1057</v>
       </c>
       <c r="H17" t="s">
-        <v>1017</v>
+        <v>1058</v>
       </c>
       <c r="K17" t="s">
-        <v>1018</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>1019</v>
+        <v>1060</v>
       </c>
       <c r="B18">
         <v>30</v>
@@ -13226,16 +13472,16 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G18" t="s">
-        <v>1020</v>
+        <v>1061</v>
       </c>
       <c r="H18" t="s">
-        <v>1021</v>
+        <v>1062</v>
       </c>
       <c r="K18" t="s">
-        <v>1022</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -13258,18 +13504,18 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>865</v>
+        <v>895</v>
       </c>
       <c r="H19" t="s">
-        <v>1023</v>
+        <v>1064</v>
       </c>
       <c r="K19" t="s">
-        <v>1024</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>1025</v>
+        <v>1066</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -13290,15 +13536,15 @@
         <v>316</v>
       </c>
       <c r="H20" t="s">
-        <v>1026</v>
+        <v>1067</v>
       </c>
       <c r="K20" t="s">
-        <v>1027</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>1028</v>
+        <v>1069</v>
       </c>
       <c r="B21">
         <v>18</v>
@@ -13313,21 +13559,21 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G21" t="s">
-        <v>1029</v>
+        <v>1070</v>
       </c>
       <c r="H21" t="s">
-        <v>1030</v>
+        <v>1071</v>
       </c>
       <c r="K21" t="s">
-        <v>1031</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>1032</v>
+        <v>1073</v>
       </c>
       <c r="B22">
         <v>17</v>
@@ -13342,21 +13588,21 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G22" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="H22" t="s">
-        <v>1034</v>
+        <v>1075</v>
       </c>
       <c r="K22" t="s">
-        <v>1035</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>1036</v>
+        <v>1077</v>
       </c>
       <c r="B23">
         <v>30</v>
@@ -13371,21 +13617,21 @@
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G23" t="s">
-        <v>1037</v>
+        <v>1078</v>
       </c>
       <c r="H23" t="s">
-        <v>1038</v>
+        <v>1079</v>
       </c>
       <c r="K23" t="s">
-        <v>1039</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>1040</v>
+        <v>1081</v>
       </c>
       <c r="B24">
         <v>49</v>
@@ -13400,21 +13646,21 @@
         <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G24" t="s">
-        <v>1041</v>
+        <v>1082</v>
       </c>
       <c r="H24" t="s">
-        <v>1042</v>
+        <v>1083</v>
       </c>
       <c r="K24" t="s">
-        <v>1043</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>1044</v>
+        <v>1085</v>
       </c>
       <c r="B25">
         <v>18</v>
@@ -13429,16 +13675,16 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G25" t="s">
-        <v>1033</v>
+        <v>1074</v>
       </c>
       <c r="H25" t="s">
-        <v>1045</v>
+        <v>1086</v>
       </c>
       <c r="K25" t="s">
-        <v>1046</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -13461,13 +13707,13 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>1047</v>
+        <v>1088</v>
       </c>
       <c r="H26" t="s">
-        <v>1048</v>
+        <v>1089</v>
       </c>
       <c r="K26" t="s">
-        <v>1049</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -13493,15 +13739,15 @@
         <v>405</v>
       </c>
       <c r="H27" t="s">
-        <v>1050</v>
+        <v>1091</v>
       </c>
       <c r="K27" t="s">
-        <v>1051</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -13519,18 +13765,18 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>1052</v>
+        <v>1093</v>
       </c>
       <c r="H28" t="s">
-        <v>1053</v>
+        <v>1094</v>
       </c>
       <c r="K28" t="s">
-        <v>1054</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>1055</v>
+        <v>1096</v>
       </c>
       <c r="B29">
         <v>11</v>
@@ -13548,18 +13794,18 @@
         <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>1056</v>
+        <v>1097</v>
       </c>
       <c r="H29" t="s">
-        <v>1057</v>
+        <v>1098</v>
       </c>
       <c r="K29" t="s">
-        <v>1058</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>1059</v>
+        <v>1100</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -13577,18 +13823,18 @@
         <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>1060</v>
+        <v>1101</v>
       </c>
       <c r="H30" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="K30" t="s">
-        <v>1062</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>1063</v>
+        <v>1104</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -13606,18 +13852,18 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
       <c r="H31" t="s">
-        <v>1065</v>
+        <v>1106</v>
       </c>
       <c r="K31" t="s">
-        <v>1066</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>1067</v>
+        <v>1108</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -13635,18 +13881,18 @@
         <v>32</v>
       </c>
       <c r="G32" t="s">
-        <v>1068</v>
+        <v>1109</v>
       </c>
       <c r="H32" t="s">
-        <v>1069</v>
+        <v>1110</v>
       </c>
       <c r="K32" t="s">
-        <v>1070</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>1071</v>
+        <v>1112</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -13664,18 +13910,18 @@
         <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>1072</v>
+        <v>1113</v>
       </c>
       <c r="H33" t="s">
-        <v>1073</v>
+        <v>1114</v>
       </c>
       <c r="K33" t="s">
-        <v>1074</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>1075</v>
+        <v>1116</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -13693,18 +13939,18 @@
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>1076</v>
+        <v>1117</v>
       </c>
       <c r="H34" t="s">
-        <v>1077</v>
+        <v>1118</v>
       </c>
       <c r="K34" t="s">
-        <v>1078</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>1079</v>
+        <v>1120</v>
       </c>
       <c r="B35">
         <v>37</v>
@@ -13722,18 +13968,18 @@
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>1080</v>
+        <v>1121</v>
       </c>
       <c r="H35" t="s">
-        <v>1081</v>
+        <v>1122</v>
       </c>
       <c r="K35" t="s">
-        <v>1082</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>1083</v>
+        <v>1124</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -13751,18 +13997,18 @@
         <v>32</v>
       </c>
       <c r="G36" t="s">
-        <v>1084</v>
+        <v>1125</v>
       </c>
       <c r="H36" t="s">
-        <v>1085</v>
+        <v>1126</v>
       </c>
       <c r="K36" t="s">
-        <v>1086</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>1087</v>
+        <v>1128</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -13777,21 +14023,21 @@
         <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G37" t="s">
-        <v>1088</v>
+        <v>1129</v>
       </c>
       <c r="H37" t="s">
-        <v>1089</v>
+        <v>1130</v>
       </c>
       <c r="K37" t="s">
-        <v>1090</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>1091</v>
+        <v>1132</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -13812,15 +14058,15 @@
         <v>610</v>
       </c>
       <c r="H38" t="s">
-        <v>1092</v>
+        <v>1133</v>
       </c>
       <c r="K38" t="s">
-        <v>1093</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>1094</v>
+        <v>1135</v>
       </c>
       <c r="B39">
         <v>28</v>
@@ -13835,21 +14081,21 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>975</v>
+        <v>1016</v>
       </c>
       <c r="G39" t="s">
-        <v>1095</v>
+        <v>1136</v>
       </c>
       <c r="H39" t="s">
-        <v>1096</v>
+        <v>1137</v>
       </c>
       <c r="K39" t="s">
-        <v>1097</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>1098</v>
+        <v>1139</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -13867,18 +14113,18 @@
         <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>1099</v>
+        <v>1140</v>
       </c>
       <c r="H40" t="s">
-        <v>1100</v>
+        <v>1141</v>
       </c>
       <c r="K40" t="s">
-        <v>1101</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>1102</v>
+        <v>1143</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -13896,18 +14142,18 @@
         <v>32</v>
       </c>
       <c r="G41" t="s">
-        <v>1103</v>
+        <v>1144</v>
       </c>
       <c r="H41" t="s">
-        <v>1104</v>
+        <v>1145</v>
       </c>
       <c r="K41" t="s">
-        <v>1105</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>1106</v>
+        <v>1147</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -13925,18 +14171,18 @@
         <v>32</v>
       </c>
       <c r="G42" t="s">
-        <v>1103</v>
+        <v>1144</v>
       </c>
       <c r="H42" t="s">
-        <v>1107</v>
+        <v>1148</v>
       </c>
       <c r="K42" t="s">
-        <v>1105</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>1108</v>
+        <v>1149</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -13954,13 +14200,13 @@
         <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>1109</v>
+        <v>1150</v>
       </c>
       <c r="H43" t="s">
-        <v>1110</v>
+        <v>1151</v>
       </c>
       <c r="K43" t="s">
-        <v>1111</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>

--- a/Merging/data_dictionaries.xlsx
+++ b/Merging/data_dictionaries.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sophiehuebler/Documents/ODSi/ODSiData/Merging/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF030087-105F-B848-B7C5-2DC0921EA770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="34880" yWindow="-14860" windowWidth="37840" windowHeight="21900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Artacho" sheetId="1" r:id="rId1"/>
@@ -17,7 +23,7 @@
     <sheet name="Spindelboek" sheetId="8" r:id="rId8"/>
     <sheet name="Vallet" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -2559,9 +2565,6 @@
     <t>0 | COND | 14 | 28 | POST</t>
   </si>
   <si>
-    <t>Named sampling time point: COND = Day -7 (conditioning phase, pre-transplant); 0 = Day 0 (transplant day); 7/14/21/28 = Days 7/14/21/28 post-transplant; POST = Day 35; DONOR = Day -50 (donor stool samples, 2 rows); IDX = Day -25 (1 row, meaning unclear). Timepoint and Day are in perfect 1:1 correspondence with no discrepancies.</t>
-  </si>
-  <si>
     <t>UNCERTAIN: IDX (1 sample, Day -25) is not documented in the paper or source files; DONOR (2 samples, Day -50) appear to be stool samples from the stem cell donor, not the transplant recipient</t>
   </si>
   <si>
@@ -2655,9 +2658,6 @@
     <t>2 | 0 | 1</t>
   </si>
   <si>
-    <t>Relationship between the stem cell donor and recipient: 0 = unrelated donor (56/77 patients = 73%, matching paper-reported 72-74% unrelated); 1 = related donor (9/77 = 12%); 2 = haploidentical donor (12/77 = 16%); 1 sample missing</t>
-  </si>
-  <si>
     <t>UNCERTAIN: codes 1 (related/sibling) and 2 (haploidentical) are inferred from clinical epidemiology (paper reports 72-74% unrelated); the paper does not provide an explicit coding key; MERGE NOTE: three-level code; do not collapse to binary without confirming how haplo donors should be treated</t>
   </si>
   <si>
@@ -3481,13 +3481,19 @@
   </si>
   <si>
     <t>PATIENT_LEVEL. Redundant with cmvD + cmvR (cmvDR = paste(cmvD, cmvR, sep='/')). Would retain cmvD and cmvR for regression; cmvDR is a convenience combination column.</t>
+  </si>
+  <si>
+    <t>Named sampling time point: COND = Day -7 (conditioning phase, pre-transplant); 0 = Day 0 (transplant day); 7/14/21/28 = Days 7/14/21/28 post-transplant; POST = Day 35; DONOR = Day -50 (donor stool samples, 2 rows); IDX = Day -25 (1 row, index). Timepoint and Day are in perfect 1:1 correspondence with no discrepancies.</t>
+  </si>
+  <si>
+    <t>Relationship between the stem cell donor and recipient: 0 = unrelated donor ; 1 = sibling; 2 = haploidentical donor ; 1 sample missing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3535,13 +3541,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3579,7 +3593,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3613,6 +3627,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3647,9 +3662,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3822,11 +3838,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3861,7 +3877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3890,7 +3906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -3919,7 +3935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3948,7 +3964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3977,7 +3993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -4003,7 +4019,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4029,7 +4045,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -4058,7 +4074,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -4084,7 +4100,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -4113,7 +4129,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -4142,7 +4158,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -4171,7 +4187,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -4200,7 +4216,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -4229,7 +4245,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -4258,7 +4274,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -4284,7 +4300,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -4313,7 +4329,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -4342,7 +4358,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -4371,7 +4387,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -4400,7 +4416,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -4429,7 +4445,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -4458,7 +4474,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -4487,7 +4503,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -4516,7 +4532,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -4545,7 +4561,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -4574,7 +4590,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>109</v>
       </c>
@@ -4609,11 +4625,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4648,7 +4664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4677,7 +4693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -4706,7 +4722,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>119</v>
       </c>
@@ -4735,7 +4751,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>123</v>
       </c>
@@ -4764,7 +4780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>126</v>
       </c>
@@ -4793,7 +4809,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -4822,7 +4838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>133</v>
       </c>
@@ -4851,7 +4867,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -4880,7 +4896,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -4909,7 +4925,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -4938,7 +4954,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>148</v>
       </c>
@@ -4967,7 +4983,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>152</v>
       </c>
@@ -4996,7 +5012,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -5025,7 +5041,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -5054,7 +5070,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -5083,7 +5099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>165</v>
       </c>
@@ -5112,7 +5128,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -5141,7 +5157,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>173</v>
       </c>
@@ -5170,7 +5186,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>177</v>
       </c>
@@ -5199,7 +5215,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>181</v>
       </c>
@@ -5228,7 +5244,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>184</v>
       </c>
@@ -5257,7 +5273,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>188</v>
       </c>
@@ -5286,7 +5302,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>192</v>
       </c>
@@ -5315,7 +5331,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>196</v>
       </c>
@@ -5344,7 +5360,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -5373,7 +5389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>201</v>
       </c>
@@ -5402,7 +5418,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>205</v>
       </c>
@@ -5431,7 +5447,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>209</v>
       </c>
@@ -5460,7 +5476,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -5489,7 +5505,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>217</v>
       </c>
@@ -5518,7 +5534,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>221</v>
       </c>
@@ -5547,7 +5563,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>225</v>
       </c>
@@ -5576,7 +5592,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>229</v>
       </c>
@@ -5605,7 +5621,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>233</v>
       </c>
@@ -5634,7 +5650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -5663,7 +5679,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>239</v>
       </c>
@@ -5692,7 +5708,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -5718,7 +5734,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>245</v>
       </c>
@@ -5747,7 +5763,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>109</v>
       </c>
@@ -5773,7 +5789,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>250</v>
       </c>
@@ -5802,7 +5818,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>254</v>
       </c>
@@ -5828,7 +5844,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -5857,7 +5873,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>260</v>
       </c>
@@ -5883,7 +5899,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -5912,7 +5928,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>266</v>
       </c>
@@ -5938,7 +5954,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>269</v>
       </c>
@@ -5964,7 +5980,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>272</v>
       </c>
@@ -5993,7 +6009,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>276</v>
       </c>
@@ -6019,7 +6035,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>279</v>
       </c>
@@ -6048,7 +6064,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -6077,7 +6093,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>286</v>
       </c>
@@ -6106,7 +6122,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>290</v>
       </c>
@@ -6132,7 +6148,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -6158,7 +6174,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>296</v>
       </c>
@@ -6187,7 +6203,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>300</v>
       </c>
@@ -6213,7 +6229,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>303</v>
       </c>
@@ -6245,11 +6261,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6284,7 +6300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6313,7 +6329,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>233</v>
       </c>
@@ -6342,7 +6358,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -6371,7 +6387,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>109</v>
       </c>
@@ -6400,7 +6416,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>315</v>
       </c>
@@ -6429,7 +6445,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>319</v>
       </c>
@@ -6458,7 +6474,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>322</v>
       </c>
@@ -6487,7 +6503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -6513,7 +6529,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>254</v>
       </c>
@@ -6539,7 +6555,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -6565,7 +6581,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>329</v>
       </c>
@@ -6594,7 +6610,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>333</v>
       </c>
@@ -6623,7 +6639,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>337</v>
       </c>
@@ -6649,7 +6665,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>340</v>
       </c>
@@ -6675,7 +6691,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>342</v>
       </c>
@@ -6704,7 +6720,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>345</v>
       </c>
@@ -6730,7 +6746,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>348</v>
       </c>
@@ -6759,7 +6775,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>352</v>
       </c>
@@ -6788,7 +6804,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>356</v>
       </c>
@@ -6817,7 +6833,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>360</v>
       </c>
@@ -6846,7 +6862,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>364</v>
       </c>
@@ -6875,7 +6891,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>368</v>
       </c>
@@ -6910,11 +6926,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6949,7 +6965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6978,7 +6994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7007,7 +7023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>374</v>
       </c>
@@ -7036,7 +7052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>376</v>
       </c>
@@ -7065,7 +7081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -7094,7 +7110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>381</v>
       </c>
@@ -7123,7 +7139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>384</v>
       </c>
@@ -7152,7 +7168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>386</v>
       </c>
@@ -7181,7 +7197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>389</v>
       </c>
@@ -7210,7 +7226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>392</v>
       </c>
@@ -7236,7 +7252,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>395</v>
       </c>
@@ -7262,7 +7278,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>398</v>
       </c>
@@ -7288,7 +7304,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>401</v>
       </c>
@@ -7314,7 +7330,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>404</v>
       </c>
@@ -7343,7 +7359,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>408</v>
       </c>
@@ -7372,7 +7388,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>412</v>
       </c>
@@ -7401,7 +7417,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>416</v>
       </c>
@@ -7427,7 +7443,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>419</v>
       </c>
@@ -7456,7 +7472,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>423</v>
       </c>
@@ -7482,7 +7498,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>426</v>
       </c>
@@ -7511,7 +7527,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>430</v>
       </c>
@@ -7537,7 +7553,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>433</v>
       </c>
@@ -7566,7 +7582,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>436</v>
       </c>
@@ -7595,7 +7611,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>439</v>
       </c>
@@ -7624,7 +7640,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>441</v>
       </c>
@@ -7650,7 +7666,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>444</v>
       </c>
@@ -7676,7 +7692,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>447</v>
       </c>
@@ -7702,7 +7718,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>451</v>
       </c>
@@ -7731,7 +7747,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>455</v>
       </c>
@@ -7757,7 +7773,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>458</v>
       </c>
@@ -7783,7 +7799,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>460</v>
       </c>
@@ -7809,7 +7825,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>463</v>
       </c>
@@ -7835,7 +7851,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>466</v>
       </c>
@@ -7864,7 +7880,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>468</v>
       </c>
@@ -7893,7 +7909,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>472</v>
       </c>
@@ -7919,7 +7935,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>475</v>
       </c>
@@ -7948,7 +7964,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>478</v>
       </c>
@@ -7974,7 +7990,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>480</v>
       </c>
@@ -8000,7 +8016,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>482</v>
       </c>
@@ -8029,7 +8045,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>486</v>
       </c>
@@ -8058,7 +8074,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>490</v>
       </c>
@@ -8087,7 +8103,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>494</v>
       </c>
@@ -8116,7 +8132,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>497</v>
       </c>
@@ -8142,7 +8158,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>499</v>
       </c>
@@ -8168,7 +8184,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>501</v>
       </c>
@@ -8179,7 +8195,7 @@
         <v>67</v>
       </c>
       <c r="D46">
-        <v>69.09999999999999</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="E46" t="s">
         <v>26</v>
@@ -8194,7 +8210,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>504</v>
       </c>
@@ -8205,7 +8221,7 @@
         <v>67</v>
       </c>
       <c r="D47">
-        <v>69.09999999999999</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="E47" t="s">
         <v>26</v>
@@ -8220,7 +8236,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>506</v>
       </c>
@@ -8246,7 +8262,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>509</v>
       </c>
@@ -8275,7 +8291,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>512</v>
       </c>
@@ -8304,7 +8320,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>516</v>
       </c>
@@ -8330,7 +8346,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>519</v>
       </c>
@@ -8356,7 +8372,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>521</v>
       </c>
@@ -8382,7 +8398,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>524</v>
       </c>
@@ -8408,7 +8424,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>527</v>
       </c>
@@ -8434,7 +8450,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>530</v>
       </c>
@@ -8463,7 +8479,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>532</v>
       </c>
@@ -8489,7 +8505,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>534</v>
       </c>
@@ -8518,7 +8534,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>538</v>
       </c>
@@ -8547,7 +8563,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>541</v>
       </c>
@@ -8573,7 +8589,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>544</v>
       </c>
@@ -8599,7 +8615,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>547</v>
       </c>
@@ -8628,7 +8644,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>550</v>
       </c>
@@ -8657,7 +8673,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>554</v>
       </c>
@@ -8683,7 +8699,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>557</v>
       </c>
@@ -8709,7 +8725,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>560</v>
       </c>
@@ -8735,7 +8751,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>562</v>
       </c>
@@ -8761,7 +8777,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>564</v>
       </c>
@@ -8793,11 +8809,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8832,7 +8848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -8858,7 +8874,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>568</v>
       </c>
@@ -8887,7 +8903,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>572</v>
       </c>
@@ -8916,7 +8932,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>575</v>
       </c>
@@ -8945,7 +8961,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>579</v>
       </c>
@@ -8974,7 +8990,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>582</v>
       </c>
@@ -9000,7 +9016,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>585</v>
       </c>
@@ -9029,7 +9045,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>589</v>
       </c>
@@ -9058,7 +9074,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>593</v>
       </c>
@@ -9087,7 +9103,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>597</v>
       </c>
@@ -9116,7 +9132,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>601</v>
       </c>
@@ -9142,7 +9158,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>604</v>
       </c>
@@ -9171,7 +9187,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>607</v>
       </c>
@@ -9197,7 +9213,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>609</v>
       </c>
@@ -9226,7 +9242,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>613</v>
       </c>
@@ -9237,7 +9253,7 @@
         <v>17</v>
       </c>
       <c r="D16">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -9255,7 +9271,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>617</v>
       </c>
@@ -9281,7 +9297,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>620</v>
       </c>
@@ -9307,7 +9323,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>623</v>
       </c>
@@ -9333,7 +9349,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>626</v>
       </c>
@@ -9362,7 +9378,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>630</v>
       </c>
@@ -9391,7 +9407,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>634</v>
       </c>
@@ -9420,7 +9436,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>638</v>
       </c>
@@ -9446,7 +9462,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>641</v>
       </c>
@@ -9472,7 +9488,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>260</v>
       </c>
@@ -9501,7 +9517,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>647</v>
       </c>
@@ -9527,7 +9543,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>650</v>
       </c>
@@ -9553,7 +9569,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>653</v>
       </c>
@@ -9582,7 +9598,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>657</v>
       </c>
@@ -9608,7 +9624,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>659</v>
       </c>
@@ -9637,7 +9653,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>663</v>
       </c>
@@ -9663,7 +9679,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>666</v>
       </c>
@@ -9689,7 +9705,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>669</v>
       </c>
@@ -9715,7 +9731,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>672</v>
       </c>
@@ -9750,11 +9766,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9789,7 +9805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -9818,7 +9834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>130</v>
       </c>
@@ -9847,7 +9863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -9876,7 +9892,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>376</v>
       </c>
@@ -9905,7 +9921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>682</v>
       </c>
@@ -9934,7 +9950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>384</v>
       </c>
@@ -9963,7 +9979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>686</v>
       </c>
@@ -9992,7 +10008,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>423</v>
       </c>
@@ -10018,7 +10034,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>692</v>
       </c>
@@ -10044,7 +10060,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>557</v>
       </c>
@@ -10070,7 +10086,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>697</v>
       </c>
@@ -10096,7 +10112,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>700</v>
       </c>
@@ -10125,7 +10141,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>412</v>
       </c>
@@ -10154,7 +10170,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>707</v>
       </c>
@@ -10183,7 +10199,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>711</v>
       </c>
@@ -10209,7 +10225,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>714</v>
       </c>
@@ -10238,7 +10254,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>718</v>
       </c>
@@ -10267,7 +10283,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>722</v>
       </c>
@@ -10296,7 +10312,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>726</v>
       </c>
@@ -10325,7 +10341,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>730</v>
       </c>
@@ -10354,7 +10370,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>734</v>
       </c>
@@ -10383,7 +10399,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>738</v>
       </c>
@@ -10412,7 +10428,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>741</v>
       </c>
@@ -10441,7 +10457,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>745</v>
       </c>
@@ -10470,7 +10486,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>748</v>
       </c>
@@ -10499,7 +10515,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>750</v>
       </c>
@@ -10528,7 +10544,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>752</v>
       </c>
@@ -10557,7 +10573,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>754</v>
       </c>
@@ -10586,7 +10602,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>758</v>
       </c>
@@ -10615,7 +10631,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>761</v>
       </c>
@@ -10644,7 +10660,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>765</v>
       </c>
@@ -10673,7 +10689,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>769</v>
       </c>
@@ -10702,7 +10718,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>772</v>
       </c>
@@ -10731,7 +10747,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>776</v>
       </c>
@@ -10760,7 +10776,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>779</v>
       </c>
@@ -10789,7 +10805,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>783</v>
       </c>
@@ -10818,7 +10834,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>786</v>
       </c>
@@ -10847,7 +10863,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>790</v>
       </c>
@@ -10876,7 +10892,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>794</v>
       </c>
@@ -10905,7 +10921,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>798</v>
       </c>
@@ -10934,7 +10950,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>802</v>
       </c>
@@ -10963,7 +10979,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>806</v>
       </c>
@@ -10974,7 +10990,7 @@
         <v>60</v>
       </c>
       <c r="D43">
-        <v>75.90000000000001</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -10992,7 +11008,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>810</v>
       </c>
@@ -11021,7 +11037,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>813</v>
       </c>
@@ -11050,7 +11066,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>817</v>
       </c>
@@ -11079,7 +11095,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>458</v>
       </c>
@@ -11114,11 +11130,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11153,7 +11169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -11182,7 +11198,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>826</v>
       </c>
@@ -11211,7 +11227,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>830</v>
       </c>
@@ -11240,7 +11256,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>389</v>
       </c>
@@ -11269,7 +11285,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -11295,7 +11311,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>837</v>
       </c>
@@ -11324,7 +11340,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>841</v>
       </c>
@@ -11350,7 +11366,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -11373,15 +11389,15 @@
         <v>844</v>
       </c>
       <c r="H9" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K9" t="s">
         <v>845</v>
       </c>
-      <c r="K9" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>846</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>847</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -11399,15 +11415,15 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
+        <v>847</v>
+      </c>
+      <c r="H10" t="s">
         <v>848</v>
       </c>
-      <c r="H10" t="s">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>849</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>850</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -11416,7 +11432,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -11425,15 +11441,15 @@
         <v>32</v>
       </c>
       <c r="G11" t="s">
+        <v>850</v>
+      </c>
+      <c r="H11" t="s">
         <v>851</v>
       </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>852</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>853</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -11454,15 +11470,15 @@
         <v>316</v>
       </c>
       <c r="H12" t="s">
+        <v>853</v>
+      </c>
+      <c r="K12" t="s">
         <v>854</v>
       </c>
-      <c r="K12" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>855</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>856</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -11471,7 +11487,7 @@
         <v>3</v>
       </c>
       <c r="D13">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -11480,18 +11496,18 @@
         <v>27</v>
       </c>
       <c r="G13" t="s">
+        <v>856</v>
+      </c>
+      <c r="H13" t="s">
         <v>857</v>
       </c>
-      <c r="H13" t="s">
+      <c r="K13" t="s">
         <v>858</v>
       </c>
-      <c r="K13" t="s">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>859</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>860</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -11509,18 +11525,18 @@
         <v>27</v>
       </c>
       <c r="G14" t="s">
+        <v>860</v>
+      </c>
+      <c r="H14" t="s">
         <v>861</v>
       </c>
-      <c r="H14" t="s">
+      <c r="K14" t="s">
         <v>862</v>
       </c>
-      <c r="K14" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>863</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>864</v>
       </c>
       <c r="B15">
         <v>65</v>
@@ -11538,15 +11554,15 @@
         <v>36</v>
       </c>
       <c r="G15" t="s">
+        <v>864</v>
+      </c>
+      <c r="H15" t="s">
         <v>865</v>
       </c>
-      <c r="H15" t="s">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>866</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>867</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -11567,10 +11583,10 @@
         <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -11590,18 +11606,18 @@
         <v>32</v>
       </c>
       <c r="G17" t="s">
+        <v>868</v>
+      </c>
+      <c r="H17" t="s">
         <v>869</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
         <v>870</v>
       </c>
-      <c r="K17" t="s">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>871</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>872</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -11622,15 +11638,15 @@
         <v>316</v>
       </c>
       <c r="H18" t="s">
+        <v>872</v>
+      </c>
+      <c r="K18" t="s">
         <v>873</v>
       </c>
-      <c r="K18" t="s">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>874</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>875</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -11648,18 +11664,18 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
+        <v>875</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K19" t="s">
         <v>876</v>
       </c>
-      <c r="H19" t="s">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>877</v>
-      </c>
-      <c r="K19" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>879</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -11680,10 +11696,10 @@
         <v>316</v>
       </c>
       <c r="H20" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>499</v>
       </c>
@@ -11706,12 +11722,12 @@
         <v>316</v>
       </c>
       <c r="H21" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -11729,18 +11745,18 @@
         <v>27</v>
       </c>
       <c r="G22" t="s">
+        <v>881</v>
+      </c>
+      <c r="H22" t="s">
+        <v>882</v>
+      </c>
+      <c r="K22" t="s">
         <v>883</v>
       </c>
-      <c r="H22" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>884</v>
-      </c>
-      <c r="K22" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>886</v>
       </c>
       <c r="B23">
         <v>28</v>
@@ -11749,7 +11765,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E23" t="s">
         <v>26</v>
@@ -11758,18 +11774,18 @@
         <v>27</v>
       </c>
       <c r="G23" t="s">
+        <v>885</v>
+      </c>
+      <c r="H23" t="s">
+        <v>886</v>
+      </c>
+      <c r="K23" t="s">
         <v>887</v>
       </c>
-      <c r="H23" t="s">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>888</v>
-      </c>
-      <c r="K23" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>890</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -11787,18 +11803,18 @@
         <v>27</v>
       </c>
       <c r="G24" t="s">
+        <v>889</v>
+      </c>
+      <c r="H24" t="s">
+        <v>890</v>
+      </c>
+      <c r="K24" t="s">
         <v>891</v>
       </c>
-      <c r="H24" t="s">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>892</v>
-      </c>
-      <c r="K24" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>894</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -11816,18 +11832,18 @@
         <v>27</v>
       </c>
       <c r="G25" t="s">
+        <v>893</v>
+      </c>
+      <c r="H25" t="s">
+        <v>894</v>
+      </c>
+      <c r="K25" t="s">
         <v>895</v>
       </c>
-      <c r="H25" t="s">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>896</v>
-      </c>
-      <c r="K25" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>898</v>
       </c>
       <c r="B26">
         <v>15</v>
@@ -11845,15 +11861,15 @@
         <v>27</v>
       </c>
       <c r="G26" t="s">
+        <v>897</v>
+      </c>
+      <c r="H26" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>899</v>
-      </c>
-      <c r="H26" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>901</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -11874,12 +11890,12 @@
         <v>316</v>
       </c>
       <c r="H27" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B28">
         <v>21</v>
@@ -11888,7 +11904,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E28" t="s">
         <v>26</v>
@@ -11897,15 +11913,15 @@
         <v>27</v>
       </c>
       <c r="G28" t="s">
+        <v>902</v>
+      </c>
+      <c r="H28" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>904</v>
-      </c>
-      <c r="H28" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>906</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -11923,15 +11939,15 @@
         <v>32</v>
       </c>
       <c r="H29" t="s">
+        <v>905</v>
+      </c>
+      <c r="K29" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>907</v>
-      </c>
-      <c r="K29" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>909</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -11949,15 +11965,15 @@
         <v>32</v>
       </c>
       <c r="H30" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="K30" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -11978,12 +11994,12 @@
         <v>316</v>
       </c>
       <c r="H31" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -12004,12 +12020,12 @@
         <v>316</v>
       </c>
       <c r="H32" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -12027,18 +12043,18 @@
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H33" t="s">
+        <v>914</v>
+      </c>
+      <c r="K33" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>916</v>
-      </c>
-      <c r="K33" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>918</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -12059,10 +12075,10 @@
         <v>316</v>
       </c>
       <c r="H34" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="K34" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -12071,11 +12087,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12110,7 +12126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -12130,18 +12146,18 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="H2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="K2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B3">
         <v>12</v>
@@ -12159,13 +12175,13 @@
         <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H3" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -12185,13 +12201,13 @@
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="H4" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>235</v>
       </c>
@@ -12211,13 +12227,13 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="H5" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>830</v>
       </c>
@@ -12237,16 +12253,16 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="H6" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="K6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>389</v>
       </c>
@@ -12266,15 +12282,15 @@
         <v>32</v>
       </c>
       <c r="G7" t="s">
+        <v>930</v>
+      </c>
+      <c r="H7" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>932</v>
-      </c>
-      <c r="H7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>934</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -12292,15 +12308,15 @@
         <v>32</v>
       </c>
       <c r="G8" t="s">
+        <v>933</v>
+      </c>
+      <c r="H8" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>935</v>
-      </c>
-      <c r="H8" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>937</v>
       </c>
       <c r="B9">
         <v>34</v>
@@ -12318,18 +12334,18 @@
         <v>27</v>
       </c>
       <c r="G9" t="s">
+        <v>936</v>
+      </c>
+      <c r="H9" t="s">
+        <v>937</v>
+      </c>
+      <c r="K9" t="s">
         <v>938</v>
       </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>939</v>
-      </c>
-      <c r="K9" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>941</v>
       </c>
       <c r="B10">
         <v>77</v>
@@ -12347,13 +12363,13 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="H10" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>557</v>
       </c>
@@ -12376,10 +12392,10 @@
         <v>695</v>
       </c>
       <c r="H11" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>423</v>
       </c>
@@ -12399,15 +12415,15 @@
         <v>27</v>
       </c>
       <c r="G12" t="s">
+        <v>943</v>
+      </c>
+      <c r="H12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>945</v>
-      </c>
-      <c r="H12" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>947</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -12425,15 +12441,15 @@
         <v>32</v>
       </c>
       <c r="G13" t="s">
+        <v>946</v>
+      </c>
+      <c r="H13" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>948</v>
-      </c>
-      <c r="H13" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>950</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -12451,18 +12467,18 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
+        <v>949</v>
+      </c>
+      <c r="H14" t="s">
+        <v>950</v>
+      </c>
+      <c r="K14" t="s">
         <v>951</v>
       </c>
-      <c r="H14" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>952</v>
-      </c>
-      <c r="K14" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>954</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -12480,18 +12496,18 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
+        <v>953</v>
+      </c>
+      <c r="H15" t="s">
+        <v>954</v>
+      </c>
+      <c r="K15" t="s">
         <v>955</v>
       </c>
-      <c r="H15" t="s">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>956</v>
-      </c>
-      <c r="K15" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>958</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -12509,18 +12525,18 @@
         <v>32</v>
       </c>
       <c r="G16" t="s">
+        <v>957</v>
+      </c>
+      <c r="H16" t="s">
+        <v>958</v>
+      </c>
+      <c r="K16" t="s">
         <v>959</v>
       </c>
-      <c r="H16" t="s">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>960</v>
-      </c>
-      <c r="K16" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>962</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -12541,12 +12557,12 @@
         <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -12567,10 +12583,10 @@
         <v>316</v>
       </c>
       <c r="H18" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>752</v>
       </c>
@@ -12593,12 +12609,12 @@
         <v>316</v>
       </c>
       <c r="H19" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B20">
         <v>9</v>
@@ -12616,15 +12632,15 @@
         <v>32</v>
       </c>
       <c r="G20" t="s">
+        <v>966</v>
+      </c>
+      <c r="H20" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>968</v>
-      </c>
-      <c r="H20" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>970</v>
       </c>
       <c r="B21">
         <v>9</v>
@@ -12642,18 +12658,18 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
+        <v>969</v>
+      </c>
+      <c r="H21" t="s">
+        <v>970</v>
+      </c>
+      <c r="K21" t="s">
         <v>971</v>
       </c>
-      <c r="H21" t="s">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>972</v>
-      </c>
-      <c r="K21" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>974</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -12671,18 +12687,18 @@
         <v>32</v>
       </c>
       <c r="G22" t="s">
+        <v>973</v>
+      </c>
+      <c r="H22" t="s">
+        <v>974</v>
+      </c>
+      <c r="K22" t="s">
         <v>975</v>
       </c>
-      <c r="H22" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>976</v>
-      </c>
-      <c r="K22" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>978</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -12700,16 +12716,16 @@
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="H23" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="K23" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>560</v>
       </c>
@@ -12732,12 +12748,12 @@
         <v>56</v>
       </c>
       <c r="H24" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -12755,13 +12771,13 @@
         <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="H25" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>468</v>
       </c>
@@ -12781,15 +12797,15 @@
         <v>32</v>
       </c>
       <c r="G26" t="s">
+        <v>983</v>
+      </c>
+      <c r="H26" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>985</v>
-      </c>
-      <c r="H26" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>987</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -12807,15 +12823,15 @@
         <v>27</v>
       </c>
       <c r="G27" t="s">
+        <v>986</v>
+      </c>
+      <c r="H27" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>988</v>
-      </c>
-      <c r="H27" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" t="s">
-        <v>990</v>
       </c>
       <c r="B28">
         <v>6</v>
@@ -12833,15 +12849,15 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
+        <v>989</v>
+      </c>
+      <c r="H28" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>991</v>
-      </c>
-      <c r="H28" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>993</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -12859,15 +12875,15 @@
         <v>27</v>
       </c>
       <c r="G29" t="s">
+        <v>992</v>
+      </c>
+      <c r="H29" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>994</v>
-      </c>
-      <c r="H29" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>996</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -12888,15 +12904,15 @@
         <v>230</v>
       </c>
       <c r="H30" t="s">
+        <v>995</v>
+      </c>
+      <c r="K30" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>997</v>
-      </c>
-      <c r="K30" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>999</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -12914,13 +12930,13 @@
         <v>27</v>
       </c>
       <c r="G31" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H31" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -12940,10 +12956,10 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
@@ -12952,11 +12968,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12991,7 +13007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -13011,7 +13027,7 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -13020,9 +13036,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B3">
         <v>50</v>
@@ -13040,18 +13056,18 @@
         <v>32</v>
       </c>
       <c r="G3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K3" t="s">
         <v>1006</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>1007</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>1009</v>
       </c>
       <c r="B4">
         <v>118</v>
@@ -13069,18 +13085,18 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="H4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="K4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B5">
         <v>50</v>
@@ -13098,18 +13114,18 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>1013</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>1015</v>
       </c>
       <c r="B6">
         <v>82</v>
@@ -13124,21 +13140,21 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H6" t="s">
         <v>1016</v>
       </c>
-      <c r="G6" t="s">
+      <c r="K6" t="s">
         <v>1017</v>
       </c>
-      <c r="H6" t="s">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>1018</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>1020</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -13159,15 +13175,15 @@
         <v>491</v>
       </c>
       <c r="H7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>1021</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>1023</v>
       </c>
       <c r="B8">
         <v>46</v>
@@ -13182,21 +13198,21 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="K8" t="s">
         <v>1024</v>
       </c>
-      <c r="H8" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>1025</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>1027</v>
       </c>
       <c r="B9">
         <v>47</v>
@@ -13211,21 +13227,21 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G9" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K9" t="s">
         <v>1028</v>
       </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>1029</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>1031</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -13243,18 +13259,18 @@
         <v>32</v>
       </c>
       <c r="G10" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K10" t="s">
         <v>1032</v>
       </c>
-      <c r="H10" t="s">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>1033</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>1035</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -13272,18 +13288,18 @@
         <v>32</v>
       </c>
       <c r="G11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K11" t="s">
         <v>1036</v>
       </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>1037</v>
-      </c>
-      <c r="K11" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>1039</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -13301,18 +13317,18 @@
         <v>32</v>
       </c>
       <c r="G12" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K12" t="s">
         <v>1040</v>
       </c>
-      <c r="H12" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>1041</v>
-      </c>
-      <c r="K12" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>1043</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -13330,16 +13346,16 @@
         <v>32</v>
       </c>
       <c r="G13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K13" t="s">
         <v>1044</v>
       </c>
-      <c r="H13" t="s">
-        <v>1045</v>
-      </c>
-      <c r="K13" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>726</v>
       </c>
@@ -13359,18 +13375,18 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K14" t="s">
         <v>1047</v>
       </c>
-      <c r="H14" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>1048</v>
-      </c>
-      <c r="K14" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>1050</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -13388,16 +13404,16 @@
         <v>32</v>
       </c>
       <c r="G15" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K15" t="s">
         <v>1051</v>
       </c>
-      <c r="H15" t="s">
-        <v>1052</v>
-      </c>
-      <c r="K15" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>458</v>
       </c>
@@ -13420,15 +13436,15 @@
         <v>513</v>
       </c>
       <c r="H16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K16" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>1054</v>
-      </c>
-      <c r="K16" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>1056</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -13446,18 +13462,18 @@
         <v>27</v>
       </c>
       <c r="G17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K17" t="s">
         <v>1057</v>
       </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>1058</v>
-      </c>
-      <c r="K17" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>1060</v>
       </c>
       <c r="B18">
         <v>30</v>
@@ -13472,19 +13488,19 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G18" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K18" t="s">
         <v>1061</v>
       </c>
-      <c r="H18" t="s">
-        <v>1062</v>
-      </c>
-      <c r="K18" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>564</v>
       </c>
@@ -13504,18 +13520,18 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="H19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K19" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>1064</v>
-      </c>
-      <c r="K19" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>1066</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -13536,15 +13552,15 @@
         <v>316</v>
       </c>
       <c r="H20" t="s">
+        <v>1065</v>
+      </c>
+      <c r="K20" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>1067</v>
-      </c>
-      <c r="K20" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>1069</v>
       </c>
       <c r="B21">
         <v>18</v>
@@ -13559,21 +13575,21 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G21" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K21" t="s">
         <v>1070</v>
       </c>
-      <c r="H21" t="s">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>1071</v>
-      </c>
-      <c r="K21" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>1073</v>
       </c>
       <c r="B22">
         <v>17</v>
@@ -13588,21 +13604,21 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K22" t="s">
         <v>1074</v>
       </c>
-      <c r="H22" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>1075</v>
-      </c>
-      <c r="K22" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>1077</v>
       </c>
       <c r="B23">
         <v>30</v>
@@ -13611,27 +13627,27 @@
         <v>41</v>
       </c>
       <c r="D23">
-        <v>34.7</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="E23" t="s">
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K23" t="s">
         <v>1078</v>
       </c>
-      <c r="H23" t="s">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>1079</v>
-      </c>
-      <c r="K23" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>1081</v>
       </c>
       <c r="B24">
         <v>49</v>
@@ -13646,21 +13662,21 @@
         <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G24" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K24" t="s">
         <v>1082</v>
       </c>
-      <c r="H24" t="s">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>1083</v>
-      </c>
-      <c r="K24" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>1085</v>
       </c>
       <c r="B25">
         <v>18</v>
@@ -13675,19 +13691,19 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G25" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="H25" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="K25" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>423</v>
       </c>
@@ -13707,16 +13723,16 @@
         <v>36</v>
       </c>
       <c r="G26" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K26" t="s">
         <v>1088</v>
       </c>
-      <c r="H26" t="s">
-        <v>1089</v>
-      </c>
-      <c r="K26" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>641</v>
       </c>
@@ -13739,15 +13755,15 @@
         <v>405</v>
       </c>
       <c r="H27" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="K27" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -13765,18 +13781,18 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K28" t="s">
         <v>1093</v>
       </c>
-      <c r="H28" t="s">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>1094</v>
-      </c>
-      <c r="K28" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>1096</v>
       </c>
       <c r="B29">
         <v>11</v>
@@ -13794,18 +13810,18 @@
         <v>32</v>
       </c>
       <c r="G29" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K29" t="s">
         <v>1097</v>
       </c>
-      <c r="H29" t="s">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>1098</v>
-      </c>
-      <c r="K29" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>1100</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -13814,7 +13830,7 @@
         <v>98</v>
       </c>
       <c r="D30">
-        <v>83.09999999999999</v>
+        <v>83.1</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -13823,18 +13839,18 @@
         <v>32</v>
       </c>
       <c r="G30" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K30" t="s">
         <v>1101</v>
       </c>
-      <c r="H30" t="s">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>1102</v>
-      </c>
-      <c r="K30" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>1104</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -13852,18 +13868,18 @@
         <v>32</v>
       </c>
       <c r="G31" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K31" t="s">
         <v>1105</v>
       </c>
-      <c r="H31" t="s">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>1106</v>
-      </c>
-      <c r="K31" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" t="s">
-        <v>1108</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -13881,18 +13897,18 @@
         <v>32</v>
       </c>
       <c r="G32" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K32" t="s">
         <v>1109</v>
       </c>
-      <c r="H32" t="s">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>1110</v>
-      </c>
-      <c r="K32" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
-        <v>1112</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -13910,18 +13926,18 @@
         <v>32</v>
       </c>
       <c r="G33" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K33" t="s">
         <v>1113</v>
       </c>
-      <c r="H33" t="s">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>1114</v>
-      </c>
-      <c r="K33" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>1116</v>
       </c>
       <c r="B34">
         <v>40</v>
@@ -13939,18 +13955,18 @@
         <v>27</v>
       </c>
       <c r="G34" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K34" t="s">
         <v>1117</v>
       </c>
-      <c r="H34" t="s">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>1118</v>
-      </c>
-      <c r="K34" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" t="s">
-        <v>1120</v>
       </c>
       <c r="B35">
         <v>37</v>
@@ -13968,18 +13984,18 @@
         <v>27</v>
       </c>
       <c r="G35" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K35" t="s">
         <v>1121</v>
       </c>
-      <c r="H35" t="s">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>1122</v>
-      </c>
-      <c r="K35" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>1124</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -13997,18 +14013,18 @@
         <v>32</v>
       </c>
       <c r="G36" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1124</v>
+      </c>
+      <c r="K36" t="s">
         <v>1125</v>
       </c>
-      <c r="H36" t="s">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>1126</v>
-      </c>
-      <c r="K36" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" t="s">
-        <v>1128</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -14023,21 +14039,21 @@
         <v>115</v>
       </c>
       <c r="F37" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G37" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K37" t="s">
         <v>1129</v>
       </c>
-      <c r="H37" t="s">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>1130</v>
-      </c>
-      <c r="K37" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" t="s">
-        <v>1132</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -14058,15 +14074,15 @@
         <v>610</v>
       </c>
       <c r="H38" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K38" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>1133</v>
-      </c>
-      <c r="K38" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" t="s">
-        <v>1135</v>
       </c>
       <c r="B39">
         <v>28</v>
@@ -14081,21 +14097,21 @@
         <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G39" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K39" t="s">
         <v>1136</v>
       </c>
-      <c r="H39" t="s">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>1137</v>
-      </c>
-      <c r="K39" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" t="s">
-        <v>1139</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -14113,18 +14129,18 @@
         <v>32</v>
       </c>
       <c r="G40" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K40" t="s">
         <v>1140</v>
       </c>
-      <c r="H40" t="s">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>1141</v>
-      </c>
-      <c r="K40" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" t="s">
-        <v>1143</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -14142,18 +14158,18 @@
         <v>32</v>
       </c>
       <c r="G41" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K41" t="s">
         <v>1144</v>
       </c>
-      <c r="H41" t="s">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>1145</v>
-      </c>
-      <c r="K41" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>1147</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -14171,18 +14187,18 @@
         <v>32</v>
       </c>
       <c r="G42" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K42" t="s">
         <v>1144</v>
       </c>
-      <c r="H42" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K42" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -14200,16 +14216,22 @@
         <v>32</v>
       </c>
       <c r="G43" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K43" t="s">
         <v>1150</v>
-      </c>
-      <c r="H43" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K43" t="s">
-        <v>1152</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{170051ed-867f-4092-a6af-8a42e27b7e09}" enabled="1" method="Standard" siteId="{5217e0e7-539d-4563-b1bf-7c6dcf074f91}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>